--- a/results/job_matches_2026-02-26.xlsx
+++ b/results/job_matches_2026-02-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,95 +643,95 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Technical Product Owner - Data Platform</t>
+          <t>Software Engineering III</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Speridian Technologies</t>
+          <t>Equitable</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>EMR, API Gateway, ECS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Flume, Zookeeper</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=829043b08de7d050</t>
+          <t>https://www.indeed.com/viewjob?jk=1753914a33e85905</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-5</t>
+          <t>Senior Advisor II, Data Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=656bcb1553978517</t>
+          <t>https://www.indeed.com/viewjob?jk=21bd27b152469170</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SRS Distribution</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,49 +741,49 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01278285fb17a0ad</t>
+          <t>https://www.indeed.com/viewjob?jk=e89cb44acf96f0ce</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer - Boston</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Xylem</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Davis, CA, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1dd8e4a22e1c65</t>
+          <t>https://www.indeed.com/viewjob?jk=b9b3e4586db8c7fd</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr AWS Data Engineer (Contract)</t>
+          <t>Software Engineer II (USA)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,120 +793,120 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c7808d3f82f3dd3</t>
+          <t>https://www.indeed.com/viewjob?jk=079fa62336e07385</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Remote)</t>
+          <t>Senior Technical Product Owner - Data Platform</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Inspira Financial</t>
+          <t>Speridian Technologies</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
+          <t>EMR, API Gateway, ECS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03f6284daa41bb63</t>
+          <t>https://www.indeed.com/viewjob?jk=829043b08de7d050</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Solution Engineer I</t>
+          <t>Senior Databricks Developer-5</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Associated Wholesale Grocers</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5985bee213bf40</t>
+          <t>https://www.indeed.com/viewjob?jk=656bcb1553978517</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior AI / ML Engineer</t>
+          <t>Senior Machine Learning Ops Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Select Minds LLC</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fbed1e14e3c66df</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8203af416f8f7f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Databricks Managing Consultant Engineer - Digital Velocity</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>GovWorx</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, Scala, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Spark, PySpark, Scala, MySQL, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91700d9dd67b6cb5</t>
+          <t>https://www.indeed.com/viewjob?jk=8ee6445287271c9d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Gradient AI</t>
+          <t>SRS Distribution</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08f4a08591f4e565</t>
+          <t>https://www.indeed.com/viewjob?jk=01278285fb17a0ad</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>CCaaS Integration Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ripple</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Athena, S3, API Gateway, ECS, Databricks, Spark, Scala</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, SQS, API Gateway, ECS, Scala, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6988d9d372dc66d3</t>
+          <t>https://www.indeed.com/viewjob?jk=da6da8715ca8e326</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Advisor II, DevOps Engineering</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, ELT, MLOps, MLflow, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,102 +1056,102 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d0a69e61901c434</t>
+          <t>https://www.indeed.com/viewjob?jk=9cc7c35c6dd83d4e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Google Data Architect</t>
+          <t>Sr AWS Data Engineer (Contract)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f601a32273482463</t>
+          <t>https://www.indeed.com/viewjob?jk=3c7808d3f82f3dd3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Google Data Architect</t>
+          <t>Sr. Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Inspira Financial</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49947d743d3056f4</t>
+          <t>https://www.indeed.com/viewjob?jk=03f6284daa41bb63</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Google Data Architect</t>
+          <t>Sr. Incident Response Engineer (Remote)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Frontdoor</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de9ca192b1459954</t>
+          <t>https://www.indeed.com/viewjob?jk=c333b0560d852231</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Google Data Architect</t>
+          <t>Sr. Incident Response Engineer (Remote)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Frontdoor</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b716973859a778f</t>
+          <t>https://www.indeed.com/viewjob?jk=d0fa96abbbb8aac8</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Google Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, PostgreSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=399ec8bc372b2857</t>
+          <t>https://www.indeed.com/viewjob?jk=693f3e0a054607b0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Google Data Architect</t>
+          <t>Solution Engineer I</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Associated Wholesale Grocers</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80249c993d37b8a1</t>
+          <t>https://www.indeed.com/viewjob?jk=5e5985bee213bf40</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Google Data Architect</t>
+          <t>Senior AI / ML Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hagerstown, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,94 +1301,94 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ee8db07c7d3c455</t>
+          <t>https://www.indeed.com/viewjob?jk=4fbed1e14e3c66df</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Google Data Architect</t>
+          <t>Databricks Managing Consultant Engineer - Digital Velocity</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, Scala, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=febb3f19f40246d8</t>
+          <t>https://www.indeed.com/viewjob?jk=91700d9dd67b6cb5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Google Data Architect</t>
+          <t>Software Engineer - Backend/Cloud Services</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Hunter Industries</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fairlawn, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, DynamoDB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34111dd75fb61db0</t>
+          <t>https://www.indeed.com/viewjob?jk=b582244014f6614c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Google Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Gradient AI</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82d12b481045d0c9</t>
+          <t>https://www.indeed.com/viewjob?jk=08f4a08591f4e565</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Google Data Architect</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Ripple</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, Kinesis, Athena, S3, API Gateway, ECS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05f13ce82a3f97f6</t>
+          <t>https://www.indeed.com/viewjob?jk=6988d9d372dc66d3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Google Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e1b0e113ab0a2ae</t>
+          <t>https://www.indeed.com/viewjob?jk=7d0a69e61901c434</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Google Data Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb0219967e4aa5c7</t>
+          <t>https://www.indeed.com/viewjob?jk=30154588ed7f957f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Google Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Delta Live Tables, BigQuery, Spark, Snowflake, Databricks Lakehouse, ELT, dbt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2009ecd614434266</t>
+          <t>https://www.indeed.com/viewjob?jk=39ce7a464350b080</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Google Data Architect</t>
+          <t>Dir - Technical Operations</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Conshohocken, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9050b1d95de595b</t>
+          <t>https://www.indeed.com/viewjob?jk=ff4bbc1a531333e0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Google Data Architect</t>
+          <t>Senior Data Visualization Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>Redshift, S3, RDS, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a306bdff16c308c</t>
+          <t>https://www.indeed.com/viewjob?jk=867f580c7e3bb0e7</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
+          <t>Senior Software Engineer - API, Services and Backend Systems</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Eurest</t>
+          <t>infinite choice</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4699f552f08a017</t>
+          <t>https://www.indeed.com/viewjob?jk=27bb048397f5661f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Software Engineer - API, Services and Backend Systems</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Gradient</t>
+          <t>infinite choice</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Kafka, PostgreSQL, MongoDB, Data Modeling, CI/CD</t>
+          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b485146fc9fd8af2</t>
+          <t>https://www.indeed.com/viewjob?jk=a80d09769e3b9b3d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
+          <t>Senior Software Engineer - API, Services and Backend Systems</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Compass Group USA</t>
+          <t>infinite choice</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Hadoop, Spark, Snowflake, Oracle, PostgreSQL, MySQL</t>
+          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65b5898fc3882a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=d4e3f617e5fa8da5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Google Data Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88095bf45f8ffd12</t>
+          <t>https://www.indeed.com/viewjob?jk=f601a32273482463</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Google Data Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Al Warren Oil Company, Inc.</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ed97260c28a913a</t>
+          <t>https://www.indeed.com/viewjob?jk=49947d743d3056f4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Google Data Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Al Warren Oil Company, Inc.</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bensenville, IL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff9397037d4364c4</t>
+          <t>https://www.indeed.com/viewjob?jk=de9ca192b1459954</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Google Data Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=370f84e82c56d5a4</t>
+          <t>https://www.indeed.com/viewjob?jk=9b716973859a778f</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Google Data Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e6f7f78ae5d82f3</t>
+          <t>https://www.indeed.com/viewjob?jk=399ec8bc372b2857</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Google Data Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3763de2ff690fcf</t>
+          <t>https://www.indeed.com/viewjob?jk=80249c993d37b8a1</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Google Data Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Hagerstown, MD, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3583ff1e8ab8b831</t>
+          <t>https://www.indeed.com/viewjob?jk=4ee8db07c7d3c455</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI Analytics and Visualization Engineer</t>
+          <t>Google Data Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, ETL, Docker</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cb4ad153c4474d3</t>
+          <t>https://www.indeed.com/viewjob?jk=febb3f19f40246d8</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Azure Data Bricks Developer</t>
+          <t>Google Data Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Fairlawn, OH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Kafka, Dimensional Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=312c6b6c4770004d</t>
+          <t>https://www.indeed.com/viewjob?jk=34111dd75fb61db0</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Google Data Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dresher, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a764bcc9a479a693</t>
+          <t>https://www.indeed.com/viewjob?jk=82d12b481045d0c9</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Google Data Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8b0a891a5da57c1</t>
+          <t>https://www.indeed.com/viewjob?jk=05f13ce82a3f97f6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Google Data Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fdde135d701446e</t>
+          <t>https://www.indeed.com/viewjob?jk=7e1b0e113ab0a2ae</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Google Data Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68e8fc35af3fc28f</t>
+          <t>https://www.indeed.com/viewjob?jk=bb0219967e4aa5c7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Google Data Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>HealthMark Group</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd869bd281c90f0</t>
+          <t>https://www.indeed.com/viewjob?jk=2009ecd614434266</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps</t>
+          <t>Google Data Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Jenkins</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c10fe2dd154808d6</t>
+          <t>https://www.indeed.com/viewjob?jk=f9050b1d95de595b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Google Data Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Heads Up Technologies</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,67 +2281,67 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29123aa9e1271d0e</t>
+          <t>https://www.indeed.com/viewjob?jk=7a306bdff16c308c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Associate MLOps Engineer</t>
+          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BlueCross BlueShield of Tennessee</t>
+          <t>Eurest</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12aaaa019404f086</t>
+          <t>https://www.indeed.com/viewjob?jk=a4699f552f08a017</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr Advisor II, AI Architect</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Gradient</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Kafka, PostgreSQL, MongoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b85a978b0b96b10</t>
+          <t>https://www.indeed.com/viewjob?jk=b485146fc9fd8af2</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer II 4P/554</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Trepp</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
+          <t>Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Oracle, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd8df1b20c5849b</t>
+          <t>https://www.indeed.com/viewjob?jk=43d963e021c819ac</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Upstream Oil &amp; Gas</t>
+          <t>Senior Data Engineer, CRM</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Crescent Energy</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,102 +2421,102 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619ee2b50d37daac</t>
+          <t>https://www.indeed.com/viewjob?jk=7b266df7f25223b6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Qcells</t>
+          <t>Compass Group USA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, BigQuery, Hadoop, Spark, Snowflake, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79f22cc4bdf57e2f</t>
+          <t>https://www.indeed.com/viewjob?jk=65b5898fc3882a0c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Qcells</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47823188919dd6f3</t>
+          <t>https://www.indeed.com/viewjob?jk=1e6f7f78ae5d82f3</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ML Support Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,137 +2526,137 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4281d96efe6a7c5</t>
+          <t>https://www.indeed.com/viewjob?jk=e3763de2ff690fcf</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (Mid-Level / Senior)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Airvet</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87ce4c6973528ac7</t>
+          <t>https://www.indeed.com/viewjob?jk=3583ff1e8ab8b831</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Azure Databricks Architect-2</t>
+          <t>Infrastructure Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Mahwah, NJ, US USA</t>
+          <t>Culver City, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ddf45c77d6d98b2</t>
+          <t>https://www.indeed.com/viewjob?jk=5f75551378db568f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Teradata Developer-5</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f4f91dff933f5cc</t>
+          <t>https://www.indeed.com/viewjob?jk=88095bf45f8ffd12</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>[CoreIgnite] Senior Java Developer (AWS) - Shashank Srivastava</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Al Warren Oil Company, Inc.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,40 +2666,1160 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0866a4d4cc7dec0c</t>
+          <t>https://www.indeed.com/viewjob?jk=7ed97260c28a913a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Al Warren Oil Company, Inc.</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Bensenville, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff9397037d4364c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Altom Transport, Inc.</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=370f84e82c56d5a4</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>AI Analytics and Visualization Engineer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, ETL, Docker</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0cb4ad153c4474d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Azure Data Bricks Developer</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Infosys</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, Kafka, Dimensional Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=312c6b6c4770004d</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Ascensus</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Dresher, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a764bcc9a479a693</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Ascensus</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Newton, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d8b0a891a5da57c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Ascensus</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0fdde135d701446e</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Ascensus</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=68e8fc35af3fc28f</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>HealthMark Group</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=abd869bd281c90f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Software Engineer - DevOps</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c10fe2dd154808d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Manufacturing Systems Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Corning</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Durham, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, Power BI, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d8532be76b040bdb</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Sr Advisor II, AI Architect</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Phillips 66</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b85a978b0b96b10</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Cloud Platform Engineer - Control Plane</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>clickhouse</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, SQS, IAM, RDS, Scala, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d85ac5dbf541cd3b</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>MLOps Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Ascendion</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4687b9b235a9a6ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Trepp</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cbd8df1b20c5849b</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer – Upstream Oil &amp; Gas</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Crescent Energy</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt, Power BI</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=619ee2b50d37daac</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Qcells</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=79f22cc4bdf57e2f</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Qcells</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=47823188919dd6f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>ML Support Engineer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, CI/CD</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a4281d96efe6a7c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Backend Software Engineer (Mid-Level / Senior)</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Airvet</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=87ce4c6973528ac7</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Chewy</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62210abb12166a07</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Chewy</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=26a71508d797185b</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Los Angeles Times</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>El Segundo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, ECS, RDS, Scala, DynamoDB, CI/CD, Docker, Git, Python</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d108b54b3fe154f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Sr. Data Science Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Waystar</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Lehi, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, MLOps, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f9f1b5af5678ef92</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e73fae08616e3afd</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2cdec8d2c07ce6a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Sr. Engineer, Go To Market AI</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>brightwheel</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, S3, SNS, RDS, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=92aac63fae4e53fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Azure Databricks Architect-2</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Mahwah, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ddf45c77d6d98b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Architect</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, CI/CD, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=948ed5bfb3c6e050</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Teradata Developer-5</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f4f91dff933f5cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>NiyamIT</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Ashburn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a1802cfcb8371e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>[CoreIgnite] Senior Java Developer (AWS) - Shashank Srivastava</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Luxoft</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0866a4d4cc7dec0c</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
           <t>Data Warehouse/BI Developer</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>ThinkMirum, Inc.</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>Richmond, VA, US USA</t>
         </is>
       </c>
-      <c r="D65" t="n">
+      <c r="D97" t="n">
         <v>10.4</v>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E97" t="inlineStr">
         <is>
           <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=fe28e970e1130d6e</t>
         </is>

--- a/results/job_matches_2026-02-26.xlsx
+++ b/results/job_matches_2026-02-26.xlsx
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AWS Data Platform Engineer</t>
+          <t>Software Engineering III</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Equitable</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,42 +626,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Flume, Zookeeper</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6aa016202f66fe</t>
+          <t>https://www.indeed.com/viewjob?jk=1753914a33e85905</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineering III</t>
+          <t>Senior Advisor II, Data Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Equitable</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Flume, Zookeeper</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1753914a33e85905</t>
+          <t>https://www.indeed.com/viewjob?jk=21bd27b152469170</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Advisor II, Data Architect</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, Kinesis, ECS, RDS, Databricks, BigQuery, Vertex AI, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21bd27b152469170</t>
+          <t>https://www.indeed.com/viewjob?jk=15f2e018b3b0d55e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>SolidLine Media</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e89cb44acf96f0ce</t>
+          <t>https://www.indeed.com/viewjob?jk=8e8185f66fc8c270</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer - Boston</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>American Family Insurance</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9b3e4586db8c7fd</t>
+          <t>https://www.indeed.com/viewjob?jk=54c5e79cbd14d908</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer II (USA)</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=079fa62336e07385</t>
+          <t>https://www.indeed.com/viewjob?jk=e89cb44acf96f0ce</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Technical Product Owner - Data Platform</t>
+          <t>Data Engineer - Boston</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Speridian Technologies</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,69 +836,69 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>EMR, API Gateway, ECS, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=829043b08de7d050</t>
+          <t>https://www.indeed.com/viewjob?jk=b9b3e4586db8c7fd</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-5</t>
+          <t>Software Engineer II (USA)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=656bcb1553978517</t>
+          <t>https://www.indeed.com/viewjob?jk=079fa62336e07385</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Ops Engineer</t>
+          <t>Senior Databricks Developer-5</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,42 +906,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8203af416f8f7f</t>
+          <t>https://www.indeed.com/viewjob?jk=656bcb1553978517</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Machine Learning Ops Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GovWorx</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Spark, PySpark, Scala, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ee6445287271c9d</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8203af416f8f7f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SRS Distribution</t>
+          <t>GovWorx</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Spark, PySpark, Scala, MySQL, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01278285fb17a0ad</t>
+          <t>https://www.indeed.com/viewjob?jk=8ee6445287271c9d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CCaaS Integration Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>SRS Distribution</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, SQS, API Gateway, ECS, Scala, MySQL, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da6da8715ca8e326</t>
+          <t>https://www.indeed.com/viewjob?jk=01278285fb17a0ad</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Advisor II, DevOps Engineering</t>
+          <t>CCaaS Integration Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, ELT, MLOps, MLflow, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, SQS, API Gateway, ECS, Scala, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cc7c35c6dd83d4e</t>
+          <t>https://www.indeed.com/viewjob?jk=da6da8715ca8e326</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr AWS Data Engineer (Contract)</t>
+          <t>Advisor II, DevOps Engineering</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,17 +1081,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, ELT, MLOps, MLflow, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c7808d3f82f3dd3</t>
+          <t>https://www.indeed.com/viewjob?jk=9cc7c35c6dd83d4e</t>
         </is>
       </c>
     </row>
@@ -1518,17 +1518,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Visualization Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Delta Live Tables, BigQuery, Spark, Snowflake, Databricks Lakehouse, ELT, dbt</t>
+          <t>Redshift, S3, RDS, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39ce7a464350b080</t>
+          <t>https://www.indeed.com/viewjob?jk=867f580c7e3bb0e7</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Dir - Technical Operations</t>
+          <t>Senior Software Engineer - API, Services and Backend Systems</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>infinite choice</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Conshohocken, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff4bbc1a531333e0</t>
+          <t>https://www.indeed.com/viewjob?jk=27bb048397f5661f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Visualization Engineer</t>
+          <t>Senior Software Engineer - API, Services and Backend Systems</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>infinite choice</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
+          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=867f580c7e3bb0e7</t>
+          <t>https://www.indeed.com/viewjob?jk=a80d09769e3b9b3d</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27bb048397f5661f</t>
+          <t>https://www.indeed.com/viewjob?jk=d4e3f617e5fa8da5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - API, Services and Backend Systems</t>
+          <t>Google Data Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>infinite choice</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a80d09769e3b9b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=f601a32273482463</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - API, Services and Backend Systems</t>
+          <t>Google Data Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>infinite choice</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e3f617e5fa8da5</t>
+          <t>https://www.indeed.com/viewjob?jk=49947d743d3056f4</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f601a32273482463</t>
+          <t>https://www.indeed.com/viewjob?jk=de9ca192b1459954</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49947d743d3056f4</t>
+          <t>https://www.indeed.com/viewjob?jk=9b716973859a778f</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de9ca192b1459954</t>
+          <t>https://www.indeed.com/viewjob?jk=399ec8bc372b2857</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b716973859a778f</t>
+          <t>https://www.indeed.com/viewjob?jk=80249c993d37b8a1</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Hagerstown, MD, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=399ec8bc372b2857</t>
+          <t>https://www.indeed.com/viewjob?jk=4ee8db07c7d3c455</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80249c993d37b8a1</t>
+          <t>https://www.indeed.com/viewjob?jk=febb3f19f40246d8</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hagerstown, MD, US USA</t>
+          <t>Fairlawn, OH, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ee8db07c7d3c455</t>
+          <t>https://www.indeed.com/viewjob?jk=34111dd75fb61db0</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=febb3f19f40246d8</t>
+          <t>https://www.indeed.com/viewjob?jk=82d12b481045d0c9</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Fairlawn, OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34111dd75fb61db0</t>
+          <t>https://www.indeed.com/viewjob?jk=05f13ce82a3f97f6</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82d12b481045d0c9</t>
+          <t>https://www.indeed.com/viewjob?jk=7e1b0e113ab0a2ae</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05f13ce82a3f97f6</t>
+          <t>https://www.indeed.com/viewjob?jk=bb0219967e4aa5c7</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e1b0e113ab0a2ae</t>
+          <t>https://www.indeed.com/viewjob?jk=2009ecd614434266</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb0219967e4aa5c7</t>
+          <t>https://www.indeed.com/viewjob?jk=f9050b1d95de595b</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2009ecd614434266</t>
+          <t>https://www.indeed.com/viewjob?jk=7a306bdff16c308c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Google Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Delta Live Tables, BigQuery, Spark, Snowflake, Databricks Lakehouse, ELT, dbt</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9050b1d95de595b</t>
+          <t>https://www.indeed.com/viewjob?jk=39ce7a464350b080</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Google Data Architect</t>
+          <t>Dir - Technical Operations</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Conshohocken, PA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a306bdff16c308c</t>
+          <t>https://www.indeed.com/viewjob?jk=ff4bbc1a531333e0</t>
         </is>
       </c>
     </row>
@@ -2463,17 +2463,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Infrastructure Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Culver City, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e6f7f78ae5d82f3</t>
+          <t>https://www.indeed.com/viewjob?jk=5f75551378db568f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3763de2ff690fcf</t>
+          <t>https://www.indeed.com/viewjob?jk=88095bf45f8ffd12</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Al Warren Oil Company, Inc.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3583ff1e8ab8b831</t>
+          <t>https://www.indeed.com/viewjob?jk=7ed97260c28a913a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Infrastructure Architect</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Al Warren Oil Company, Inc.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Culver City, CA, US USA</t>
+          <t>Bensenville, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Terraform</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f75551378db568f</t>
+          <t>https://www.indeed.com/viewjob?jk=ff9397037d4364c4</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88095bf45f8ffd12</t>
+          <t>https://www.indeed.com/viewjob?jk=370f84e82c56d5a4</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Al Warren Oil Company, Inc.</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ed97260c28a913a</t>
+          <t>https://www.indeed.com/viewjob?jk=1e6f7f78ae5d82f3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>AI Analytics and Visualization Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Al Warren Oil Company, Inc.</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bensenville, IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, ETL, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff9397037d4364c4</t>
+          <t>https://www.indeed.com/viewjob?jk=0cb4ad153c4474d3</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Azure Data Bricks Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>RDS, Azure, Databricks, Spark, Kafka, Dimensional Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=370f84e82c56d5a4</t>
+          <t>https://www.indeed.com/viewjob?jk=312c6b6c4770004d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AI Analytics and Visualization Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, ETL, Docker</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cb4ad153c4474d3</t>
+          <t>https://www.indeed.com/viewjob?jk=e3763de2ff690fcf</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Azure Data Bricks Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Kafka, Dimensional Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=312c6b6c4770004d</t>
+          <t>https://www.indeed.com/viewjob?jk=3583ff1e8ab8b831</t>
         </is>
       </c>
     </row>
@@ -3443,17 +3443,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Fullstack Software Engineer (Special Projects Team)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Los Angeles Times</t>
+          <t>Aeroflow Health</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Asheville, NC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Scala, DynamoDB, CI/CD, Docker, Git, Python</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d108b54b3fe154f0</t>
+          <t>https://www.indeed.com/viewjob?jk=61e2c56fc5827763</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr. Data Science Platform Engineer</t>
+          <t>Azure Databricks Architect-2</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Mahwah, NJ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9f1b5af5678ef92</t>
+          <t>https://www.indeed.com/viewjob?jk=6ddf45c77d6d98b2</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+          <t>Architect</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73fae08616e3afd</t>
+          <t>https://www.indeed.com/viewjob?jk=948ed5bfb3c6e050</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cdec8d2c07ce6a8</t>
+          <t>https://www.indeed.com/viewjob?jk=e73fae08616e3afd</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Go To Market AI</t>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>brightwheel</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, SNS, RDS, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92aac63fae4e53fd</t>
+          <t>https://www.indeed.com/viewjob?jk=2cdec8d2c07ce6a8</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Azure Databricks Architect-2</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Los Angeles Times</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Mahwah, NJ, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, ECS, RDS, Scala, DynamoDB, CI/CD, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ddf45c77d6d98b2</t>
+          <t>https://www.indeed.com/viewjob?jk=d108b54b3fe154f0</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>Sr. Data Science Platform Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=948ed5bfb3c6e050</t>
+          <t>https://www.indeed.com/viewjob?jk=f9f1b5af5678ef92</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Teradata Developer-5</t>
+          <t>Sr. Engineer, Go To Market AI</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>brightwheel</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, S3, SNS, RDS, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f4f91dff933f5cc</t>
+          <t>https://www.indeed.com/viewjob?jk=92aac63fae4e53fd</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Teradata Developer-5</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>NiyamIT</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a1802cfcb8371e8</t>
+          <t>https://www.indeed.com/viewjob?jk=6f4f91dff933f5cc</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>[CoreIgnite] Senior Java Developer (AWS) - Shashank Srivastava</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>NiyamIT</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0866a4d4cc7dec0c</t>
+          <t>https://www.indeed.com/viewjob?jk=1a1802cfcb8371e8</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Warehouse/BI Developer</t>
+          <t>[CoreIgnite] Senior Java Developer (AWS) - Shashank Srivastava</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ThinkMirum, Inc.</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe28e970e1130d6e</t>
+          <t>https://www.indeed.com/viewjob?jk=0866a4d4cc7dec0c</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-26.xlsx
+++ b/results/job_matches_2026-02-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior AI / ML Engineer</t>
+          <t>Senior Customer Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Select Minds LLC</t>
+          <t>Harness</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fbed1e14e3c66df</t>
+          <t>https://www.indeed.com/viewjob?jk=927541bc7fc9c876</t>
         </is>
       </c>
     </row>
@@ -1518,17 +1518,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Visualization Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
+          <t>AWS, RDS, Databricks, Delta Live Tables, BigQuery, Spark, Snowflake, Databricks Lakehouse, ELT, dbt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=867f580c7e3bb0e7</t>
+          <t>https://www.indeed.com/viewjob?jk=39ce7a464350b080</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - API, Services and Backend Systems</t>
+          <t>Dir - Technical Operations</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>infinite choice</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Conshohocken, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27bb048397f5661f</t>
+          <t>https://www.indeed.com/viewjob?jk=ff4bbc1a531333e0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - API, Services and Backend Systems</t>
+          <t>Senior Data Visualization Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>infinite choice</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>Redshift, S3, RDS, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a80d09769e3b9b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=867f580c7e3bb0e7</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e3f617e5fa8da5</t>
+          <t>https://www.indeed.com/viewjob?jk=27bb048397f5661f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Google Data Architect</t>
+          <t>Senior Software Engineer - API, Services and Backend Systems</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>infinite choice</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f601a32273482463</t>
+          <t>https://www.indeed.com/viewjob?jk=a80d09769e3b9b3d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Google Data Architect</t>
+          <t>Senior Software Engineer - API, Services and Backend Systems</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>infinite choice</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49947d743d3056f4</t>
+          <t>https://www.indeed.com/viewjob?jk=d4e3f617e5fa8da5</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de9ca192b1459954</t>
+          <t>https://www.indeed.com/viewjob?jk=f601a32273482463</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b716973859a778f</t>
+          <t>https://www.indeed.com/viewjob?jk=49947d743d3056f4</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=399ec8bc372b2857</t>
+          <t>https://www.indeed.com/viewjob?jk=de9ca192b1459954</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80249c993d37b8a1</t>
+          <t>https://www.indeed.com/viewjob?jk=9b716973859a778f</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hagerstown, MD, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ee8db07c7d3c455</t>
+          <t>https://www.indeed.com/viewjob?jk=399ec8bc372b2857</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=febb3f19f40246d8</t>
+          <t>https://www.indeed.com/viewjob?jk=80249c993d37b8a1</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Fairlawn, OH, US USA</t>
+          <t>Hagerstown, MD, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34111dd75fb61db0</t>
+          <t>https://www.indeed.com/viewjob?jk=4ee8db07c7d3c455</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82d12b481045d0c9</t>
+          <t>https://www.indeed.com/viewjob?jk=febb3f19f40246d8</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Fairlawn, OH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05f13ce82a3f97f6</t>
+          <t>https://www.indeed.com/viewjob?jk=34111dd75fb61db0</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e1b0e113ab0a2ae</t>
+          <t>https://www.indeed.com/viewjob?jk=82d12b481045d0c9</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb0219967e4aa5c7</t>
+          <t>https://www.indeed.com/viewjob?jk=05f13ce82a3f97f6</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2009ecd614434266</t>
+          <t>https://www.indeed.com/viewjob?jk=7e1b0e113ab0a2ae</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9050b1d95de595b</t>
+          <t>https://www.indeed.com/viewjob?jk=bb0219967e4aa5c7</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a306bdff16c308c</t>
+          <t>https://www.indeed.com/viewjob?jk=2009ecd614434266</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Google Data Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Delta Live Tables, BigQuery, Spark, Snowflake, Databricks Lakehouse, ELT, dbt</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39ce7a464350b080</t>
+          <t>https://www.indeed.com/viewjob?jk=f9050b1d95de595b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Dir - Technical Operations</t>
+          <t>Google Data Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Conshohocken, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff4bbc1a531333e0</t>
+          <t>https://www.indeed.com/viewjob?jk=7a306bdff16c308c</t>
         </is>
       </c>
     </row>
@@ -2463,17 +2463,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Infrastructure Architect</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Culver City, CA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f75551378db568f</t>
+          <t>https://www.indeed.com/viewjob?jk=1e6f7f78ae5d82f3</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Infrastructure Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Culver City, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88095bf45f8ffd12</t>
+          <t>https://www.indeed.com/viewjob?jk=5f75551378db568f</t>
         </is>
       </c>
     </row>
@@ -2538,12 +2538,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Al Warren Oil Company, Inc.</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ed97260c28a913a</t>
+          <t>https://www.indeed.com/viewjob?jk=88095bf45f8ffd12</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bensenville, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff9397037d4364c4</t>
+          <t>https://www.indeed.com/viewjob?jk=7ed97260c28a913a</t>
         </is>
       </c>
     </row>
@@ -2608,12 +2608,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>Al Warren Oil Company, Inc.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bensenville, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=370f84e82c56d5a4</t>
+          <t>https://www.indeed.com/viewjob?jk=ff9397037d4364c4</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e6f7f78ae5d82f3</t>
+          <t>https://www.indeed.com/viewjob?jk=370f84e82c56d5a4</t>
         </is>
       </c>
     </row>
@@ -2708,17 +2708,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Azure Data Bricks Developer</t>
+          <t>Manufacturing Systems Integration Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Kafka, Dimensional Modeling, ETL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, Power BI, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=312c6b6c4770004d</t>
+          <t>https://www.indeed.com/viewjob?jk=d8532be76b040bdb</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Advisor II, AI Architect</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3763de2ff690fcf</t>
+          <t>https://www.indeed.com/viewjob?jk=1b85a978b0b96b10</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,14 +2806,14 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3583ff1e8ab8b831</t>
+          <t>https://www.indeed.com/viewjob?jk=e3763de2ff690fcf</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Dresher, PA, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a764bcc9a479a693</t>
+          <t>https://www.indeed.com/viewjob?jk=3583ff1e8ab8b831</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Dresher, PA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8b0a891a5da57c1</t>
+          <t>https://www.indeed.com/viewjob?jk=a764bcc9a479a693</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fdde135d701446e</t>
+          <t>https://www.indeed.com/viewjob?jk=d8b0a891a5da57c1</t>
         </is>
       </c>
     </row>
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68e8fc35af3fc28f</t>
+          <t>https://www.indeed.com/viewjob?jk=0fdde135d701446e</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>HealthMark Group</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd869bd281c90f0</t>
+          <t>https://www.indeed.com/viewjob?jk=68e8fc35af3fc28f</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>HealthMark Group</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Jenkins</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c10fe2dd154808d6</t>
+          <t>https://www.indeed.com/viewjob?jk=abd869bd281c90f0</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Manufacturing Systems Integration Engineer</t>
+          <t>Software Engineer - DevOps</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, Power BI, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8532be76b040bdb</t>
+          <t>https://www.indeed.com/viewjob?jk=c10fe2dd154808d6</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr Advisor II, AI Architect</t>
+          <t>Consultant - Cloud SRE Admin</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b85a978b0b96b10</t>
+          <t>https://www.indeed.com/viewjob?jk=f3dc8b002eb283aa</t>
         </is>
       </c>
     </row>
@@ -3443,17 +3443,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Fullstack Software Engineer (Special Projects Team)</t>
+          <t>Senior Customer Architect - AppSec (Enterprise and Federal)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Aeroflow Health</t>
+          <t>Harness</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Asheville, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, DynamoDB, CI/CD</t>
+          <t>AWS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61e2c56fc5827763</t>
+          <t>https://www.indeed.com/viewjob?jk=75750b39b6d9f7e1</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Azure Databricks Architect-2</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Los Angeles Times</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Mahwah, NJ, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, ECS, RDS, Scala, DynamoDB, CI/CD, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ddf45c77d6d98b2</t>
+          <t>https://www.indeed.com/viewjob?jk=d108b54b3fe154f0</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>Sr. Data Science Platform Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=948ed5bfb3c6e050</t>
+          <t>https://www.indeed.com/viewjob?jk=f9f1b5af5678ef92</t>
         </is>
       </c>
     </row>
@@ -3618,17 +3618,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Engineer, Go To Market AI</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Los Angeles Times</t>
+          <t>brightwheel</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Scala, DynamoDB, CI/CD, Docker, Git, Python</t>
+          <t>AWS, S3, SNS, RDS, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d108b54b3fe154f0</t>
+          <t>https://www.indeed.com/viewjob?jk=92aac63fae4e53fd</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sr. Data Science Platform Engineer</t>
+          <t>Fullstack Software Engineer (Special Projects Team)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Aeroflow Health</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Asheville, NC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9f1b5af5678ef92</t>
+          <t>https://www.indeed.com/viewjob?jk=61e2c56fc5827763</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Go To Market AI</t>
+          <t>Azure Databricks Architect-2</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>brightwheel</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Mahwah, NJ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, S3, SNS, RDS, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92aac63fae4e53fd</t>
+          <t>https://www.indeed.com/viewjob?jk=6ddf45c77d6d98b2</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Teradata Developer-5</t>
+          <t>Architect</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f4f91dff933f5cc</t>
+          <t>https://www.indeed.com/viewjob?jk=948ed5bfb3c6e050</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Teradata Developer-5</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>NiyamIT</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a1802cfcb8371e8</t>
+          <t>https://www.indeed.com/viewjob?jk=6f4f91dff933f5cc</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>[CoreIgnite] Senior Java Developer (AWS) - Shashank Srivastava</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>NiyamIT</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,15 +3811,50 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a1802cfcb8371e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>[CoreIgnite] Senior Java Developer (AWS) - Shashank Srivastava</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Luxoft</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
           <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=0866a4d4cc7dec0c</t>
         </is>

--- a/results/job_matches_2026-02-26.xlsx
+++ b/results/job_matches_2026-02-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer - Boston</t>
+          <t>Sr. Data Engineer (Only W2)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>ACR Technology Inc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>Azure, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9b3e4586db8c7fd</t>
+          <t>https://www.indeed.com/viewjob?jk=8be431de16824436</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer II (USA)</t>
+          <t>Data Engineer - Boston</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,69 +871,69 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=079fa62336e07385</t>
+          <t>https://www.indeed.com/viewjob?jk=b9b3e4586db8c7fd</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-5</t>
+          <t>Software Engineer II (USA)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=656bcb1553978517</t>
+          <t>https://www.indeed.com/viewjob?jk=079fa62336e07385</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Ops Engineer</t>
+          <t>Senior Databricks Developer-5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,42 +941,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8203af416f8f7f</t>
+          <t>https://www.indeed.com/viewjob?jk=656bcb1553978517</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Machine Learning Ops Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GovWorx</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Spark, PySpark, Scala, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ee6445287271c9d</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8203af416f8f7f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SRS Distribution</t>
+          <t>GovWorx</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Spark, PySpark, Scala, MySQL, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01278285fb17a0ad</t>
+          <t>https://www.indeed.com/viewjob?jk=8ee6445287271c9d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CCaaS Integration Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>SRS Distribution</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, SQS, API Gateway, ECS, Scala, MySQL, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da6da8715ca8e326</t>
+          <t>https://www.indeed.com/viewjob?jk=01278285fb17a0ad</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Advisor II, DevOps Engineering</t>
+          <t>CCaaS Integration Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, ELT, MLOps, MLflow, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, SQS, API Gateway, ECS, Scala, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cc7c35c6dd83d4e</t>
+          <t>https://www.indeed.com/viewjob?jk=da6da8715ca8e326</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Remote)</t>
+          <t>Advisor II, DevOps Engineering</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Inspira Financial</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,52 +1116,52 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, ELT, MLOps, MLflow, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03f6284daa41bb63</t>
+          <t>https://www.indeed.com/viewjob?jk=9cc7c35c6dd83d4e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Incident Response Engineer (Remote)</t>
+          <t>Sr. Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Frontdoor</t>
+          <t>Inspira Financial</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Kafka, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c333b0560d852231</t>
+          <t>https://www.indeed.com/viewjob?jk=03f6284daa41bb63</t>
         </is>
       </c>
     </row>
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0fa96abbbb8aac8</t>
+          <t>https://www.indeed.com/viewjob?jk=c333b0560d852231</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Incident Response Engineer (Remote)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Frontdoor</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, PostgreSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=693f3e0a054607b0</t>
+          <t>https://www.indeed.com/viewjob?jk=d0fa96abbbb8aac8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Solution Engineer I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Associated Wholesale Grocers</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, PostgreSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5985bee213bf40</t>
+          <t>https://www.indeed.com/viewjob?jk=693f3e0a054607b0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Customer Engineer</t>
+          <t>Solution Engineer I</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Harness</t>
+          <t>Associated Wholesale Grocers</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,19 +1301,19 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=927541bc7fc9c876</t>
+          <t>https://www.indeed.com/viewjob?jk=5e5985bee213bf40</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Databricks Managing Consultant Engineer - Digital Velocity</t>
+          <t>Senior Customer Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>Harness</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, Scala, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91700d9dd67b6cb5</t>
+          <t>https://www.indeed.com/viewjob?jk=927541bc7fc9c876</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend/Cloud Services</t>
+          <t>Databricks Managing Consultant Engineer - Digital Velocity</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Hunter Industries</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,69 +1361,69 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, DynamoDB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, Scala, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b582244014f6614c</t>
+          <t>https://www.indeed.com/viewjob?jk=91700d9dd67b6cb5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - Backend/Cloud Services</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Gradient AI</t>
+          <t>Hunter Industries</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, DynamoDB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08f4a08591f4e565</t>
+          <t>https://www.indeed.com/viewjob?jk=b582244014f6614c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ripple</t>
+          <t>Gradient AI</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Athena, S3, API Gateway, ECS, Databricks, Spark, Scala</t>
+          <t>AWS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6988d9d372dc66d3</t>
+          <t>https://www.indeed.com/viewjob?jk=08f4a08591f4e565</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>Ripple</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, Kinesis, Athena, S3, API Gateway, ECS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d0a69e61901c434</t>
+          <t>https://www.indeed.com/viewjob?jk=6988d9d372dc66d3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30154588ed7f957f</t>
+          <t>https://www.indeed.com/viewjob?jk=7d0a69e61901c434</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Delta Live Tables, BigQuery, Spark, Snowflake, Databricks Lakehouse, ELT, dbt</t>
+          <t>AWS, S3, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39ce7a464350b080</t>
+          <t>https://www.indeed.com/viewjob?jk=30154588ed7f957f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Dir - Technical Operations</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Conshohocken, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, Delta Live Tables, BigQuery, Spark, Snowflake, Databricks Lakehouse, ELT, dbt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff4bbc1a531333e0</t>
+          <t>https://www.indeed.com/viewjob?jk=39ce7a464350b080</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Visualization Engineer</t>
+          <t>Dir - Technical Operations</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Conshohocken, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=867f580c7e3bb0e7</t>
+          <t>https://www.indeed.com/viewjob?jk=ff4bbc1a531333e0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - API, Services and Backend Systems</t>
+          <t>Senior Data Visualization Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>infinite choice</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>Redshift, S3, RDS, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27bb048397f5661f</t>
+          <t>https://www.indeed.com/viewjob?jk=867f580c7e3bb0e7</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a80d09769e3b9b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=27bb048397f5661f</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e3f617e5fa8da5</t>
+          <t>https://www.indeed.com/viewjob?jk=a80d09769e3b9b3d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Google Data Architect</t>
+          <t>Senior Software Engineer - API, Services and Backend Systems</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>infinite choice</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f601a32273482463</t>
+          <t>https://www.indeed.com/viewjob?jk=d4e3f617e5fa8da5</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49947d743d3056f4</t>
+          <t>https://www.indeed.com/viewjob?jk=f601a32273482463</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de9ca192b1459954</t>
+          <t>https://www.indeed.com/viewjob?jk=49947d743d3056f4</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b716973859a778f</t>
+          <t>https://www.indeed.com/viewjob?jk=de9ca192b1459954</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=399ec8bc372b2857</t>
+          <t>https://www.indeed.com/viewjob?jk=9b716973859a778f</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80249c993d37b8a1</t>
+          <t>https://www.indeed.com/viewjob?jk=399ec8bc372b2857</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hagerstown, MD, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ee8db07c7d3c455</t>
+          <t>https://www.indeed.com/viewjob?jk=80249c993d37b8a1</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Hagerstown, MD, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=febb3f19f40246d8</t>
+          <t>https://www.indeed.com/viewjob?jk=4ee8db07c7d3c455</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Fairlawn, OH, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34111dd75fb61db0</t>
+          <t>https://www.indeed.com/viewjob?jk=febb3f19f40246d8</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Fairlawn, OH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82d12b481045d0c9</t>
+          <t>https://www.indeed.com/viewjob?jk=34111dd75fb61db0</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05f13ce82a3f97f6</t>
+          <t>https://www.indeed.com/viewjob?jk=82d12b481045d0c9</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e1b0e113ab0a2ae</t>
+          <t>https://www.indeed.com/viewjob?jk=05f13ce82a3f97f6</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb0219967e4aa5c7</t>
+          <t>https://www.indeed.com/viewjob?jk=7e1b0e113ab0a2ae</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2009ecd614434266</t>
+          <t>https://www.indeed.com/viewjob?jk=bb0219967e4aa5c7</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9050b1d95de595b</t>
+          <t>https://www.indeed.com/viewjob?jk=2009ecd614434266</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a306bdff16c308c</t>
+          <t>https://www.indeed.com/viewjob?jk=f9050b1d95de595b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
+          <t>Google Data Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Eurest</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4699f552f08a017</t>
+          <t>https://www.indeed.com/viewjob?jk=7a306bdff16c308c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Gradient</t>
+          <t>Eurest</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,42 +2341,42 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Kafka, PostgreSQL, MongoDB, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b485146fc9fd8af2</t>
+          <t>https://www.indeed.com/viewjob?jk=a4699f552f08a017</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer II 4P/554</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>Gradient</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Oracle, SQL Server, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Kafka, PostgreSQL, MongoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d963e021c819ac</t>
+          <t>https://www.indeed.com/viewjob?jk=b485146fc9fd8af2</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, CRM</t>
+          <t>Data Engineer II 4P/554</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
+          <t>Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Oracle, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b266df7f25223b6</t>
+          <t>https://www.indeed.com/viewjob?jk=43d963e021c819ac</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
+          <t>Senior Data Engineer, CRM</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Compass Group USA</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Hadoop, Spark, Snowflake, Oracle, PostgreSQL, MySQL</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65b5898fc3882a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=7b266df7f25223b6</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Compass Group USA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>AWS, Redshift, RDS, BigQuery, Hadoop, Spark, Snowflake, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e6f7f78ae5d82f3</t>
+          <t>https://www.indeed.com/viewjob?jk=65b5898fc3882a0c</t>
         </is>
       </c>
     </row>
@@ -2778,17 +2778,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3763de2ff690fcf</t>
+          <t>https://www.indeed.com/viewjob?jk=1e6f7f78ae5d82f3</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,14 +2841,14 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3583ff1e8ab8b831</t>
+          <t>https://www.indeed.com/viewjob?jk=e3763de2ff690fcf</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Dresher, PA, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a764bcc9a479a693</t>
+          <t>https://www.indeed.com/viewjob?jk=3583ff1e8ab8b831</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Dresher, PA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8b0a891a5da57c1</t>
+          <t>https://www.indeed.com/viewjob?jk=a764bcc9a479a693</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fdde135d701446e</t>
+          <t>https://www.indeed.com/viewjob?jk=d8b0a891a5da57c1</t>
         </is>
       </c>
     </row>
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68e8fc35af3fc28f</t>
+          <t>https://www.indeed.com/viewjob?jk=0fdde135d701446e</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>HealthMark Group</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd869bd281c90f0</t>
+          <t>https://www.indeed.com/viewjob?jk=68e8fc35af3fc28f</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>HealthMark Group</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Jenkins</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c10fe2dd154808d6</t>
+          <t>https://www.indeed.com/viewjob?jk=abd869bd281c90f0</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Consultant - Cloud SRE Admin</t>
+          <t>Software Engineer - DevOps</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3dc8b002eb283aa</t>
+          <t>https://www.indeed.com/viewjob?jk=c10fe2dd154808d6</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer - Control Plane</t>
+          <t>Consultant - Cloud SRE Admin</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>clickhouse</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, IAM, RDS, Scala, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d85ac5dbf541cd3b</t>
+          <t>https://www.indeed.com/viewjob?jk=f3dc8b002eb283aa</t>
         </is>
       </c>
     </row>
@@ -3857,6 +3857,41 @@
       <c r="G98" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=0866a4d4cc7dec0c</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Data Warehouse/BI Developer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>ThinkMirum, Inc.</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe28e970e1130d6e</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-26.xlsx
+++ b/results/job_matches_2026-02-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1063,17 +1063,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CCaaS Integration Engineer</t>
+          <t>Distinguished Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, SQS, API Gateway, ECS, Scala, MySQL, MongoDB</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Cassandra, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da6da8715ca8e326</t>
+          <t>https://www.indeed.com/viewjob?jk=ab3a4b9f2c783845</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Advisor II, DevOps Engineering</t>
+          <t>CCaaS Integration Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, ELT, MLOps, MLflow, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, SQS, API Gateway, ECS, Scala, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cc7c35c6dd83d4e</t>
+          <t>https://www.indeed.com/viewjob?jk=da6da8715ca8e326</t>
         </is>
       </c>
     </row>
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Databricks Managing Consultant Engineer - Digital Velocity</t>
+          <t>Software Engineer - Backend/Cloud Services</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>Hunter Industries</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,69 +1361,69 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, Scala, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, DynamoDB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91700d9dd67b6cb5</t>
+          <t>https://www.indeed.com/viewjob?jk=b582244014f6614c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend/Cloud Services</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Hunter Industries</t>
+          <t>Gradient AI</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, DynamoDB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b582244014f6614c</t>
+          <t>https://www.indeed.com/viewjob?jk=08f4a08591f4e565</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Gradient AI</t>
+          <t>Ripple</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Kinesis, Athena, S3, API Gateway, ECS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08f4a08591f4e565</t>
+          <t>https://www.indeed.com/viewjob?jk=6988d9d372dc66d3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ripple</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Athena, S3, API Gateway, ECS, Databricks, Spark, Scala</t>
+          <t>AWS, S3, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6988d9d372dc66d3</t>
+          <t>https://www.indeed.com/viewjob?jk=30154588ed7f957f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d0a69e61901c434</t>
+          <t>https://www.indeed.com/viewjob?jk=4a077c257a4cf0b5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer- Policy Configuration</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,17 +1536,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30154588ed7f957f</t>
+          <t>https://www.indeed.com/viewjob?jk=1acf3efd34722f19</t>
         </is>
       </c>
     </row>
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Google Data Architect</t>
+          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Eurest</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f601a32273482463</t>
+          <t>https://www.indeed.com/viewjob?jk=a4699f552f08a017</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49947d743d3056f4</t>
+          <t>https://www.indeed.com/viewjob?jk=f601a32273482463</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de9ca192b1459954</t>
+          <t>https://www.indeed.com/viewjob?jk=49947d743d3056f4</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b716973859a778f</t>
+          <t>https://www.indeed.com/viewjob?jk=de9ca192b1459954</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=399ec8bc372b2857</t>
+          <t>https://www.indeed.com/viewjob?jk=9b716973859a778f</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80249c993d37b8a1</t>
+          <t>https://www.indeed.com/viewjob?jk=399ec8bc372b2857</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hagerstown, MD, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ee8db07c7d3c455</t>
+          <t>https://www.indeed.com/viewjob?jk=80249c993d37b8a1</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Hagerstown, MD, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=febb3f19f40246d8</t>
+          <t>https://www.indeed.com/viewjob?jk=4ee8db07c7d3c455</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Fairlawn, OH, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34111dd75fb61db0</t>
+          <t>https://www.indeed.com/viewjob?jk=febb3f19f40246d8</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Fairlawn, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82d12b481045d0c9</t>
+          <t>https://www.indeed.com/viewjob?jk=34111dd75fb61db0</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05f13ce82a3f97f6</t>
+          <t>https://www.indeed.com/viewjob?jk=82d12b481045d0c9</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e1b0e113ab0a2ae</t>
+          <t>https://www.indeed.com/viewjob?jk=05f13ce82a3f97f6</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb0219967e4aa5c7</t>
+          <t>https://www.indeed.com/viewjob?jk=7e1b0e113ab0a2ae</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2009ecd614434266</t>
+          <t>https://www.indeed.com/viewjob?jk=bb0219967e4aa5c7</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9050b1d95de595b</t>
+          <t>https://www.indeed.com/viewjob?jk=2009ecd614434266</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a306bdff16c308c</t>
+          <t>https://www.indeed.com/viewjob?jk=f9050b1d95de595b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
+          <t>Google Data Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Eurest</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,42 +2341,42 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4699f552f08a017</t>
+          <t>https://www.indeed.com/viewjob?jk=7a306bdff16c308c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Data Engineer II 4P/554</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Gradient</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Kafka, PostgreSQL, MongoDB, Data Modeling, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Oracle, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b485146fc9fd8af2</t>
+          <t>https://www.indeed.com/viewjob?jk=43d963e021c819ac</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer II 4P/554</t>
+          <t>Senior Data Engineer, CRM</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Oracle, SQL Server, NoSQL, Data Modeling</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d963e021c819ac</t>
+          <t>https://www.indeed.com/viewjob?jk=7b266df7f25223b6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, CRM</t>
+          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Compass Group USA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
+          <t>AWS, Redshift, RDS, BigQuery, Hadoop, Spark, Snowflake, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b266df7f25223b6</t>
+          <t>https://www.indeed.com/viewjob?jk=65b5898fc3882a0c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
+          <t>Infrastructure Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Compass Group USA</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Culver City, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Hadoop, Spark, Snowflake, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65b5898fc3882a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=5f75551378db568f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Infrastructure Architect</t>
+          <t>Manufacturing Systems Integration Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Culver City, CA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, Power BI, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,19 +2526,19 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f75551378db568f</t>
+          <t>https://www.indeed.com/viewjob?jk=d8532be76b040bdb</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Sr Advisor II, AI Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88095bf45f8ffd12</t>
+          <t>https://www.indeed.com/viewjob?jk=1b85a978b0b96b10</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Al Warren Oil Company, Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ed97260c28a913a</t>
+          <t>https://www.indeed.com/viewjob?jk=b11bc9d20fc1e2e2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Al Warren Oil Company, Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bensenville, IL, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff9397037d4364c4</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a6f623279ee6d4</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=370f84e82c56d5a4</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3cccca60e879db</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AI Analytics and Visualization Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, ETL, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cb4ad153c4474d3</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f821dc8a5f6559</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Manufacturing Systems Integration Engineer</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, Power BI, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8532be76b040bdb</t>
+          <t>https://www.indeed.com/viewjob?jk=1e6f7f78ae5d82f3</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr Advisor II, AI Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b85a978b0b96b10</t>
+          <t>https://www.indeed.com/viewjob?jk=e3763de2ff690fcf</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,14 +2806,14 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e6f7f78ae5d82f3</t>
+          <t>https://www.indeed.com/viewjob?jk=3583ff1e8ab8b831</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dresher, PA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,14 +2841,14 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3763de2ff690fcf</t>
+          <t>https://www.indeed.com/viewjob?jk=a764bcc9a479a693</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3583ff1e8ab8b831</t>
+          <t>https://www.indeed.com/viewjob?jk=d8b0a891a5da57c1</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dresher, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a764bcc9a479a693</t>
+          <t>https://www.indeed.com/viewjob?jk=0fdde135d701446e</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8b0a891a5da57c1</t>
+          <t>https://www.indeed.com/viewjob?jk=68e8fc35af3fc28f</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>HealthMark Group</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fdde135d701446e</t>
+          <t>https://www.indeed.com/viewjob?jk=abd869bd281c90f0</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer - DevOps</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68e8fc35af3fc28f</t>
+          <t>https://www.indeed.com/viewjob?jk=c10fe2dd154808d6</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Consultant - Cloud SRE Admin</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>HealthMark Group</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd869bd281c90f0</t>
+          <t>https://www.indeed.com/viewjob?jk=f3dc8b002eb283aa</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps</t>
+          <t>MLOps Platform Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Jenkins</t>
+          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c10fe2dd154808d6</t>
+          <t>https://www.indeed.com/viewjob?jk=4687b9b235a9a6ce</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Consultant - Cloud SRE Admin</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>Trepp</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3dc8b002eb283aa</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd8df1b20c5849b</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MLOps Platform Engineer</t>
+          <t>Senior Data Engineer – Upstream Oil &amp; Gas</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Crescent Energy</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4687b9b235a9a6ce</t>
+          <t>https://www.indeed.com/viewjob?jk=619ee2b50d37daac</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>ML Support Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Trepp</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd8df1b20c5849b</t>
+          <t>https://www.indeed.com/viewjob?jk=a4281d96efe6a7c5</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Upstream Oil &amp; Gas</t>
+          <t>Backend Software Engineer (Mid-Level / Senior)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Crescent Energy</t>
+          <t>Airvet</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619ee2b50d37daac</t>
+          <t>https://www.indeed.com/viewjob?jk=87ce4c6973528ac7</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Qcells</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79f22cc4bdf57e2f</t>
+          <t>https://www.indeed.com/viewjob?jk=62210abb12166a07</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Qcells</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47823188919dd6f3</t>
+          <t>https://www.indeed.com/viewjob?jk=26a71508d797185b</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ML Support Engineer</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4281d96efe6a7c5</t>
+          <t>https://www.indeed.com/viewjob?jk=dbeb792ea58b7a87</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (Mid-Level / Senior)</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Airvet</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87ce4c6973528ac7</t>
+          <t>https://www.indeed.com/viewjob?jk=f22565dd904e0808</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62210abb12166a07</t>
+          <t>https://www.indeed.com/viewjob?jk=f8fcbfbc5352b0bf</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26a71508d797185b</t>
+          <t>https://www.indeed.com/viewjob?jk=d1da94812ec374b4</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Customer Architect - AppSec (Enterprise and Federal)</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Harness</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,17 +3461,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75750b39b6d9f7e1</t>
+          <t>https://www.indeed.com/viewjob?jk=ee5cdada52faf29e</t>
         </is>
       </c>
     </row>
@@ -3513,17 +3513,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr. Data Science Platform Engineer</t>
+          <t>Fullstack Software Engineer (Special Projects Team)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Aeroflow Health</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Asheville, NC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9f1b5af5678ef92</t>
+          <t>https://www.indeed.com/viewjob?jk=61e2c56fc5827763</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+          <t>Architect</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73fae08616e3afd</t>
+          <t>https://www.indeed.com/viewjob?jk=948ed5bfb3c6e050</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cdec8d2c07ce6a8</t>
+          <t>https://www.indeed.com/viewjob?jk=e73fae08616e3afd</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Go To Market AI</t>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>brightwheel</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, S3, SNS, RDS, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92aac63fae4e53fd</t>
+          <t>https://www.indeed.com/viewjob?jk=2cdec8d2c07ce6a8</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Fullstack Software Engineer (Special Projects Team)</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Aeroflow Health</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Asheville, NC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61e2c56fc5827763</t>
+          <t>https://www.indeed.com/viewjob?jk=503269b060f28151</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Azure Databricks Architect-2</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Mahwah, NJ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ddf45c77d6d98b2</t>
+          <t>https://www.indeed.com/viewjob?jk=fd899ffea8f1b74c</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=948ed5bfb3c6e050</t>
+          <t>https://www.indeed.com/viewjob?jk=5676e61db2aa81f3</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Teradata Developer-5</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f4f91dff933f5cc</t>
+          <t>https://www.indeed.com/viewjob?jk=de6aa6e4975245c5</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Teradata Developer-5</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>NiyamIT</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a1802cfcb8371e8</t>
+          <t>https://www.indeed.com/viewjob?jk=6f4f91dff933f5cc</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>[CoreIgnite] Senior Java Developer (AWS) - Shashank Srivastava</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>NiyamIT</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0866a4d4cc7dec0c</t>
+          <t>https://www.indeed.com/viewjob?jk=1a1802cfcb8371e8</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Warehouse/BI Developer</t>
+          <t>[CoreIgnite] Senior Java Developer (AWS) - Shashank Srivastava</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ThinkMirum, Inc.</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,17 +3881,87 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
+          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0866a4d4cc7dec0c</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Data Warehouse/BI Developer</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>ThinkMirum, Inc.</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
           <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=fe28e970e1130d6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Sr. Engineer, Go To Market AI</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>brightwheel</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, S3, SNS, RDS, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=92aac63fae4e53fd</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-26.xlsx
+++ b/results/job_matches_2026-02-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,52 +538,52 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>DevOps &amp; Backend Engineer — Mid/Senior</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Stifel</t>
+          <t>Open Insurance</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Spark</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1cae88bbe2455c</t>
+          <t>https://www.indeed.com/viewjob?jk=6691fd82745fd2c9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Engineering III</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Stifel</t>
+          <t>Equitable</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,42 +591,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Spark</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Flume, Zookeeper</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3346a397aa58e367</t>
+          <t>https://www.indeed.com/viewjob?jk=1753914a33e85905</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineering III</t>
+          <t>Senior Advisor II, Data Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Equitable</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Flume, Zookeeper</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1753914a33e85905</t>
+          <t>https://www.indeed.com/viewjob?jk=21bd27b152469170</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Advisor II, Data Architect</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, Kinesis, ECS, RDS, Databricks, BigQuery, Vertex AI, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,59 +671,59 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21bd27b152469170</t>
+          <t>https://www.indeed.com/viewjob?jk=15f2e018b3b0d55e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>SolidLine Media</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, ECS, RDS, Databricks, BigQuery, Vertex AI, Spark, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15f2e018b3b0d55e</t>
+          <t>https://www.indeed.com/viewjob?jk=8e8185f66fc8c270</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SolidLine Media</t>
+          <t>American Family Insurance</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e8185f66fc8c270</t>
+          <t>https://www.indeed.com/viewjob?jk=54c5e79cbd14d908</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>American Family Insurance</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c5e79cbd14d908</t>
+          <t>https://www.indeed.com/viewjob?jk=e89cb44acf96f0ce</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Data Engineer - Boston</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e89cb44acf96f0ce</t>
+          <t>https://www.indeed.com/viewjob?jk=b9b3e4586db8c7fd</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Only W2)</t>
+          <t>Software Engineer II (USA)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ACR Technology Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Azure, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, SQL Server, Dimensional Modeling</t>
+          <t>AWS, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8be431de16824436</t>
+          <t>https://www.indeed.com/viewjob?jk=079fa62336e07385</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer - Boston</t>
+          <t>Senior Databricks Developer-5</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9b3e4586db8c7fd</t>
+          <t>https://www.indeed.com/viewjob?jk=656bcb1553978517</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer II (USA)</t>
+          <t>Senior Machine Learning Ops Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=079fa62336e07385</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8203af416f8f7f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-5</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>SRS Distribution</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=656bcb1553978517</t>
+          <t>https://www.indeed.com/viewjob?jk=e9fcb451d7086751</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Ops Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>GovWorx</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Spark, PySpark, Scala, MySQL, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8203af416f8f7f</t>
+          <t>https://www.indeed.com/viewjob?jk=8ee6445287271c9d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Distinguished Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GovWorx</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Spark, PySpark, Scala, MySQL, ETL</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Cassandra, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ee6445287271c9d</t>
+          <t>https://www.indeed.com/viewjob?jk=ab3a4b9f2c783845</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Application Developer III, Platform Engineering</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SRS Distribution</t>
+          <t>Herbalife</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>Torrance, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01278285fb17a0ad</t>
+          <t>https://www.indeed.com/viewjob?jk=116acc2ab05b269d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Distinguished Engineer</t>
+          <t>Sr. Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Inspira Financial</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Cassandra, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab3a4b9f2c783845</t>
+          <t>https://www.indeed.com/viewjob?jk=03f6284daa41bb63</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CCaaS Integration Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Ramsey Solutions</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, SQS, API Gateway, ECS, Scala, MySQL, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da6da8715ca8e326</t>
+          <t>https://www.indeed.com/viewjob?jk=ba46b1aa50f7279f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Inspira Financial</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, PostgreSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03f6284daa41bb63</t>
+          <t>https://www.indeed.com/viewjob?jk=693f3e0a054607b0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Incident Response Engineer (Remote)</t>
+          <t>Solution Engineer I</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Frontdoor</t>
+          <t>Associated Wholesale Grocers</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Kafka, MongoDB</t>
+          <t>AWS, Redshift, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c333b0560d852231</t>
+          <t>https://www.indeed.com/viewjob?jk=5e5985bee213bf40</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Incident Response Engineer (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Frontdoor</t>
+          <t>Gradient AI</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Kafka, MongoDB</t>
+          <t>AWS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0fa96abbbb8aac8</t>
+          <t>https://www.indeed.com/viewjob?jk=08f4a08591f4e565</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Ripple</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, PostgreSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Kinesis, Athena, S3, API Gateway, ECS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,89 +1266,89 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=693f3e0a054607b0</t>
+          <t>https://www.indeed.com/viewjob?jk=6988d9d372dc66d3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Solution Engineer I</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Associated Wholesale Grocers</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, S3, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5985bee213bf40</t>
+          <t>https://www.indeed.com/viewjob?jk=30154588ed7f957f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Customer Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Harness</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, ETL</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=927541bc7fc9c876</t>
+          <t>https://www.indeed.com/viewjob?jk=4a077c257a4cf0b5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend/Cloud Services</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Hunter Industries</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1357,38 +1357,38 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, DynamoDB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Databricks, Delta Live Tables, BigQuery, Spark, Snowflake, Databricks Lakehouse, ELT, dbt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b582244014f6614c</t>
+          <t>https://www.indeed.com/viewjob?jk=39ce7a464350b080</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Gradient AI</t>
+          <t>Eurest</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08f4a08591f4e565</t>
+          <t>https://www.indeed.com/viewjob?jk=a4699f552f08a017</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Data Visualization Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ripple</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Athena, S3, API Gateway, ECS, Databricks, Spark, Scala</t>
+          <t>Redshift, S3, RDS, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6988d9d372dc66d3</t>
+          <t>https://www.indeed.com/viewjob?jk=867f580c7e3bb0e7</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer- Policy Configuration</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,112 +1466,112 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30154588ed7f957f</t>
+          <t>https://www.indeed.com/viewjob?jk=1acf3efd34722f19</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Engineer II 4P/554</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Oracle, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a077c257a4cf0b5</t>
+          <t>https://www.indeed.com/viewjob?jk=43d963e021c819ac</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Policy Configuration</t>
+          <t>Senior Data Engineer, CRM</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1acf3efd34722f19</t>
+          <t>https://www.indeed.com/viewjob?jk=7b266df7f25223b6</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Compass Group USA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Delta Live Tables, BigQuery, Spark, Snowflake, Databricks Lakehouse, ELT, dbt</t>
+          <t>AWS, Redshift, RDS, BigQuery, Hadoop, Spark, Snowflake, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39ce7a464350b080</t>
+          <t>https://www.indeed.com/viewjob?jk=65b5898fc3882a0c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Dir - Technical Operations</t>
+          <t>Manufacturing Systems Integration Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Conshohocken, PA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, Power BI, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff4bbc1a531333e0</t>
+          <t>https://www.indeed.com/viewjob?jk=d8532be76b040bdb</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Visualization Engineer</t>
+          <t>Sr Advisor II, AI Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,172 +1651,172 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=867f580c7e3bb0e7</t>
+          <t>https://www.indeed.com/viewjob?jk=1b85a978b0b96b10</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - API, Services and Backend Systems</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>infinite choice</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27bb048397f5661f</t>
+          <t>https://www.indeed.com/viewjob?jk=b11bc9d20fc1e2e2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - API, Services and Backend Systems</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>infinite choice</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a80d09769e3b9b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a6f623279ee6d4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - API, Services and Backend Systems</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>infinite choice</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e3f617e5fa8da5</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3cccca60e879db</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Eurest</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4699f552f08a017</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f821dc8a5f6559</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Google Data Architect</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f601a32273482463</t>
+          <t>https://www.indeed.com/viewjob?jk=1e6f7f78ae5d82f3</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Google Data Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49947d743d3056f4</t>
+          <t>https://www.indeed.com/viewjob?jk=e3763de2ff690fcf</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Google Data Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de9ca192b1459954</t>
+          <t>https://www.indeed.com/viewjob?jk=3583ff1e8ab8b831</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Google Data Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Dresher, PA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b716973859a778f</t>
+          <t>https://www.indeed.com/viewjob?jk=a764bcc9a479a693</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Google Data Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=399ec8bc372b2857</t>
+          <t>https://www.indeed.com/viewjob?jk=d8b0a891a5da57c1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Google Data Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80249c993d37b8a1</t>
+          <t>https://www.indeed.com/viewjob?jk=0fdde135d701446e</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Google Data Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hagerstown, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ee8db07c7d3c455</t>
+          <t>https://www.indeed.com/viewjob?jk=68e8fc35af3fc28f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Google Data Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>HealthMark Group</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=febb3f19f40246d8</t>
+          <t>https://www.indeed.com/viewjob?jk=abd869bd281c90f0</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Google Data Architect</t>
+          <t>Software Engineer - DevOps</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Fairlawn, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34111dd75fb61db0</t>
+          <t>https://www.indeed.com/viewjob?jk=c10fe2dd154808d6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Google Data Architect</t>
+          <t>Consultant - Cloud SRE Admin</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82d12b481045d0c9</t>
+          <t>https://www.indeed.com/viewjob?jk=f3dc8b002eb283aa</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Google Data Architect</t>
+          <t>MLOps Platform Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05f13ce82a3f97f6</t>
+          <t>https://www.indeed.com/viewjob?jk=4687b9b235a9a6ce</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Google Data Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Trepp</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e1b0e113ab0a2ae</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd8df1b20c5849b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Google Data Architect</t>
+          <t>Senior Data Engineer – Upstream Oil &amp; Gas</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Crescent Energy</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb0219967e4aa5c7</t>
+          <t>https://www.indeed.com/viewjob?jk=619ee2b50d37daac</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Google Data Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Spark, Scala, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2009ecd614434266</t>
+          <t>https://www.indeed.com/viewjob?jk=e7929c83226ae75b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Google Data Architect</t>
+          <t>ML Support Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,207 +2316,207 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9050b1d95de595b</t>
+          <t>https://www.indeed.com/viewjob?jk=a4281d96efe6a7c5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Google Data Architect</t>
+          <t>Backend Software Engineer (Mid-Level / Senior)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Airvet</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a306bdff16c308c</t>
+          <t>https://www.indeed.com/viewjob?jk=87ce4c6973528ac7</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer II 4P/554</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Oracle, SQL Server, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d963e021c819ac</t>
+          <t>https://www.indeed.com/viewjob?jk=62210abb12166a07</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, CRM</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b266df7f25223b6</t>
+          <t>https://www.indeed.com/viewjob?jk=26a71508d797185b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
+          <t>Enterprise AI Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Compass Group USA</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Hadoop, Spark, Snowflake, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65b5898fc3882a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=291c96af0e7cea02</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Infrastructure Architect</t>
+          <t>Teradata Developer-5</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Culver City, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Terraform</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f75551378db568f</t>
+          <t>https://www.indeed.com/viewjob?jk=6f4f91dff933f5cc</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Manufacturing Systems Integration Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>NiyamIT</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, Power BI, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8532be76b040bdb</t>
+          <t>https://www.indeed.com/viewjob?jk=1a1802cfcb8371e8</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr Advisor II, AI Architect</t>
+          <t>[CoreIgnite] Senior Java Developer (AWS) - Shashank Srivastava</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,67 +2561,67 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b85a978b0b96b10</t>
+          <t>https://www.indeed.com/viewjob?jk=0866a4d4cc7dec0c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Data Warehouse/BI Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>ThinkMirum, Inc.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b11bc9d20fc1e2e2</t>
+          <t>https://www.indeed.com/viewjob?jk=fe28e970e1130d6e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Fullstack Software Engineer (Special Projects Team)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Aeroflow Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Asheville, NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a6f623279ee6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=61e2c56fc5827763</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2648,15 +2648,15 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,14 +2666,14 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3cccca60e879db</t>
+          <t>https://www.indeed.com/viewjob?jk=503269b060f28151</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2683,15 +2683,15 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,277 +2701,277 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f821dc8a5f6559</t>
+          <t>https://www.indeed.com/viewjob?jk=dbeb792ea58b7a87</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e6f7f78ae5d82f3</t>
+          <t>https://www.indeed.com/viewjob?jk=fd899ffea8f1b74c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3763de2ff690fcf</t>
+          <t>https://www.indeed.com/viewjob?jk=f22565dd904e0808</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3583ff1e8ab8b831</t>
+          <t>https://www.indeed.com/viewjob?jk=f8fcbfbc5352b0bf</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Dresher, PA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a764bcc9a479a693</t>
+          <t>https://www.indeed.com/viewjob?jk=d1da94812ec374b4</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8b0a891a5da57c1</t>
+          <t>https://www.indeed.com/viewjob?jk=ee5cdada52faf29e</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fdde135d701446e</t>
+          <t>https://www.indeed.com/viewjob?jk=5676e61db2aa81f3</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68e8fc35af3fc28f</t>
+          <t>https://www.indeed.com/viewjob?jk=de6aa6e4975245c5</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>HealthMark Group</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd869bd281c90f0</t>
+          <t>https://www.indeed.com/viewjob?jk=e73fae08616e3afd</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps</t>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,952 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c10fe2dd154808d6</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Consultant - Cloud SRE Admin</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Genpact</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f3dc8b002eb283aa</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>MLOps Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Ascendion</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4687b9b235a9a6ce</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Trepp</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd8df1b20c5849b</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer – Upstream Oil &amp; Gas</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Crescent Energy</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt, Power BI</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=619ee2b50d37daac</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>ML Support Engineer</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, CI/CD</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a4281d96efe6a7c5</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Backend Software Engineer (Mid-Level / Senior)</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Airvet</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=87ce4c6973528ac7</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Data Scientist II</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Chewy</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=62210abb12166a07</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Data Scientist II</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Chewy</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=26a71508d797185b</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dbeb792ea58b7a87</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f22565dd904e0808</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f8fcbfbc5352b0bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Senior Engineer - .NET</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d1da94812ec374b4</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ee5cdada52faf29e</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Los Angeles Times</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>El Segundo, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, ECS, RDS, Scala, DynamoDB, CI/CD, Docker, Git, Python</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d108b54b3fe154f0</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Fullstack Software Engineer (Special Projects Team)</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Aeroflow Health</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Asheville, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, DynamoDB, CI/CD</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=61e2c56fc5827763</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Architect</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, CI/CD, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=948ed5bfb3c6e050</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e73fae08616e3afd</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=2cdec8d2c07ce6a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Engineer II</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=503269b060f28151</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Engineer II- .Net</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fd899ffea8f1b74c</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Engineer II</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5676e61db2aa81f3</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Engineer II- .Net</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=de6aa6e4975245c5</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Teradata Developer-5</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6f4f91dff933f5cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>NiyamIT</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Ashburn, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1a1802cfcb8371e8</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>[CoreIgnite] Senior Java Developer (AWS) - Shashank Srivastava</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Luxoft</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0866a4d4cc7dec0c</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Data Warehouse/BI Developer</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>ThinkMirum, Inc.</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe28e970e1130d6e</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Sr. Engineer, Go To Market AI</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>brightwheel</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, S3, SNS, RDS, PostgreSQL, Data Modeling, CI/CD, GitHub Actions, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=92aac63fae4e53fd</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-26.xlsx
+++ b/results/job_matches_2026-02-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,52 +608,52 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Advisor II, Data Architect</t>
+          <t>DevOps Software Engineer III</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, EMR, Lambda, Redshift, Athena, S3, RDS, Oozie, Scala, Oracle</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21bd27b152469170</t>
+          <t>https://www.indeed.com/viewjob?jk=ae9c515199307b36</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Senior Advisor II, Data Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, ECS, RDS, Databricks, BigQuery, Vertex AI, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,59 +671,59 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15f2e018b3b0d55e</t>
+          <t>https://www.indeed.com/viewjob?jk=21bd27b152469170</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SolidLine Media</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Kinesis, ECS, RDS, Databricks, BigQuery, Vertex AI, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e8185f66fc8c270</t>
+          <t>https://www.indeed.com/viewjob?jk=15f2e018b3b0d55e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>American Family Insurance</t>
+          <t>SolidLine Media</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c5e79cbd14d908</t>
+          <t>https://www.indeed.com/viewjob?jk=8e8185f66fc8c270</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>American Family Insurance</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e89cb44acf96f0ce</t>
+          <t>https://www.indeed.com/viewjob?jk=54c5e79cbd14d908</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer - Boston</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9b3e4586db8c7fd</t>
+          <t>https://www.indeed.com/viewjob?jk=e89cb44acf96f0ce</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer II (USA)</t>
+          <t>Data Engineer - Boston</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,69 +836,69 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=079fa62336e07385</t>
+          <t>https://www.indeed.com/viewjob?jk=b9b3e4586db8c7fd</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-5</t>
+          <t>Software Engineer II (USA)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=656bcb1553978517</t>
+          <t>https://www.indeed.com/viewjob?jk=079fa62336e07385</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Ops Engineer</t>
+          <t>Senior Databricks Developer-5</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,69 +906,69 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8203af416f8f7f</t>
+          <t>https://www.indeed.com/viewjob?jk=656bcb1553978517</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Machine Learning Ops Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SRS Distribution</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9fcb451d7086751</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8203af416f8f7f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GovWorx</t>
+          <t>SRS Distribution</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Spark, PySpark, Scala, MySQL, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ee6445287271c9d</t>
+          <t>https://www.indeed.com/viewjob?jk=e9fcb451d7086751</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Distinguished Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>GovWorx</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Cassandra, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Spark, PySpark, Scala, MySQL, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab3a4b9f2c783845</t>
+          <t>https://www.indeed.com/viewjob?jk=8ee6445287271c9d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Application Developer III, Platform Engineering</t>
+          <t>Distinguished Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Herbalife</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Torrance, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Cassandra, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116acc2ab05b269d</t>
+          <t>https://www.indeed.com/viewjob?jk=ab3a4b9f2c783845</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Remote)</t>
+          <t>Software Engineer III - AI/ML</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Inspira Financial</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03f6284daa41bb63</t>
+          <t>https://www.indeed.com/viewjob?jk=330acb9fbf425d3a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Application Developer III, Platform Engineering</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ramsey Solutions</t>
+          <t>Herbalife</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Torrance, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,59 +1126,59 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba46b1aa50f7279f</t>
+          <t>https://www.indeed.com/viewjob?jk=116acc2ab05b269d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Inspira Financial</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, PostgreSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=693f3e0a054607b0</t>
+          <t>https://www.indeed.com/viewjob?jk=03f6284daa41bb63</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Solution Engineer I</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Associated Wholesale Grocers</t>
+          <t>Ramsey Solutions</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5985bee213bf40</t>
+          <t>https://www.indeed.com/viewjob?jk=ba46b1aa50f7279f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Gradient AI</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, PostgreSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08f4a08591f4e565</t>
+          <t>https://www.indeed.com/viewjob?jk=693f3e0a054607b0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Solution Engineer I</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ripple</t>
+          <t>Associated Wholesale Grocers</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Athena, S3, API Gateway, ECS, Databricks, Spark, Scala</t>
+          <t>AWS, Redshift, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6988d9d372dc66d3</t>
+          <t>https://www.indeed.com/viewjob?jk=5e5985bee213bf40</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Gradient AI</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30154588ed7f957f</t>
+          <t>https://www.indeed.com/viewjob?jk=08f4a08591f4e565</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Ripple</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Kinesis, Athena, S3, API Gateway, ECS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a077c257a4cf0b5</t>
+          <t>https://www.indeed.com/viewjob?jk=6988d9d372dc66d3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Delta Live Tables, BigQuery, Spark, Snowflake, Databricks Lakehouse, ELT, dbt</t>
+          <t>AWS, S3, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39ce7a464350b080</t>
+          <t>https://www.indeed.com/viewjob?jk=30154588ed7f957f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
+          <t>Senior Machine Learning Engineer (Remote)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Eurest</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4699f552f08a017</t>
+          <t>https://www.indeed.com/viewjob?jk=64eeda5b2dfcfe99</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Visualization Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=867f580c7e3bb0e7</t>
+          <t>https://www.indeed.com/viewjob?jk=4a077c257a4cf0b5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Policy Configuration</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,77 +1466,77 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Databricks, Delta Live Tables, BigQuery, Spark, Snowflake, Databricks Lakehouse, ELT, dbt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1acf3efd34722f19</t>
+          <t>https://www.indeed.com/viewjob?jk=39ce7a464350b080</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer II 4P/554</t>
+          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>Eurest</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Oracle, SQL Server, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d963e021c819ac</t>
+          <t>https://www.indeed.com/viewjob?jk=a4699f552f08a017</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, CRM</t>
+          <t>Senior Data Visualization Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
+          <t>Redshift, S3, RDS, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,59 +1546,59 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b266df7f25223b6</t>
+          <t>https://www.indeed.com/viewjob?jk=867f580c7e3bb0e7</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
+          <t>Senior Software Engineer- Policy Configuration</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Compass Group USA</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Hadoop, Spark, Snowflake, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65b5898fc3882a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=1acf3efd34722f19</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Manufacturing Systems Integration Engineer</t>
+          <t>Software Engineer III - Data Engineering Java/Python</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, Power BI, Docker, Kubernetes, Git</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8532be76b040bdb</t>
+          <t>https://www.indeed.com/viewjob?jk=5ec8999487afb4f6</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr Advisor II, AI Architect</t>
+          <t>Data Engineer II 4P/554</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Oracle, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b85a978b0b96b10</t>
+          <t>https://www.indeed.com/viewjob?jk=43d963e021c819ac</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Senior Data Engineer, CRM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b11bc9d20fc1e2e2</t>
+          <t>https://www.indeed.com/viewjob?jk=7b266df7f25223b6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Compass Group USA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Redshift, RDS, BigQuery, Hadoop, Spark, Snowflake, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a6f623279ee6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=65b5898fc3882a0c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Manufacturing Systems Integration Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, Power BI, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3cccca60e879db</t>
+          <t>https://www.indeed.com/viewjob?jk=d8532be76b040bdb</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Sr Advisor II, AI Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f821dc8a5f6559</t>
+          <t>https://www.indeed.com/viewjob?jk=1b85a978b0b96b10</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e6f7f78ae5d82f3</t>
+          <t>https://www.indeed.com/viewjob?jk=b11bc9d20fc1e2e2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3763de2ff690fcf</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a6f623279ee6d4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3583ff1e8ab8b831</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3cccca60e879db</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dresher, PA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a764bcc9a479a693</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f821dc8a5f6559</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,14 +1966,14 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8b0a891a5da57c1</t>
+          <t>https://www.indeed.com/viewjob?jk=1e6f7f78ae5d82f3</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2001,14 +2001,14 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fdde135d701446e</t>
+          <t>https://www.indeed.com/viewjob?jk=e3763de2ff690fcf</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68e8fc35af3fc28f</t>
+          <t>https://www.indeed.com/viewjob?jk=3583ff1e8ab8b831</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>HealthMark Group</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dresher, PA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd869bd281c90f0</t>
+          <t>https://www.indeed.com/viewjob?jk=a764bcc9a479a693</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c10fe2dd154808d6</t>
+          <t>https://www.indeed.com/viewjob?jk=d8b0a891a5da57c1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Consultant - Cloud SRE Admin</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3dc8b002eb283aa</t>
+          <t>https://www.indeed.com/viewjob?jk=0fdde135d701446e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MLOps Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4687b9b235a9a6ce</t>
+          <t>https://www.indeed.com/viewjob?jk=68e8fc35af3fc28f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Trepp</t>
+          <t>HealthMark Group</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd8df1b20c5849b</t>
+          <t>https://www.indeed.com/viewjob?jk=abd869bd281c90f0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Upstream Oil &amp; Gas</t>
+          <t>Software Engineer - DevOps</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Crescent Energy</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619ee2b50d37daac</t>
+          <t>https://www.indeed.com/viewjob?jk=c10fe2dd154808d6</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Consultant - Cloud SRE Admin</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Spark, Scala, CI/CD, Terraform, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7929c83226ae75b</t>
+          <t>https://www.indeed.com/viewjob?jk=f3dc8b002eb283aa</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ML Support Engineer</t>
+          <t>MLOps Platform Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4281d96efe6a7c5</t>
+          <t>https://www.indeed.com/viewjob?jk=4687b9b235a9a6ce</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (Mid-Level / Senior)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Airvet</t>
+          <t>Trepp</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87ce4c6973528ac7</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd8df1b20c5849b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Senior Data Engineer – Upstream Oil &amp; Gas</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Crescent Energy</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
+          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62210abb12166a07</t>
+          <t>https://www.indeed.com/viewjob?jk=619ee2b50d37daac</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Machine Learning Engineer II (Remote)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, CI/CD, Git, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26a71508d797185b</t>
+          <t>https://www.indeed.com/viewjob?jk=dd0ef78a415d3113</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Enterprise AI Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Spark, Scala, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=291c96af0e7cea02</t>
+          <t>https://www.indeed.com/viewjob?jk=e7929c83226ae75b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Teradata Developer-5</t>
+          <t>ML Support Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f4f91dff933f5cc</t>
+          <t>https://www.indeed.com/viewjob?jk=a4281d96efe6a7c5</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Backend Software Engineer (Mid-Level / Senior)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NiyamIT</t>
+          <t>Airvet</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
+          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a1802cfcb8371e8</t>
+          <t>https://www.indeed.com/viewjob?jk=87ce4c6973528ac7</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>[CoreIgnite] Senior Java Developer (AWS) - Shashank Srivastava</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0866a4d4cc7dec0c</t>
+          <t>https://www.indeed.com/viewjob?jk=62210abb12166a07</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Warehouse/BI Developer</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ThinkMirum, Inc.</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe28e970e1130d6e</t>
+          <t>https://www.indeed.com/viewjob?jk=26a71508d797185b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Fullstack Software Engineer (Special Projects Team)</t>
+          <t>Enterprise AI Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Aeroflow Health</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Asheville, NC, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61e2c56fc5827763</t>
+          <t>https://www.indeed.com/viewjob?jk=291c96af0e7cea02</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Software Engineer III - DevOps Automation Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503269b060f28151</t>
+          <t>https://www.indeed.com/viewjob?jk=58638a1a93a5925c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Teradata Developer-5</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbeb792ea58b7a87</t>
+          <t>https://www.indeed.com/viewjob?jk=6f4f91dff933f5cc</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NiyamIT</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd899ffea8f1b74c</t>
+          <t>https://www.indeed.com/viewjob?jk=1a1802cfcb8371e8</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>[CoreIgnite] Senior Java Developer (AWS) - Shashank Srivastava</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f22565dd904e0808</t>
+          <t>https://www.indeed.com/viewjob?jk=0866a4d4cc7dec0c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
+          <t>Data Warehouse/BI Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>ThinkMirum, Inc.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8fcbfbc5352b0bf</t>
+          <t>https://www.indeed.com/viewjob?jk=fe28e970e1130d6e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Fullstack Software Engineer (Special Projects Team)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Aeroflow Health</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Asheville, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,14 +2841,14 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1da94812ec374b4</t>
+          <t>https://www.indeed.com/viewjob?jk=61e2c56fc5827763</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,14 +2876,14 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee5cdada52faf29e</t>
+          <t>https://www.indeed.com/viewjob?jk=503269b060f28151</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5676e61db2aa81f3</t>
+          <t>https://www.indeed.com/viewjob?jk=dbeb792ea58b7a87</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,14 +2946,14 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de6aa6e4975245c5</t>
+          <t>https://www.indeed.com/viewjob?jk=fd899ffea8f1b74c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,24 +2971,24 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73fae08616e3afd</t>
+          <t>https://www.indeed.com/viewjob?jk=f22565dd904e0808</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,15 +3006,225 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f8fcbfbc5352b0bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Senior Engineer - .NET</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Chevy Chase, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1da94812ec374b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Chevy Chase, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee5cdada52faf29e</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Engineer II</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Chevy Chase, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5676e61db2aa81f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Engineer II- .Net</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Chevy Chase, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de6aa6e4975245c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
           <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e73fae08616e3afd</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2cdec8d2c07ce6a8</t>
         </is>

--- a/results/job_matches_2026-02-26.xlsx
+++ b/results/job_matches_2026-02-26.xlsx
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineering III</t>
+          <t>DevOps Software Engineer III</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Equitable</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,34 +591,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Flume, Zookeeper</t>
+          <t>AWS, EMR, Lambda, Redshift, Athena, S3, RDS, Oozie, Scala, Oracle</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1753914a33e85905</t>
+          <t>https://www.indeed.com/viewjob?jk=ae9c515199307b36</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer III</t>
+          <t>Software Engineering III</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Equitable</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,17 +626,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, Athena, S3, RDS, Oozie, Scala, Oracle</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Flume, Zookeeper</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae9c515199307b36</t>
+          <t>https://www.indeed.com/viewjob?jk=1753914a33e85905</t>
         </is>
       </c>
     </row>
@@ -1063,17 +1063,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML</t>
+          <t>Application Developer III, Platform Engineering</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Herbalife</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Torrance, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=330acb9fbf425d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=116acc2ab05b269d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Application Developer III, Platform Engineering</t>
+          <t>Software Engineer III - AI/ML</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Herbalife</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Torrance, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,17 +1116,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116acc2ab05b269d</t>
+          <t>https://www.indeed.com/viewjob?jk=330acb9fbf425d3a</t>
         </is>
       </c>
     </row>
@@ -2393,17 +2393,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II (Remote)</t>
+          <t>Enterprise AI Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, CI/CD, Git, Python, SQL, Java</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd0ef78a415d3113</t>
+          <t>https://www.indeed.com/viewjob?jk=291c96af0e7cea02</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Machine Learning Engineer II (Remote)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Spark, Scala, CI/CD, Terraform, Git</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, CI/CD, Git, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7929c83226ae75b</t>
+          <t>https://www.indeed.com/viewjob?jk=dd0ef78a415d3113</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ML Support Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Spark, Scala, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4281d96efe6a7c5</t>
+          <t>https://www.indeed.com/viewjob?jk=e7929c83226ae75b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (Mid-Level / Senior)</t>
+          <t>ML Support Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Airvet</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87ce4c6973528ac7</t>
+          <t>https://www.indeed.com/viewjob?jk=a4281d96efe6a7c5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Backend Software Engineer (Mid-Level / Senior)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Airvet</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,17 +2551,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
+          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62210abb12166a07</t>
+          <t>https://www.indeed.com/viewjob?jk=87ce4c6973528ac7</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26a71508d797185b</t>
+          <t>https://www.indeed.com/viewjob?jk=62210abb12166a07</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Enterprise AI Architect</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=291c96af0e7cea02</t>
+          <t>https://www.indeed.com/viewjob?jk=26a71508d797185b</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-26.xlsx
+++ b/results/job_matches_2026-02-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer III</t>
+          <t>Software Engineering III</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Equitable</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,34 +591,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, Athena, S3, RDS, Oozie, Scala, Oracle</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Flume, Zookeeper</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae9c515199307b36</t>
+          <t>https://www.indeed.com/viewjob?jk=1753914a33e85905</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineering III</t>
+          <t>DevOps Software Engineer III</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Equitable</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Flume, Zookeeper</t>
+          <t>AWS, EMR, Lambda, Redshift, Athena, S3, RDS, Oozie, Scala, Oracle</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1753914a33e85905</t>
+          <t>https://www.indeed.com/viewjob?jk=ae9c515199307b36</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Advisor II, Data Architect</t>
+          <t>Senior Data Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>First American</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21bd27b152469170</t>
+          <t>https://www.indeed.com/viewjob?jk=05ccb57abd2eb2be</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Senior Advisor II, Data Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, ECS, RDS, Databricks, BigQuery, Vertex AI, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,59 +706,59 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15f2e018b3b0d55e</t>
+          <t>https://www.indeed.com/viewjob?jk=21bd27b152469170</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SolidLine Media</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Kinesis, ECS, RDS, Databricks, BigQuery, Vertex AI, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e8185f66fc8c270</t>
+          <t>https://www.indeed.com/viewjob?jk=15f2e018b3b0d55e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>American Family Insurance</t>
+          <t>SolidLine Media</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c5e79cbd14d908</t>
+          <t>https://www.indeed.com/viewjob?jk=8e8185f66fc8c270</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>American Family Insurance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e89cb44acf96f0ce</t>
+          <t>https://www.indeed.com/viewjob?jk=54c5e79cbd14d908</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer - Boston</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9b3e4586db8c7fd</t>
+          <t>https://www.indeed.com/viewjob?jk=e89cb44acf96f0ce</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer II (USA)</t>
+          <t>Data Engineer - Boston</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,69 +871,69 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=079fa62336e07385</t>
+          <t>https://www.indeed.com/viewjob?jk=b9b3e4586db8c7fd</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-5</t>
+          <t>Software Engineer II (USA)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=656bcb1553978517</t>
+          <t>https://www.indeed.com/viewjob?jk=079fa62336e07385</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Ops Engineer</t>
+          <t>Senior Databricks Developer-5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,77 +941,77 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8203af416f8f7f</t>
+          <t>https://www.indeed.com/viewjob?jk=656bcb1553978517</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Azure Data Engineer I</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SRS Distribution</t>
+          <t>Premise Health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ELT, Talend</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9fcb451d7086751</t>
+          <t>https://www.indeed.com/viewjob?jk=353cdf1ee00c6fd9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Machine Learning Ops Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GovWorx</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Spark, PySpark, Scala, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ee6445287271c9d</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8203af416f8f7f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Distinguished Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>SRS Distribution</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Cassandra, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab3a4b9f2c783845</t>
+          <t>https://www.indeed.com/viewjob?jk=e9fcb451d7086751</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Application Developer III, Platform Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Herbalife</t>
+          <t>GovWorx</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Torrance, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Spark, PySpark, Scala, MySQL, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116acc2ab05b269d</t>
+          <t>https://www.indeed.com/viewjob?jk=8ee6445287271c9d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML</t>
+          <t>Application Developer III, Platform Engineering</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Herbalife</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Torrance, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=330acb9fbf425d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=116acc2ab05b269d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Remote)</t>
+          <t>Distinguished Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Inspira Financial</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,104 +1151,104 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Cassandra, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03f6284daa41bb63</t>
+          <t>https://www.indeed.com/viewjob?jk=ab3a4b9f2c783845</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer III - AI/ML</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ramsey Solutions</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba46b1aa50f7279f</t>
+          <t>https://www.indeed.com/viewjob?jk=330acb9fbf425d3a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Inspira Financial</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, PostgreSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=693f3e0a054607b0</t>
+          <t>https://www.indeed.com/viewjob?jk=03f6284daa41bb63</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Solution Engineer I</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Associated Wholesale Grocers</t>
+          <t>Ramsey Solutions</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5985bee213bf40</t>
+          <t>https://www.indeed.com/viewjob?jk=ba46b1aa50f7279f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Gradient AI</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, PostgreSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08f4a08591f4e565</t>
+          <t>https://www.indeed.com/viewjob?jk=693f3e0a054607b0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Solution Engineer I</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ripple</t>
+          <t>Associated Wholesale Grocers</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Athena, S3, API Gateway, ECS, Databricks, Spark, Scala</t>
+          <t>AWS, Redshift, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6988d9d372dc66d3</t>
+          <t>https://www.indeed.com/viewjob?jk=5e5985bee213bf40</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Gradient AI</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30154588ed7f957f</t>
+          <t>https://www.indeed.com/viewjob?jk=08f4a08591f4e565</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Remote)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Ripple</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
+          <t>AWS, Lambda, Kinesis, Athena, S3, API Gateway, ECS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64eeda5b2dfcfe99</t>
+          <t>https://www.indeed.com/viewjob?jk=6988d9d372dc66d3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, S3, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a077c257a4cf0b5</t>
+          <t>https://www.indeed.com/viewjob?jk=30154588ed7f957f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Machine Learning Engineer (Remote)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Delta Live Tables, BigQuery, Spark, Snowflake, Databricks Lakehouse, ELT, dbt</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39ce7a464350b080</t>
+          <t>https://www.indeed.com/viewjob?jk=64eeda5b2dfcfe99</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Eurest</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4699f552f08a017</t>
+          <t>https://www.indeed.com/viewjob?jk=4a077c257a4cf0b5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Visualization Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
+          <t>AWS, RDS, Databricks, Delta Live Tables, BigQuery, Spark, Snowflake, Databricks Lakehouse, ELT, dbt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=867f580c7e3bb0e7</t>
+          <t>https://www.indeed.com/viewjob?jk=39ce7a464350b080</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Policy Configuration</t>
+          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Eurest</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,104 +1571,104 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1acf3efd34722f19</t>
+          <t>https://www.indeed.com/viewjob?jk=a4699f552f08a017</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Engineering Java/Python</t>
+          <t>Senior Data Visualization Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
+          <t>Redshift, S3, RDS, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ec8999487afb4f6</t>
+          <t>https://www.indeed.com/viewjob?jk=867f580c7e3bb0e7</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer II 4P/554</t>
+          <t>Senior Software Engineer- Policy Configuration</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Oracle, SQL Server, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d963e021c819ac</t>
+          <t>https://www.indeed.com/viewjob?jk=1acf3efd34722f19</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, CRM</t>
+          <t>Software Engineer III - Data Engineering Java/Python</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b266df7f25223b6</t>
+          <t>https://www.indeed.com/viewjob?jk=5ec8999487afb4f6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
+          <t>Data Engineer II 4P/554</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Compass Group USA</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Hadoop, Spark, Snowflake, Oracle, PostgreSQL, MySQL</t>
+          <t>Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Oracle, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65b5898fc3882a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=43d963e021c819ac</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Manufacturing Systems Integration Engineer</t>
+          <t>Senior Data Engineer, CRM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, Power BI, Docker, Kubernetes, Git</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8532be76b040bdb</t>
+          <t>https://www.indeed.com/viewjob?jk=7b266df7f25223b6</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr Advisor II, AI Architect</t>
+          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Compass Group USA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, BigQuery, Hadoop, Spark, Snowflake, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b85a978b0b96b10</t>
+          <t>https://www.indeed.com/viewjob?jk=65b5898fc3882a0c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Manufacturing Systems Integration Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, Power BI, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b11bc9d20fc1e2e2</t>
+          <t>https://www.indeed.com/viewjob?jk=d8532be76b040bdb</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Sr Advisor II, AI Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,17 +1851,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a6f623279ee6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=1b85a978b0b96b10</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3cccca60e879db</t>
+          <t>https://www.indeed.com/viewjob?jk=b11bc9d20fc1e2e2</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f821dc8a5f6559</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a6f623279ee6d4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e6f7f78ae5d82f3</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3cccca60e879db</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3763de2ff690fcf</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f821dc8a5f6559</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,14 +2036,14 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3583ff1e8ab8b831</t>
+          <t>https://www.indeed.com/viewjob?jk=1e6f7f78ae5d82f3</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dresher, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,14 +2071,14 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a764bcc9a479a693</t>
+          <t>https://www.indeed.com/viewjob?jk=e3763de2ff690fcf</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8b0a891a5da57c1</t>
+          <t>https://www.indeed.com/viewjob?jk=3583ff1e8ab8b831</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dresher, PA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fdde135d701446e</t>
+          <t>https://www.indeed.com/viewjob?jk=a764bcc9a479a693</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68e8fc35af3fc28f</t>
+          <t>https://www.indeed.com/viewjob?jk=d8b0a891a5da57c1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>HealthMark Group</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd869bd281c90f0</t>
+          <t>https://www.indeed.com/viewjob?jk=0fdde135d701446e</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c10fe2dd154808d6</t>
+          <t>https://www.indeed.com/viewjob?jk=68e8fc35af3fc28f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Consultant - Cloud SRE Admin</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>HealthMark Group</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3dc8b002eb283aa</t>
+          <t>https://www.indeed.com/viewjob?jk=abd869bd281c90f0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MLOps Platform Engineer</t>
+          <t>Software Engineer - DevOps</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4687b9b235a9a6ce</t>
+          <t>https://www.indeed.com/viewjob?jk=c10fe2dd154808d6</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Consultant - Cloud SRE Admin</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Trepp</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd8df1b20c5849b</t>
+          <t>https://www.indeed.com/viewjob?jk=f3dc8b002eb283aa</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Upstream Oil &amp; Gas</t>
+          <t>MLOps Platform Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Crescent Energy</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619ee2b50d37daac</t>
+          <t>https://www.indeed.com/viewjob?jk=4687b9b235a9a6ce</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Enterprise AI Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>Trepp</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=291c96af0e7cea02</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd8df1b20c5849b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II (Remote)</t>
+          <t>Senior Data Engineer – Upstream Oil &amp; Gas</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Crescent Energy</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, CI/CD, Git, Python, SQL, Java</t>
+          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd0ef78a415d3113</t>
+          <t>https://www.indeed.com/viewjob?jk=619ee2b50d37daac</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer III - DevOps Automation Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Spark, Scala, CI/CD, Terraform, Git</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7929c83226ae75b</t>
+          <t>https://www.indeed.com/viewjob?jk=58638a1a93a5925c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ML Support Engineer</t>
+          <t>Enterprise AI Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4281d96efe6a7c5</t>
+          <t>https://www.indeed.com/viewjob?jk=291c96af0e7cea02</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (Mid-Level / Senior)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Airvet</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Spark, Scala, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87ce4c6973528ac7</t>
+          <t>https://www.indeed.com/viewjob?jk=e7929c83226ae75b</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Machine Learning Engineer II (Remote)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, CI/CD, Git, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62210abb12166a07</t>
+          <t>https://www.indeed.com/viewjob?jk=dd0ef78a415d3113</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>ML Support Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26a71508d797185b</t>
+          <t>https://www.indeed.com/viewjob?jk=a4281d96efe6a7c5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer III - DevOps Automation Engineer</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58638a1a93a5925c</t>
+          <t>https://www.indeed.com/viewjob?jk=62210abb12166a07</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Teradata Developer-5</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f4f91dff933f5cc</t>
+          <t>https://www.indeed.com/viewjob?jk=26a71508d797185b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Teradata Developer-5</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NiyamIT</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a1802cfcb8371e8</t>
+          <t>https://www.indeed.com/viewjob?jk=6f4f91dff933f5cc</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>[CoreIgnite] Senior Java Developer (AWS) - Shashank Srivastava</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>NiyamIT</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0866a4d4cc7dec0c</t>
+          <t>https://www.indeed.com/viewjob?jk=1a1802cfcb8371e8</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Warehouse/BI Developer</t>
+          <t>[CoreIgnite] Senior Java Developer (AWS) - Shashank Srivastava</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ThinkMirum, Inc.</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe28e970e1130d6e</t>
+          <t>https://www.indeed.com/viewjob?jk=0866a4d4cc7dec0c</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Fullstack Software Engineer (Special Projects Team)</t>
+          <t>Data Warehouse/BI Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Aeroflow Health</t>
+          <t>ThinkMirum, Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Asheville, NC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, DynamoDB, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61e2c56fc5827763</t>
+          <t>https://www.indeed.com/viewjob?jk=fe28e970e1130d6e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Fullstack Software Engineer (Special Projects Team)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Aeroflow Health</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Asheville, NC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,14 +2876,14 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503269b060f28151</t>
+          <t>https://www.indeed.com/viewjob?jk=61e2c56fc5827763</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,14 +2911,14 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbeb792ea58b7a87</t>
+          <t>https://www.indeed.com/viewjob?jk=503269b060f28151</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,14 +2946,14 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd899ffea8f1b74c</t>
+          <t>https://www.indeed.com/viewjob?jk=dbeb792ea58b7a87</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,14 +2981,14 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f22565dd904e0808</t>
+          <t>https://www.indeed.com/viewjob?jk=fd899ffea8f1b74c</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,14 +3016,14 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8fcbfbc5352b0bf</t>
+          <t>https://www.indeed.com/viewjob?jk=f22565dd904e0808</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,14 +3051,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1da94812ec374b4</t>
+          <t>https://www.indeed.com/viewjob?jk=f8fcbfbc5352b0bf</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3086,14 +3086,14 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee5cdada52faf29e</t>
+          <t>https://www.indeed.com/viewjob?jk=d1da94812ec374b4</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,14 +3121,14 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5676e61db2aa81f3</t>
+          <t>https://www.indeed.com/viewjob?jk=ee5cdada52faf29e</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,14 +3156,14 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de6aa6e4975245c5</t>
+          <t>https://www.indeed.com/viewjob?jk=5676e61db2aa81f3</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,17 +3181,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73fae08616e3afd</t>
+          <t>https://www.indeed.com/viewjob?jk=de6aa6e4975245c5</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3225,6 +3225,41 @@
         </is>
       </c>
       <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e73fae08616e3afd</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2cdec8d2c07ce6a8</t>
         </is>

--- a/results/job_matches_2026-02-26.xlsx
+++ b/results/job_matches_2026-02-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Application Developer III, Platform Engineering</t>
+          <t>Distinguished Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Herbalife</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Torrance, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Cassandra, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116acc2ab05b269d</t>
+          <t>https://www.indeed.com/viewjob?jk=ab3a4b9f2c783845</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Distinguished Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Cassandra, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab3a4b9f2c783845</t>
+          <t>https://www.indeed.com/viewjob?jk=b57d55c8e2a74923</t>
         </is>
       </c>
     </row>
@@ -1203,17 +1203,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Remote)</t>
+          <t>Application Developer III, Platform Engineering</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Inspira Financial</t>
+          <t>Herbalife</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Torrance, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,69 +1221,69 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03f6284daa41bb63</t>
+          <t>https://www.indeed.com/viewjob?jk=116acc2ab05b269d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ramsey Solutions</t>
+          <t>Inspira Financial</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba46b1aa50f7279f</t>
+          <t>https://www.indeed.com/viewjob?jk=03f6284daa41bb63</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Ramsey Solutions</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, PostgreSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=693f3e0a054607b0</t>
+          <t>https://www.indeed.com/viewjob?jk=ba46b1aa50f7279f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Solution Engineer I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Associated Wholesale Grocers</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, PostgreSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5985bee213bf40</t>
+          <t>https://www.indeed.com/viewjob?jk=693f3e0a054607b0</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Solution Engineer I</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Gradient AI</t>
+          <t>Associated Wholesale Grocers</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Terraform</t>
+          <t>AWS, Redshift, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08f4a08591f4e565</t>
+          <t>https://www.indeed.com/viewjob?jk=5e5985bee213bf40</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ripple</t>
+          <t>Gradient AI</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Athena, S3, API Gateway, ECS, Databricks, Spark, Scala</t>
+          <t>AWS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6988d9d372dc66d3</t>
+          <t>https://www.indeed.com/viewjob?jk=08f4a08591f4e565</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Ripple</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, Athena, S3, API Gateway, ECS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30154588ed7f957f</t>
+          <t>https://www.indeed.com/viewjob?jk=6988d9d372dc66d3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Remote)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
+          <t>AWS, S3, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64eeda5b2dfcfe99</t>
+          <t>https://www.indeed.com/viewjob?jk=30154588ed7f957f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Machine Learning Engineer (Remote)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a077c257a4cf0b5</t>
+          <t>https://www.indeed.com/viewjob?jk=64eeda5b2dfcfe99</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Delta Live Tables, BigQuery, Spark, Snowflake, Databricks Lakehouse, ELT, dbt</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39ce7a464350b080</t>
+          <t>https://www.indeed.com/viewjob?jk=4a077c257a4cf0b5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Eurest</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Databricks, Delta Live Tables, BigQuery, Spark, Snowflake, Databricks Lakehouse, ELT, dbt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4699f552f08a017</t>
+          <t>https://www.indeed.com/viewjob?jk=39ce7a464350b080</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Visualization Engineer</t>
+          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Eurest</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=867f580c7e3bb0e7</t>
+          <t>https://www.indeed.com/viewjob?jk=a4699f552f08a017</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Policy Configuration</t>
+          <t>Senior Data Visualization Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,42 +1641,42 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
+          <t>Redshift, S3, RDS, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1acf3efd34722f19</t>
+          <t>https://www.indeed.com/viewjob?jk=867f580c7e3bb0e7</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Engineering Java/Python</t>
+          <t>Senior Software Engineer- Policy Configuration</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ec8999487afb4f6</t>
+          <t>https://www.indeed.com/viewjob?jk=1acf3efd34722f19</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer II 4P/554</t>
+          <t>Software Engineer III - Data Engineering Java/Python</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Oracle, SQL Server, NoSQL, Data Modeling</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d963e021c819ac</t>
+          <t>https://www.indeed.com/viewjob?jk=5ec8999487afb4f6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, CRM</t>
+          <t>Data Engineer II 4P/554</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
+          <t>Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Oracle, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b266df7f25223b6</t>
+          <t>https://www.indeed.com/viewjob?jk=43d963e021c819ac</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
+          <t>Senior Data Engineer, CRM</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Compass Group USA</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Hadoop, Spark, Snowflake, Oracle, PostgreSQL, MySQL</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65b5898fc3882a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=7b266df7f25223b6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Manufacturing Systems Integration Engineer</t>
+          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>Compass Group USA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, Power BI, Docker, Kubernetes, Git</t>
+          <t>AWS, Redshift, RDS, BigQuery, Hadoop, Spark, Snowflake, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8532be76b040bdb</t>
+          <t>https://www.indeed.com/viewjob?jk=65b5898fc3882a0c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr Advisor II, AI Architect</t>
+          <t>Manufacturing Systems Integration Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, Power BI, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b85a978b0b96b10</t>
+          <t>https://www.indeed.com/viewjob?jk=d8532be76b040bdb</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Sr Advisor II, AI Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,17 +1886,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b11bc9d20fc1e2e2</t>
+          <t>https://www.indeed.com/viewjob?jk=1b85a978b0b96b10</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a6f623279ee6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=b11bc9d20fc1e2e2</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3cccca60e879db</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a6f623279ee6d4</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f821dc8a5f6559</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3cccca60e879db</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e6f7f78ae5d82f3</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f821dc8a5f6559</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3763de2ff690fcf</t>
+          <t>https://www.indeed.com/viewjob?jk=1e6f7f78ae5d82f3</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,14 +2106,14 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3583ff1e8ab8b831</t>
+          <t>https://www.indeed.com/viewjob?jk=e3763de2ff690fcf</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dresher, PA, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a764bcc9a479a693</t>
+          <t>https://www.indeed.com/viewjob?jk=3583ff1e8ab8b831</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Dresher, PA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8b0a891a5da57c1</t>
+          <t>https://www.indeed.com/viewjob?jk=a764bcc9a479a693</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fdde135d701446e</t>
+          <t>https://www.indeed.com/viewjob?jk=d8b0a891a5da57c1</t>
         </is>
       </c>
     </row>
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68e8fc35af3fc28f</t>
+          <t>https://www.indeed.com/viewjob?jk=0fdde135d701446e</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>HealthMark Group</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd869bd281c90f0</t>
+          <t>https://www.indeed.com/viewjob?jk=68e8fc35af3fc28f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>HealthMark Group</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Jenkins</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c10fe2dd154808d6</t>
+          <t>https://www.indeed.com/viewjob?jk=abd869bd281c90f0</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Consultant - Cloud SRE Admin</t>
+          <t>Software Engineer - DevOps</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3dc8b002eb283aa</t>
+          <t>https://www.indeed.com/viewjob?jk=c10fe2dd154808d6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MLOps Platform Engineer</t>
+          <t>Consultant - Cloud SRE Admin</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4687b9b235a9a6ce</t>
+          <t>https://www.indeed.com/viewjob?jk=f3dc8b002eb283aa</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>MLOps Platform Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Trepp</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
+          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd8df1b20c5849b</t>
+          <t>https://www.indeed.com/viewjob?jk=4687b9b235a9a6ce</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Upstream Oil &amp; Gas</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Crescent Energy</t>
+          <t>Trepp</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,19 +2456,19 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619ee2b50d37daac</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd8df1b20c5849b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer III - DevOps Automation Engineer</t>
+          <t>Senior Data Engineer – Upstream Oil &amp; Gas</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Crescent Energy</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
+          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58638a1a93a5925c</t>
+          <t>https://www.indeed.com/viewjob?jk=619ee2b50d37daac</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Enterprise AI Architect</t>
+          <t>Machine Learning Engineer II (Remote)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, CI/CD, Git, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=291c96af0e7cea02</t>
+          <t>https://www.indeed.com/viewjob?jk=dd0ef78a415d3113</t>
         </is>
       </c>
     </row>
@@ -2568,17 +2568,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II (Remote)</t>
+          <t>ML Support Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, CI/CD, Git, Python, SQL, Java</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd0ef78a415d3113</t>
+          <t>https://www.indeed.com/viewjob?jk=a4281d96efe6a7c5</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ML Support Engineer</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4281d96efe6a7c5</t>
+          <t>https://www.indeed.com/viewjob?jk=62210abb12166a07</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62210abb12166a07</t>
+          <t>https://www.indeed.com/viewjob?jk=26a71508d797185b</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Enterprise AI Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26a71508d797185b</t>
+          <t>https://www.indeed.com/viewjob?jk=291c96af0e7cea02</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Teradata Developer-5</t>
+          <t>Software Engineer III - DevOps Automation Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f4f91dff933f5cc</t>
+          <t>https://www.indeed.com/viewjob?jk=58638a1a93a5925c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Teradata Developer-5</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NiyamIT</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a1802cfcb8371e8</t>
+          <t>https://www.indeed.com/viewjob?jk=6f4f91dff933f5cc</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>[CoreIgnite] Senior Java Developer (AWS) - Shashank Srivastava</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>NiyamIT</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0866a4d4cc7dec0c</t>
+          <t>https://www.indeed.com/viewjob?jk=1a1802cfcb8371e8</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Warehouse/BI Developer</t>
+          <t>[CoreIgnite] Senior Java Developer (AWS) - Shashank Srivastava</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ThinkMirum, Inc.</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe28e970e1130d6e</t>
+          <t>https://www.indeed.com/viewjob?jk=0866a4d4cc7dec0c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Fullstack Software Engineer (Special Projects Team)</t>
+          <t>Data Warehouse/BI Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Aeroflow Health</t>
+          <t>ThinkMirum, Inc.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Asheville, NC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, DynamoDB, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61e2c56fc5827763</t>
+          <t>https://www.indeed.com/viewjob?jk=fe28e970e1130d6e</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Fullstack Software Engineer (Special Projects Team)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Aeroflow Health</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Asheville, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,14 +2911,14 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503269b060f28151</t>
+          <t>https://www.indeed.com/viewjob?jk=61e2c56fc5827763</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,14 +2946,14 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbeb792ea58b7a87</t>
+          <t>https://www.indeed.com/viewjob?jk=503269b060f28151</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,14 +2981,14 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd899ffea8f1b74c</t>
+          <t>https://www.indeed.com/viewjob?jk=dbeb792ea58b7a87</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,14 +3016,14 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f22565dd904e0808</t>
+          <t>https://www.indeed.com/viewjob?jk=fd899ffea8f1b74c</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,14 +3051,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8fcbfbc5352b0bf</t>
+          <t>https://www.indeed.com/viewjob?jk=f22565dd904e0808</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,14 +3086,14 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1da94812ec374b4</t>
+          <t>https://www.indeed.com/viewjob?jk=f8fcbfbc5352b0bf</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3121,14 +3121,14 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee5cdada52faf29e</t>
+          <t>https://www.indeed.com/viewjob?jk=d1da94812ec374b4</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,14 +3156,14 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5676e61db2aa81f3</t>
+          <t>https://www.indeed.com/viewjob?jk=ee5cdada52faf29e</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,14 +3191,14 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de6aa6e4975245c5</t>
+          <t>https://www.indeed.com/viewjob?jk=5676e61db2aa81f3</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,17 +3216,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73fae08616e3afd</t>
+          <t>https://www.indeed.com/viewjob?jk=de6aa6e4975245c5</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3260,6 +3260,41 @@
         </is>
       </c>
       <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e73fae08616e3afd</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2cdec8d2c07ce6a8</t>
         </is>

--- a/results/job_matches_2026-02-26.xlsx
+++ b/results/job_matches_2026-02-26.xlsx
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DevOps &amp; Backend Engineer — Mid/Senior</t>
+          <t>Software Engineering III</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Open Insurance</t>
+          <t>Equitable</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Flume, Zookeeper</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6691fd82745fd2c9</t>
+          <t>https://www.indeed.com/viewjob?jk=1753914a33e85905</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineering III</t>
+          <t>Senior Data Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Equitable</t>
+          <t>First American</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Flume, Zookeeper</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,59 +601,59 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1753914a33e85905</t>
+          <t>https://www.indeed.com/viewjob?jk=05ccb57abd2eb2be</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer III</t>
+          <t>Senior Advisor II, Data Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, Athena, S3, RDS, Oozie, Scala, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae9c515199307b36</t>
+          <t>https://www.indeed.com/viewjob?jk=21bd27b152469170</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote in CA)</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>First American</t>
+          <t>Disney Entertainment Television</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, Kinesis, ECS, RDS, Databricks, BigQuery, Vertex AI, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05ccb57abd2eb2be</t>
+          <t>https://www.indeed.com/viewjob?jk=06c7525b9f402e34</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Advisor II, Data Architect</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, Kinesis, ECS, RDS, Databricks, BigQuery, Vertex AI, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,59 +706,59 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21bd27b152469170</t>
+          <t>https://www.indeed.com/viewjob?jk=15f2e018b3b0d55e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>SolidLine Media</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, ECS, RDS, Databricks, BigQuery, Vertex AI, Spark, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15f2e018b3b0d55e</t>
+          <t>https://www.indeed.com/viewjob?jk=8e8185f66fc8c270</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Python, SQL, AWS) - Navigator Platform</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SolidLine Media</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,17 +766,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e8185f66fc8c270</t>
+          <t>https://www.indeed.com/viewjob?jk=38b02b46801c7f10</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>American Family Insurance</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c5e79cbd14d908</t>
+          <t>https://www.indeed.com/viewjob?jk=ef8a3d8ad1cf49b7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>American Family Insurance</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e89cb44acf96f0ce</t>
+          <t>https://www.indeed.com/viewjob?jk=54c5e79cbd14d908</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer - Boston</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9b3e4586db8c7fd</t>
+          <t>https://www.indeed.com/viewjob?jk=e89cb44acf96f0ce</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer II (USA)</t>
+          <t>Data Engineer - Boston</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,77 +906,77 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=079fa62336e07385</t>
+          <t>https://www.indeed.com/viewjob?jk=b9b3e4586db8c7fd</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-5</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=656bcb1553978517</t>
+          <t>https://www.indeed.com/viewjob?jk=2d7b87445d04d0bb</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Azure Data Engineer I</t>
+          <t>Software Engineer II (USA)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Premise Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ELT, Talend</t>
+          <t>AWS, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=353cdf1ee00c6fd9</t>
+          <t>https://www.indeed.com/viewjob?jk=079fa62336e07385</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Ops Engineer</t>
+          <t>Senior Databricks Developer-5</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,77 +1011,77 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8203af416f8f7f</t>
+          <t>https://www.indeed.com/viewjob?jk=656bcb1553978517</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Azure Data Engineer I</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SRS Distribution</t>
+          <t>Premise Health</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ELT, Talend</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9fcb451d7086751</t>
+          <t>https://www.indeed.com/viewjob?jk=353cdf1ee00c6fd9</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Machine Learning Ops Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GovWorx</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Spark, PySpark, Scala, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ee6445287271c9d</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8203af416f8f7f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Distinguished Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>SRS Distribution</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Cassandra, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab3a4b9f2c783845</t>
+          <t>https://www.indeed.com/viewjob?jk=e9fcb451d7086751</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>GovWorx</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Spark, PySpark, Scala, MySQL, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b57d55c8e2a74923</t>
+          <t>https://www.indeed.com/viewjob?jk=8ee6445287271c9d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML</t>
+          <t>Distinguished Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Cassandra, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=330acb9fbf425d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=ab3a4b9f2c783845</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Application Developer III, Platform Engineering</t>
+          <t>Sr. Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Herbalife</t>
+          <t>Inspira Financial</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Torrance, CA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116acc2ab05b269d</t>
+          <t>https://www.indeed.com/viewjob?jk=03f6284daa41bb63</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Remote)</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Inspira Financial</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,42 +1256,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03f6284daa41bb63</t>
+          <t>https://www.indeed.com/viewjob?jk=b57d55c8e2a74923</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Application Developer III, Platform Engineering</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ramsey Solutions</t>
+          <t>Herbalife</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Torrance, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba46b1aa50f7279f</t>
+          <t>https://www.indeed.com/viewjob?jk=116acc2ab05b269d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Ramsey Solutions</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, PostgreSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=693f3e0a054607b0</t>
+          <t>https://www.indeed.com/viewjob?jk=ba46b1aa50f7279f</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Solution Engineer I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Associated Wholesale Grocers</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, PostgreSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5985bee213bf40</t>
+          <t>https://www.indeed.com/viewjob?jk=693f3e0a054607b0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Solution Engineer I</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Gradient AI</t>
+          <t>Associated Wholesale Grocers</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Terraform</t>
+          <t>AWS, Redshift, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08f4a08591f4e565</t>
+          <t>https://www.indeed.com/viewjob?jk=5e5985bee213bf40</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ripple</t>
+          <t>Gradient AI</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Athena, S3, API Gateway, ECS, Databricks, Spark, Scala</t>
+          <t>AWS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6988d9d372dc66d3</t>
+          <t>https://www.indeed.com/viewjob?jk=08f4a08591f4e565</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Ripple</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, Athena, S3, API Gateway, ECS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30154588ed7f957f</t>
+          <t>https://www.indeed.com/viewjob?jk=6988d9d372dc66d3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Remote)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
+          <t>AWS, S3, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64eeda5b2dfcfe99</t>
+          <t>https://www.indeed.com/viewjob?jk=30154588ed7f957f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Machine Learning Engineer (Remote)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a077c257a4cf0b5</t>
+          <t>https://www.indeed.com/viewjob?jk=64eeda5b2dfcfe99</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Delta Live Tables, BigQuery, Spark, Snowflake, Databricks Lakehouse, ELT, dbt</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39ce7a464350b080</t>
+          <t>https://www.indeed.com/viewjob?jk=4a077c257a4cf0b5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
+          <t>Machine Learning Engineer (171679)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Eurest</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4699f552f08a017</t>
+          <t>https://www.indeed.com/viewjob?jk=7b373595b350ec3d</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Visualization Engineer</t>
+          <t>Solutions Architect III</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>IDEMIA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=867f580c7e3bb0e7</t>
+          <t>https://www.indeed.com/viewjob?jk=b223a04c01fe717f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Policy Configuration</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,112 +1676,112 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Databricks, Delta Live Tables, BigQuery, Spark, Snowflake, Databricks Lakehouse, ELT, dbt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1acf3efd34722f19</t>
+          <t>https://www.indeed.com/viewjob?jk=39ce7a464350b080</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Engineering Java/Python</t>
+          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Eurest</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ec8999487afb4f6</t>
+          <t>https://www.indeed.com/viewjob?jk=a4699f552f08a017</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer II 4P/554</t>
+          <t>Senior Software Engineer- Policy Configuration</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Oracle, SQL Server, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d963e021c819ac</t>
+          <t>https://www.indeed.com/viewjob?jk=1acf3efd34722f19</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, CRM</t>
+          <t>Senior Data Visualization Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
+          <t>Redshift, S3, RDS, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b266df7f25223b6</t>
+          <t>https://www.indeed.com/viewjob?jk=867f580c7e3bb0e7</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
+          <t>Software Engineer III - Data Engineering Java/Python</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Compass Group USA</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Hadoop, Spark, Snowflake, Oracle, PostgreSQL, MySQL</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65b5898fc3882a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=5ec8999487afb4f6</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Manufacturing Systems Integration Engineer</t>
+          <t>Data Engineer II 4P/554</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, Power BI, Docker, Kubernetes, Git</t>
+          <t>Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Oracle, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8532be76b040bdb</t>
+          <t>https://www.indeed.com/viewjob?jk=43d963e021c819ac</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr Advisor II, AI Architect</t>
+          <t>Senior Data Engineer, CRM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b85a978b0b96b10</t>
+          <t>https://www.indeed.com/viewjob?jk=7b266df7f25223b6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Compass Group USA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Redshift, RDS, BigQuery, Hadoop, Spark, Snowflake, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b11bc9d20fc1e2e2</t>
+          <t>https://www.indeed.com/viewjob?jk=65b5898fc3882a0c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Data Operations Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Geotab</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a6f623279ee6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd3315942275dbc</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Manufacturing Systems Integration Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, Power BI, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3cccca60e879db</t>
+          <t>https://www.indeed.com/viewjob?jk=d8532be76b040bdb</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Sr Advisor II, AI Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f821dc8a5f6559</t>
+          <t>https://www.indeed.com/viewjob?jk=1b85a978b0b96b10</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e6f7f78ae5d82f3</t>
+          <t>https://www.indeed.com/viewjob?jk=b11bc9d20fc1e2e2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3763de2ff690fcf</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a6f623279ee6d4</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3583ff1e8ab8b831</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3cccca60e879db</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dresher, PA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a764bcc9a479a693</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f821dc8a5f6559</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,14 +2211,14 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8b0a891a5da57c1</t>
+          <t>https://www.indeed.com/viewjob?jk=1e6f7f78ae5d82f3</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2246,14 +2246,14 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fdde135d701446e</t>
+          <t>https://www.indeed.com/viewjob?jk=e3763de2ff690fcf</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68e8fc35af3fc28f</t>
+          <t>https://www.indeed.com/viewjob?jk=3583ff1e8ab8b831</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>HealthMark Group</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dresher, PA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd869bd281c90f0</t>
+          <t>https://www.indeed.com/viewjob?jk=a764bcc9a479a693</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c10fe2dd154808d6</t>
+          <t>https://www.indeed.com/viewjob?jk=d8b0a891a5da57c1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Consultant - Cloud SRE Admin</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3dc8b002eb283aa</t>
+          <t>https://www.indeed.com/viewjob?jk=0fdde135d701446e</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MLOps Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4687b9b235a9a6ce</t>
+          <t>https://www.indeed.com/viewjob?jk=68e8fc35af3fc28f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Trepp</t>
+          <t>HealthMark Group</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd8df1b20c5849b</t>
+          <t>https://www.indeed.com/viewjob?jk=abd869bd281c90f0</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Upstream Oil &amp; Gas</t>
+          <t>Consultant - Cloud SRE Admin</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Crescent Energy</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=619ee2b50d37daac</t>
+          <t>https://www.indeed.com/viewjob?jk=f3dc8b002eb283aa</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II (Remote)</t>
+          <t>MLOps Platform Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, CI/CD, Git, Python, SQL, Java</t>
+          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd0ef78a415d3113</t>
+          <t>https://www.indeed.com/viewjob?jk=4687b9b235a9a6ce</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>Trepp</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Spark, Scala, CI/CD, Terraform, Git</t>
+          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7929c83226ae75b</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd8df1b20c5849b</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ML Support Engineer</t>
+          <t>Machine Learning Engineer II (Remote)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, CI/CD</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, CI/CD, Git, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4281d96efe6a7c5</t>
+          <t>https://www.indeed.com/viewjob?jk=dd0ef78a415d3113</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Spark, Scala, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62210abb12166a07</t>
+          <t>https://www.indeed.com/viewjob?jk=e7929c83226ae75b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>ML Support Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26a71508d797185b</t>
+          <t>https://www.indeed.com/viewjob?jk=a4281d96efe6a7c5</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Enterprise AI Architect</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=291c96af0e7cea02</t>
+          <t>https://www.indeed.com/viewjob?jk=62210abb12166a07</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer III - DevOps Automation Engineer</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58638a1a93a5925c</t>
+          <t>https://www.indeed.com/viewjob?jk=26a71508d797185b</t>
         </is>
       </c>
     </row>
@@ -2848,17 +2848,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Warehouse/BI Developer</t>
+          <t>Software Engineer III - DevOps Automation Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ThinkMirum, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe28e970e1130d6e</t>
+          <t>https://www.indeed.com/viewjob?jk=58638a1a93a5925c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Fullstack Software Engineer (Special Projects Team)</t>
+          <t>Enterprise AI Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Aeroflow Health</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Asheville, NC, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61e2c56fc5827763</t>
+          <t>https://www.indeed.com/viewjob?jk=291c96af0e7cea02</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-26.xlsx
+++ b/results/job_matches_2026-02-26.xlsx
@@ -1413,17 +1413,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Gradient AI</t>
+          <t>The Friedkin Group</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Dataflow, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08f4a08591f4e565</t>
+          <t>https://www.indeed.com/viewjob?jk=f7ede0f34ce25b71</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ripple</t>
+          <t>Gradient AI</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Athena, S3, API Gateway, ECS, Databricks, Spark, Scala</t>
+          <t>AWS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6988d9d372dc66d3</t>
+          <t>https://www.indeed.com/viewjob?jk=08f4a08591f4e565</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Ripple</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, Athena, S3, API Gateway, ECS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30154588ed7f957f</t>
+          <t>https://www.indeed.com/viewjob?jk=6988d9d372dc66d3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Remote)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
+          <t>AWS, S3, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64eeda5b2dfcfe99</t>
+          <t>https://www.indeed.com/viewjob?jk=30154588ed7f957f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Machine Learning Engineer (Remote)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a077c257a4cf0b5</t>
+          <t>https://www.indeed.com/viewjob?jk=64eeda5b2dfcfe99</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (171679)</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,17 +1606,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b373595b350ec3d</t>
+          <t>https://www.indeed.com/viewjob?jk=4a077c257a4cf0b5</t>
         </is>
       </c>
     </row>
@@ -1693,17 +1693,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
+          <t>Machine Learning Engineer (171679)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Eurest</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4699f552f08a017</t>
+          <t>https://www.indeed.com/viewjob?jk=7b373595b350ec3d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Policy Configuration</t>
+          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Eurest</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1acf3efd34722f19</t>
+          <t>https://www.indeed.com/viewjob?jk=a4699f552f08a017</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Visualization Engineer</t>
+          <t>Senior Software Engineer- Policy Configuration</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,69 +1781,69 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=867f580c7e3bb0e7</t>
+          <t>https://www.indeed.com/viewjob?jk=1acf3efd34722f19</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Engineering Java/Python</t>
+          <t>Senior Data Visualization Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
+          <t>Redshift, S3, RDS, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ec8999487afb4f6</t>
+          <t>https://www.indeed.com/viewjob?jk=867f580c7e3bb0e7</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer II 4P/554</t>
+          <t>Software Engineer III - Data Engineering Java/Python</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Oracle, SQL Server, NoSQL, Data Modeling</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d963e021c819ac</t>
+          <t>https://www.indeed.com/viewjob?jk=5ec8999487afb4f6</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, CRM</t>
+          <t>Data Engineer II 4P/554</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
+          <t>Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Oracle, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b266df7f25223b6</t>
+          <t>https://www.indeed.com/viewjob?jk=43d963e021c819ac</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
+          <t>Senior Data Engineer, CRM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Compass Group USA</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Hadoop, Spark, Snowflake, Oracle, PostgreSQL, MySQL</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65b5898fc3882a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=7b266df7f25223b6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Operations Developer</t>
+          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Geotab</t>
+          <t>Compass Group USA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, Redshift, RDS, BigQuery, Hadoop, Spark, Snowflake, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd3315942275dbc</t>
+          <t>https://www.indeed.com/viewjob?jk=65b5898fc3882a0c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Manufacturing Systems Integration Engineer</t>
+          <t>Data Operations Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>Geotab</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, Power BI, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8532be76b040bdb</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd3315942275dbc</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr Advisor II, AI Architect</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,17 +2026,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b85a978b0b96b10</t>
+          <t>https://www.indeed.com/viewjob?jk=b11bc9d20fc1e2e2</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b11bc9d20fc1e2e2</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a6f623279ee6d4</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a6f623279ee6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3cccca60e879db</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3cccca60e879db</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f821dc8a5f6559</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f821dc8a5f6559</t>
+          <t>https://www.indeed.com/viewjob?jk=1e6f7f78ae5d82f3</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e6f7f78ae5d82f3</t>
+          <t>https://www.indeed.com/viewjob?jk=e3763de2ff690fcf</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,14 +2246,14 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3763de2ff690fcf</t>
+          <t>https://www.indeed.com/viewjob?jk=3583ff1e8ab8b831</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Dresher, PA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3583ff1e8ab8b831</t>
+          <t>https://www.indeed.com/viewjob?jk=a764bcc9a479a693</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dresher, PA, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a764bcc9a479a693</t>
+          <t>https://www.indeed.com/viewjob?jk=d8b0a891a5da57c1</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8b0a891a5da57c1</t>
+          <t>https://www.indeed.com/viewjob?jk=0fdde135d701446e</t>
         </is>
       </c>
     </row>
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fdde135d701446e</t>
+          <t>https://www.indeed.com/viewjob?jk=68e8fc35af3fc28f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>HealthMark Group</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68e8fc35af3fc28f</t>
+          <t>https://www.indeed.com/viewjob?jk=abd869bd281c90f0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Manufacturing Systems Integration Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>HealthMark Group</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, Power BI, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd869bd281c90f0</t>
+          <t>https://www.indeed.com/viewjob?jk=d8532be76b040bdb</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Consultant - Cloud SRE Admin</t>
+          <t>Sr Advisor II, AI Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3dc8b002eb283aa</t>
+          <t>https://www.indeed.com/viewjob?jk=1b85a978b0b96b10</t>
         </is>
       </c>
     </row>
@@ -2638,17 +2638,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ML Support Engineer</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,17 +2656,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4281d96efe6a7c5</t>
+          <t>https://www.indeed.com/viewjob?jk=62210abb12166a07</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62210abb12166a07</t>
+          <t>https://www.indeed.com/viewjob?jk=26a71508d797185b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Teradata Developer-5</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26a71508d797185b</t>
+          <t>https://www.indeed.com/viewjob?jk=6f4f91dff933f5cc</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Teradata Developer-5</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>NiyamIT</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f4f91dff933f5cc</t>
+          <t>https://www.indeed.com/viewjob?jk=1a1802cfcb8371e8</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>[CoreIgnite] Senior Java Developer (AWS) - Shashank Srivastava</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NiyamIT</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
+          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a1802cfcb8371e8</t>
+          <t>https://www.indeed.com/viewjob?jk=0866a4d4cc7dec0c</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>[CoreIgnite] Senior Java Developer (AWS) - Shashank Srivastava</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0866a4d4cc7dec0c</t>
+          <t>https://www.indeed.com/viewjob?jk=503269b060f28151</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer III - DevOps Automation Engineer</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58638a1a93a5925c</t>
+          <t>https://www.indeed.com/viewjob?jk=dbeb792ea58b7a87</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Enterprise AI Architect</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,14 +2911,14 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=291c96af0e7cea02</t>
+          <t>https://www.indeed.com/viewjob?jk=fd899ffea8f1b74c</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2946,14 +2946,14 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503269b060f28151</t>
+          <t>https://www.indeed.com/viewjob?jk=f22565dd904e0808</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2981,14 +2981,14 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbeb792ea58b7a87</t>
+          <t>https://www.indeed.com/viewjob?jk=f8fcbfbc5352b0bf</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,14 +3016,14 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd899ffea8f1b74c</t>
+          <t>https://www.indeed.com/viewjob?jk=d1da94812ec374b4</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,14 +3051,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f22565dd904e0808</t>
+          <t>https://www.indeed.com/viewjob?jk=ee5cdada52faf29e</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3086,14 +3086,14 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8fcbfbc5352b0bf</t>
+          <t>https://www.indeed.com/viewjob?jk=5676e61db2aa81f3</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,14 +3121,14 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1da94812ec374b4</t>
+          <t>https://www.indeed.com/viewjob?jk=de6aa6e4975245c5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,24 +3146,24 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee5cdada52faf29e</t>
+          <t>https://www.indeed.com/viewjob?jk=e73fae08616e3afd</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5676e61db2aa81f3</t>
+          <t>https://www.indeed.com/viewjob?jk=2cdec8d2c07ce6a8</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Software Engineer III - DevOps Automation Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de6aa6e4975245c5</t>
+          <t>https://www.indeed.com/viewjob?jk=58638a1a93a5925c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+          <t>Enterprise AI Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73fae08616e3afd</t>
+          <t>https://www.indeed.com/viewjob?jk=291c96af0e7cea02</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Matrix Medical Network</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,17 +3286,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cdec8d2c07ce6a8</t>
+          <t>https://www.indeed.com/viewjob?jk=939ed479d96c418b</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-26.xlsx
+++ b/results/job_matches_2026-02-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (React + Node.js)</t>
+          <t>Senior Consultant - Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Torq</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.1</v>
+        <v>21.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, BigQuery, Scala, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,102 +496,102 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35decd7954b0dd0a</t>
+          <t>https://www.indeed.com/viewjob?jk=5c9f68666dbb80cd</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Ops Engineer</t>
+          <t>Sr. Solution Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Shamrock Trading Corporation</t>
+          <t>Associated Wholesale Grocers</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Databricks, Unity Catalog, Spark</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=325e4219bc2f7757</t>
+          <t>https://www.indeed.com/viewjob?jk=3d4780af39e79827</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineering III</t>
+          <t>Full Stack Engineer (React + Node.js)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Equitable</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Flume, Zookeeper</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1753914a33e85905</t>
+          <t>https://www.indeed.com/viewjob?jk=35decd7954b0dd0a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote in CA)</t>
+          <t>Data Ops Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>First American</t>
+          <t>Shamrock Trading Corporation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>19.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Databricks, Unity Catalog, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05ccb57abd2eb2be</t>
+          <t>https://www.indeed.com/viewjob?jk=325e4219bc2f7757</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Advisor II, Data Architect</t>
+          <t>Software Engineering III</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Equitable</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Flume, Zookeeper</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21bd27b152469170</t>
+          <t>https://www.indeed.com/viewjob?jk=1753914a33e85905</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Senior Data Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Disney Entertainment Television</t>
+          <t>First American</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, ECS, RDS, Databricks, BigQuery, Vertex AI, Spark, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c7525b9f402e34</t>
+          <t>https://www.indeed.com/viewjob?jk=05ccb57abd2eb2be</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Senior Advisor II, Data Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, ECS, RDS, Databricks, BigQuery, Vertex AI, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15f2e018b3b0d55e</t>
+          <t>https://www.indeed.com/viewjob?jk=21bd27b152469170</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SolidLine Media</t>
+          <t>Disney Entertainment Television</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Kinesis, ECS, RDS, Databricks, BigQuery, Vertex AI, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e8185f66fc8c270</t>
+          <t>https://www.indeed.com/viewjob?jk=06c7525b9f402e34</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, SQL, AWS) - Navigator Platform</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Kinesis, ECS, RDS, Databricks, BigQuery, Vertex AI, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38b02b46801c7f10</t>
+          <t>https://www.indeed.com/viewjob?jk=15f2e018b3b0d55e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef8a3d8ad1cf49b7</t>
+          <t>https://www.indeed.com/viewjob?jk=fc1052fb6437c3a3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>American Family Insurance</t>
+          <t>SolidLine Media</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c5e79cbd14d908</t>
+          <t>https://www.indeed.com/viewjob?jk=8e8185f66fc8c270</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Data Engineer (Python, SQL, AWS) - Navigator Platform</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e89cb44acf96f0ce</t>
+          <t>https://www.indeed.com/viewjob?jk=38b02b46801c7f10</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer - Boston</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9b3e4586db8c7fd</t>
+          <t>https://www.indeed.com/viewjob?jk=ef8a3d8ad1cf49b7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>American Family Insurance</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d7b87445d04d0bb</t>
+          <t>https://www.indeed.com/viewjob?jk=54c5e79cbd14d908</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer II (USA)</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,102 +986,102 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=079fa62336e07385</t>
+          <t>https://www.indeed.com/viewjob?jk=e89cb44acf96f0ce</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-5</t>
+          <t>Data Engineer - Boston</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=656bcb1553978517</t>
+          <t>https://www.indeed.com/viewjob?jk=b9b3e4586db8c7fd</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Azure Data Engineer I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Premise Health</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ELT, Talend</t>
+          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=353cdf1ee00c6fd9</t>
+          <t>https://www.indeed.com/viewjob?jk=2d7b87445d04d0bb</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Ops Engineer</t>
+          <t>Software Engineer II (USA)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MLOps, MLflow, CI/CD</t>
+          <t>AWS, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8203af416f8f7f</t>
+          <t>https://www.indeed.com/viewjob?jk=079fa62336e07385</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Databricks Developer-5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SRS Distribution</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9fcb451d7086751</t>
+          <t>https://www.indeed.com/viewjob?jk=656bcb1553978517</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Data Engineer I</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GovWorx</t>
+          <t>Premise Health</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Spark, PySpark, Scala, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ELT, Talend</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,59 +1161,59 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ee6445287271c9d</t>
+          <t>https://www.indeed.com/viewjob?jk=353cdf1ee00c6fd9</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Distinguished Engineer</t>
+          <t>Senior Machine Learning Ops Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Cassandra, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab3a4b9f2c783845</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8203af416f8f7f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Remote)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Inspira Financial</t>
+          <t>SRS Distribution</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03f6284daa41bb63</t>
+          <t>https://www.indeed.com/viewjob?jk=e9fcb451d7086751</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>GovWorx</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Spark, PySpark, Scala, MySQL, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b57d55c8e2a74923</t>
+          <t>https://www.indeed.com/viewjob?jk=8ee6445287271c9d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Application Developer III, Platform Engineering</t>
+          <t>Distinguished Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Herbalife</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Torrance, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,42 +1291,42 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Cassandra, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116acc2ab05b269d</t>
+          <t>https://www.indeed.com/viewjob?jk=ab3a4b9f2c783845</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Application Developer III, Platform Engineering</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ramsey Solutions</t>
+          <t>Herbalife</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Torrance, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba46b1aa50f7279f</t>
+          <t>https://www.indeed.com/viewjob?jk=116acc2ab05b269d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Inspira Financial</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, PostgreSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=693f3e0a054607b0</t>
+          <t>https://www.indeed.com/viewjob?jk=03f6284daa41bb63</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Solution Engineer I</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Associated Wholesale Grocers</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,67 +1406,67 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5985bee213bf40</t>
+          <t>https://www.indeed.com/viewjob?jk=b57d55c8e2a74923</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The Friedkin Group</t>
+          <t>Ramsey Solutions</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Dataflow, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7ede0f34ce25b71</t>
+          <t>https://www.indeed.com/viewjob?jk=ba46b1aa50f7279f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Gradient AI</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, PostgreSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08f4a08591f4e565</t>
+          <t>https://www.indeed.com/viewjob?jk=693f3e0a054607b0</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Solution Engineer I</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ripple</t>
+          <t>Associated Wholesale Grocers</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Athena, S3, API Gateway, ECS, Databricks, Spark, Scala</t>
+          <t>AWS, Redshift, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6988d9d372dc66d3</t>
+          <t>https://www.indeed.com/viewjob?jk=5e5985bee213bf40</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>The Friedkin Group</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Dataflow, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30154588ed7f957f</t>
+          <t>https://www.indeed.com/viewjob?jk=f7ede0f34ce25b71</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Gradient AI</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
+          <t>AWS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64eeda5b2dfcfe99</t>
+          <t>https://www.indeed.com/viewjob?jk=08f4a08591f4e565</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Ripple</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Kinesis, Athena, S3, API Gateway, ECS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a077c257a4cf0b5</t>
+          <t>https://www.indeed.com/viewjob?jk=6988d9d372dc66d3</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Solutions Architect III</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>IDEMIA</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, S3, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b223a04c01fe717f</t>
+          <t>https://www.indeed.com/viewjob?jk=30154588ed7f957f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Machine Learning Engineer (Remote)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Delta Live Tables, BigQuery, Spark, Snowflake, Databricks Lakehouse, ELT, dbt</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39ce7a464350b080</t>
+          <t>https://www.indeed.com/viewjob?jk=64eeda5b2dfcfe99</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (171679)</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b373595b350ec3d</t>
+          <t>https://www.indeed.com/viewjob?jk=4a077c257a4cf0b5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
+          <t>Solutions Architect III</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Eurest</t>
+          <t>IDEMIA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4699f552f08a017</t>
+          <t>https://www.indeed.com/viewjob?jk=b223a04c01fe717f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Policy Configuration</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Databricks, Delta Live Tables, BigQuery, Spark, Snowflake, Databricks Lakehouse, ELT, dbt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1acf3efd34722f19</t>
+          <t>https://www.indeed.com/viewjob?jk=39ce7a464350b080</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Visualization Engineer</t>
+          <t>Senior Software Engineer- Policy Configuration</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,112 +1816,112 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=867f580c7e3bb0e7</t>
+          <t>https://www.indeed.com/viewjob?jk=1acf3efd34722f19</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Engineering Java/Python</t>
+          <t>Machine Learning Engineer (171679)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ec8999487afb4f6</t>
+          <t>https://www.indeed.com/viewjob?jk=7b373595b350ec3d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer II 4P/554</t>
+          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>Eurest</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Oracle, SQL Server, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d963e021c819ac</t>
+          <t>https://www.indeed.com/viewjob?jk=a4699f552f08a017</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, CRM</t>
+          <t>Senior Data Visualization Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
+          <t>Redshift, S3, RDS, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b266df7f25223b6</t>
+          <t>https://www.indeed.com/viewjob?jk=867f580c7e3bb0e7</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
+          <t>Software Engineer III - Data Engineering Java/Python</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Compass Group USA</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Hadoop, Spark, Snowflake, Oracle, PostgreSQL, MySQL</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65b5898fc3882a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=5ec8999487afb4f6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Operations Developer</t>
+          <t>Data Engineer II 4P/554</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Geotab</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, CI/CD, Airflow</t>
+          <t>Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Oracle, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd3315942275dbc</t>
+          <t>https://www.indeed.com/viewjob?jk=43d963e021c819ac</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Senior Data Engineer, CRM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b11bc9d20fc1e2e2</t>
+          <t>https://www.indeed.com/viewjob?jk=7b266df7f25223b6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Senior Backend Software Engineer (HPC/AI &amp; Distributed Systems)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a6f623279ee6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=dce54831329652c4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Compass Group USA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,17 +2096,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Redshift, RDS, BigQuery, Hadoop, Spark, Snowflake, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3cccca60e879db</t>
+          <t>https://www.indeed.com/viewjob?jk=65b5898fc3882a0c</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f821dc8a5f6559</t>
+          <t>https://www.indeed.com/viewjob?jk=b11bc9d20fc1e2e2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e6f7f78ae5d82f3</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a6f623279ee6d4</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3763de2ff690fcf</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3cccca60e879db</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3583ff1e8ab8b831</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f821dc8a5f6559</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dresher, PA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,14 +2281,14 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a764bcc9a479a693</t>
+          <t>https://www.indeed.com/viewjob?jk=1e6f7f78ae5d82f3</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,14 +2316,14 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8b0a891a5da57c1</t>
+          <t>https://www.indeed.com/viewjob?jk=e3763de2ff690fcf</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fdde135d701446e</t>
+          <t>https://www.indeed.com/viewjob?jk=3583ff1e8ab8b831</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dresher, PA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68e8fc35af3fc28f</t>
+          <t>https://www.indeed.com/viewjob?jk=a764bcc9a479a693</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>HealthMark Group</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd869bd281c90f0</t>
+          <t>https://www.indeed.com/viewjob?jk=d8b0a891a5da57c1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Manufacturing Systems Integration Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, Power BI, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8532be76b040bdb</t>
+          <t>https://www.indeed.com/viewjob?jk=0fdde135d701446e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr Advisor II, AI Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b85a978b0b96b10</t>
+          <t>https://www.indeed.com/viewjob?jk=68e8fc35af3fc28f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MLOps Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>HealthMark Group</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,102 +2526,102 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4687b9b235a9a6ce</t>
+          <t>https://www.indeed.com/viewjob?jk=abd869bd281c90f0</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Operations Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Trepp</t>
+          <t>Geotab</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd8df1b20c5849b</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd3315942275dbc</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II (Remote)</t>
+          <t>Manufacturing Systems Integration Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, CI/CD, Git, Python, SQL, Java</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, Power BI, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd0ef78a415d3113</t>
+          <t>https://www.indeed.com/viewjob?jk=d8532be76b040bdb</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr Advisor II, AI Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Spark, Scala, CI/CD, Terraform, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7929c83226ae75b</t>
+          <t>https://www.indeed.com/viewjob?jk=1b85a978b0b96b10</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>MLOps Platform Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
+          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62210abb12166a07</t>
+          <t>https://www.indeed.com/viewjob?jk=4687b9b235a9a6ce</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Trepp</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
+          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26a71508d797185b</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd8df1b20c5849b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Teradata Developer-5</t>
+          <t>Machine Learning Engineer II (Remote)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, CI/CD, Git, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f4f91dff933f5cc</t>
+          <t>https://www.indeed.com/viewjob?jk=dd0ef78a415d3113</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NiyamIT</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Spark, Scala, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a1802cfcb8371e8</t>
+          <t>https://www.indeed.com/viewjob?jk=e7929c83226ae75b</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>[CoreIgnite] Senior Java Developer (AWS) - Shashank Srivastava</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Kafka, PostgreSQL, MongoDB, ETL, CI/CD, Terraform</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0866a4d4cc7dec0c</t>
+          <t>https://www.indeed.com/viewjob?jk=62210abb12166a07</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503269b060f28151</t>
+          <t>https://www.indeed.com/viewjob?jk=26a71508d797185b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,14 +2876,14 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbeb792ea58b7a87</t>
+          <t>https://www.indeed.com/viewjob?jk=bc8599dc51df5400</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd899ffea8f1b74c</t>
+          <t>https://www.indeed.com/viewjob?jk=503269b060f28151</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,14 +2946,14 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f22565dd904e0808</t>
+          <t>https://www.indeed.com/viewjob?jk=dbeb792ea58b7a87</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,14 +2981,14 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8fcbfbc5352b0bf</t>
+          <t>https://www.indeed.com/viewjob?jk=fd899ffea8f1b74c</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,14 +3016,14 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1da94812ec374b4</t>
+          <t>https://www.indeed.com/viewjob?jk=f22565dd904e0808</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,14 +3051,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee5cdada52faf29e</t>
+          <t>https://www.indeed.com/viewjob?jk=f8fcbfbc5352b0bf</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,14 +3086,14 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5676e61db2aa81f3</t>
+          <t>https://www.indeed.com/viewjob?jk=d1da94812ec374b4</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,14 +3121,14 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de6aa6e4975245c5</t>
+          <t>https://www.indeed.com/viewjob?jk=ee5cdada52faf29e</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,24 +3146,24 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73fae08616e3afd</t>
+          <t>https://www.indeed.com/viewjob?jk=5676e61db2aa81f3</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cdec8d2c07ce6a8</t>
+          <t>https://www.indeed.com/viewjob?jk=de6aa6e4975245c5</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer III - DevOps Automation Engineer</t>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58638a1a93a5925c</t>
+          <t>https://www.indeed.com/viewjob?jk=e73fae08616e3afd</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Enterprise AI Architect</t>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=291c96af0e7cea02</t>
+          <t>https://www.indeed.com/viewjob?jk=2cdec8d2c07ce6a8</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Matrix Medical Network</t>
+          <t>University of Texas Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,15 +3286,225 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6fff225f154716cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Teradata Developer-5</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f4f91dff933f5cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>NiyamIT</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ashburn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a1802cfcb8371e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Software Engineer III - DevOps Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=58638a1a93a5925c</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Enterprise AI Architect</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Radwell International</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Willingboro, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=291c96af0e7cea02</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>(Remote) Fullstack Software Engineer (Special Projects Team)</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Aeroflow Health</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Asheville, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, DynamoDB, CI/CD</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61e2c56fc5827763</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Matrix Medical Network</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>2026-01-29</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=939ed479d96c418b</t>
         </is>

--- a/results/job_matches_2026-02-26.xlsx
+++ b/results/job_matches_2026-02-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Ops Engineer</t>
+          <t>Software Engineering III</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Shamrock Trading Corporation</t>
+          <t>Equitable</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Databricks, Unity Catalog, Spark</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Flume, Zookeeper</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=325e4219bc2f7757</t>
+          <t>https://www.indeed.com/viewjob?jk=1753914a33e85905</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineering III</t>
+          <t>Senior Data Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Equitable</t>
+          <t>First American</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Flume, Zookeeper</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1753914a33e85905</t>
+          <t>https://www.indeed.com/viewjob?jk=05ccb57abd2eb2be</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote in CA)</t>
+          <t>Senior Advisor II, Data Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>First American</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05ccb57abd2eb2be</t>
+          <t>https://www.indeed.com/viewjob?jk=21bd27b152469170</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Advisor II, Data Architect</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Disney Entertainment Television</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,17 +696,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, Kinesis, ECS, RDS, Databricks, BigQuery, Vertex AI, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21bd27b152469170</t>
+          <t>https://www.indeed.com/viewjob?jk=06c7525b9f402e34</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Disney Entertainment Television</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -736,64 +736,64 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c7525b9f402e34</t>
+          <t>https://www.indeed.com/viewjob?jk=15f2e018b3b0d55e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, ECS, RDS, Databricks, BigQuery, Vertex AI, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15f2e018b3b0d55e</t>
+          <t>https://www.indeed.com/viewjob?jk=fc1052fb6437c3a3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SolidLine Media</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc1052fb6437c3a3</t>
+          <t>https://www.indeed.com/viewjob?jk=8e8185f66fc8c270</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Python, SQL, AWS) - Navigator Platform</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SolidLine Media</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,24 +836,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e8185f66fc8c270</t>
+          <t>https://www.indeed.com/viewjob?jk=38b02b46801c7f10</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, SQL, AWS) - Navigator Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38b02b46801c7f10</t>
+          <t>https://www.indeed.com/viewjob?jk=ef8a3d8ad1cf49b7</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>American Family Insurance</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef8a3d8ad1cf49b7</t>
+          <t>https://www.indeed.com/viewjob?jk=54c5e79cbd14d908</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>American Family Insurance</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c5e79cbd14d908</t>
+          <t>https://www.indeed.com/viewjob?jk=e89cb44acf96f0ce</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Data Engineer - Boston</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e89cb44acf96f0ce</t>
+          <t>https://www.indeed.com/viewjob?jk=b9b3e4586db8c7fd</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer - Boston</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9b3e4586db8c7fd</t>
+          <t>https://www.indeed.com/viewjob?jk=2d7b87445d04d0bb</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II (USA)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,69 +1046,69 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
+          <t>AWS, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d7b87445d04d0bb</t>
+          <t>https://www.indeed.com/viewjob?jk=079fa62336e07385</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer II (USA)</t>
+          <t>Senior Databricks Developer-5</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=079fa62336e07385</t>
+          <t>https://www.indeed.com/viewjob?jk=656bcb1553978517</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-5</t>
+          <t>Azure Data Engineer I</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Premise Health</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ELT, Talend</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=656bcb1553978517</t>
+          <t>https://www.indeed.com/viewjob?jk=353cdf1ee00c6fd9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Azure Data Engineer I</t>
+          <t>Senior Machine Learning Ops Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Premise Health</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ELT, Talend</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,59 +1161,59 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=353cdf1ee00c6fd9</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8203af416f8f7f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Ops Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>SRS Distribution</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8203af416f8f7f</t>
+          <t>https://www.indeed.com/viewjob?jk=e9fcb451d7086751</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SRS Distribution</t>
+          <t>GovWorx</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Spark, PySpark, Scala, MySQL, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9fcb451d7086751</t>
+          <t>https://www.indeed.com/viewjob?jk=8ee6445287271c9d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Distinguished Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GovWorx</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Spark, PySpark, Scala, MySQL, ETL</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Cassandra, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ee6445287271c9d</t>
+          <t>https://www.indeed.com/viewjob?jk=ab3a4b9f2c783845</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Distinguished Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Cassandra, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab3a4b9f2c783845</t>
+          <t>https://www.indeed.com/viewjob?jk=b57d55c8e2a74923</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Application Developer III, Platform Engineering</t>
+          <t>Sr. Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Herbalife</t>
+          <t>Inspira Financial</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Torrance, CA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116acc2ab05b269d</t>
+          <t>https://www.indeed.com/viewjob?jk=03f6284daa41bb63</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Remote)</t>
+          <t>Application Developer III, Platform Engineering</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Inspira Financial</t>
+          <t>Herbalife</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Torrance, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,42 +1361,42 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03f6284daa41bb63</t>
+          <t>https://www.indeed.com/viewjob?jk=116acc2ab05b269d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Ramsey Solutions</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b57d55c8e2a74923</t>
+          <t>https://www.indeed.com/viewjob?jk=ba46b1aa50f7279f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ramsey Solutions</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, PostgreSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba46b1aa50f7279f</t>
+          <t>https://www.indeed.com/viewjob?jk=693f3e0a054607b0</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solution Engineer I</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Associated Wholesale Grocers</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, PostgreSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,59 +1476,59 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=693f3e0a054607b0</t>
+          <t>https://www.indeed.com/viewjob?jk=5e5985bee213bf40</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Solution Engineer I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Associated Wholesale Grocers</t>
+          <t>The Friedkin Group</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Dataflow, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5985bee213bf40</t>
+          <t>https://www.indeed.com/viewjob?jk=f7ede0f34ce25b71</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>The Friedkin Group</t>
+          <t>Gradient AI</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Dataflow, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7ede0f34ce25b71</t>
+          <t>https://www.indeed.com/viewjob?jk=08f4a08591f4e565</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Gradient AI</t>
+          <t>Ripple</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Kinesis, Athena, S3, API Gateway, ECS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08f4a08591f4e565</t>
+          <t>https://www.indeed.com/viewjob?jk=6988d9d372dc66d3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ripple</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Athena, S3, API Gateway, ECS, Databricks, Spark, Scala</t>
+          <t>AWS, S3, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6988d9d372dc66d3</t>
+          <t>https://www.indeed.com/viewjob?jk=30154588ed7f957f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Machine Learning Engineer (Remote)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30154588ed7f957f</t>
+          <t>https://www.indeed.com/viewjob?jk=64eeda5b2dfcfe99</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Remote)</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64eeda5b2dfcfe99</t>
+          <t>https://www.indeed.com/viewjob?jk=4a077c257a4cf0b5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Solutions Architect III</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>IDEMIA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,29 +1711,29 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a077c257a4cf0b5</t>
+          <t>https://www.indeed.com/viewjob?jk=b223a04c01fe717f</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Solutions Architect III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>IDEMIA</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, RDS, Databricks, Delta Live Tables, BigQuery, Spark, Snowflake, Databricks Lakehouse, ELT, dbt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b223a04c01fe717f</t>
+          <t>https://www.indeed.com/viewjob?jk=39ce7a464350b080</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer- Policy Configuration</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Delta Live Tables, BigQuery, Spark, Snowflake, Databricks Lakehouse, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39ce7a464350b080</t>
+          <t>https://www.indeed.com/viewjob?jk=1acf3efd34722f19</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Policy Configuration</t>
+          <t>Machine Learning Engineer (171679)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1acf3efd34722f19</t>
+          <t>https://www.indeed.com/viewjob?jk=7b373595b350ec3d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (171679)</t>
+          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Eurest</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b373595b350ec3d</t>
+          <t>https://www.indeed.com/viewjob?jk=a4699f552f08a017</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
+          <t>Senior Data Visualization Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Eurest</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,69 +1886,69 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>Redshift, S3, RDS, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4699f552f08a017</t>
+          <t>https://www.indeed.com/viewjob?jk=867f580c7e3bb0e7</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Visualization Engineer</t>
+          <t>Software Engineer III - Data Engineering Java/Python</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=867f580c7e3bb0e7</t>
+          <t>https://www.indeed.com/viewjob?jk=5ec8999487afb4f6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Engineering Java/Python</t>
+          <t>Data Engineer II 4P/554</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Oracle, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ec8999487afb4f6</t>
+          <t>https://www.indeed.com/viewjob?jk=43d963e021c819ac</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer II 4P/554</t>
+          <t>Senior Data Engineer, CRM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Oracle, SQL Server, NoSQL, Data Modeling</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d963e021c819ac</t>
+          <t>https://www.indeed.com/viewjob?jk=7b266df7f25223b6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, CRM</t>
+          <t>Senior Backend Software Engineer (HPC/AI &amp; Distributed Systems)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b266df7f25223b6</t>
+          <t>https://www.indeed.com/viewjob?jk=dce54831329652c4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer (HPC/AI &amp; Distributed Systems)</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dce54831329652c4</t>
+          <t>https://www.indeed.com/viewjob?jk=b11bc9d20fc1e2e2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SR. DATA ENGINEER THREAT MANAGEMENT DATA &amp; ANALYTICS (HYBRID-CHARLOTTE, NC)</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Compass Group USA</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,17 +2096,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Hadoop, Spark, Snowflake, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65b5898fc3882a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a6f623279ee6d4</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b11bc9d20fc1e2e2</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3cccca60e879db</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a6f623279ee6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f821dc8a5f6559</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Full Stack Engineer, Consultant</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3cccca60e879db</t>
+          <t>https://www.indeed.com/viewjob?jk=1e6f7f78ae5d82f3</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f821dc8a5f6559</t>
+          <t>https://www.indeed.com/viewjob?jk=e3763de2ff690fcf</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,14 +2281,14 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e6f7f78ae5d82f3</t>
+          <t>https://www.indeed.com/viewjob?jk=3583ff1e8ab8b831</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dresher, PA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,14 +2316,14 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3763de2ff690fcf</t>
+          <t>https://www.indeed.com/viewjob?jk=a764bcc9a479a693</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3583ff1e8ab8b831</t>
+          <t>https://www.indeed.com/viewjob?jk=d8b0a891a5da57c1</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dresher, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a764bcc9a479a693</t>
+          <t>https://www.indeed.com/viewjob?jk=0fdde135d701446e</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8b0a891a5da57c1</t>
+          <t>https://www.indeed.com/viewjob?jk=68e8fc35af3fc28f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>HealthMark Group</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fdde135d701446e</t>
+          <t>https://www.indeed.com/viewjob?jk=abd869bd281c90f0</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Manufacturing Systems Integration Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, Power BI, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68e8fc35af3fc28f</t>
+          <t>https://www.indeed.com/viewjob?jk=d8532be76b040bdb</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Advisor II, AI Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>HealthMark Group</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd869bd281c90f0</t>
+          <t>https://www.indeed.com/viewjob?jk=1b85a978b0b96b10</t>
         </is>
       </c>
     </row>
@@ -2568,60 +2568,60 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Manufacturing Systems Integration Engineer</t>
+          <t>Data Engineer - II</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>CINC</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, Power BI, Docker, Kubernetes, Git</t>
+          <t>AWS, Kinesis, Redshift, ECS, Scala, Kafka, DynamoDB, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8532be76b040bdb</t>
+          <t>https://www.indeed.com/viewjob?jk=32c97e76b6269664</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr Advisor II, AI Architect</t>
+          <t>MLOps Platform Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b85a978b0b96b10</t>
+          <t>https://www.indeed.com/viewjob?jk=4687b9b235a9a6ce</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MLOps Platform Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Trepp</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4687b9b235a9a6ce</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd8df1b20c5849b</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Machine Learning Engineer II (Remote)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Trepp</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, CI/CD, Git, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd8df1b20c5849b</t>
+          <t>https://www.indeed.com/viewjob?jk=dd0ef78a415d3113</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II (Remote)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, CI/CD, Git, Python, SQL, Java</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Spark, Scala, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd0ef78a415d3113</t>
+          <t>https://www.indeed.com/viewjob?jk=e7929c83226ae75b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,17 +2761,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Spark, Scala, CI/CD, Terraform, Git</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7929c83226ae75b</t>
+          <t>https://www.indeed.com/viewjob?jk=62210abb12166a07</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62210abb12166a07</t>
+          <t>https://www.indeed.com/viewjob?jk=26a71508d797185b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
+          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26a71508d797185b</t>
+          <t>https://www.indeed.com/viewjob?jk=bc8599dc51df5400</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,14 +2876,14 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc8599dc51df5400</t>
+          <t>https://www.indeed.com/viewjob?jk=503269b060f28151</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,14 +2911,14 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503269b060f28151</t>
+          <t>https://www.indeed.com/viewjob?jk=dbeb792ea58b7a87</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,14 +2946,14 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbeb792ea58b7a87</t>
+          <t>https://www.indeed.com/viewjob?jk=fd899ffea8f1b74c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,14 +2981,14 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd899ffea8f1b74c</t>
+          <t>https://www.indeed.com/viewjob?jk=f22565dd904e0808</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,14 +3016,14 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f22565dd904e0808</t>
+          <t>https://www.indeed.com/viewjob?jk=f8fcbfbc5352b0bf</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,14 +3051,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8fcbfbc5352b0bf</t>
+          <t>https://www.indeed.com/viewjob?jk=d1da94812ec374b4</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3086,14 +3086,14 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1da94812ec374b4</t>
+          <t>https://www.indeed.com/viewjob?jk=ee5cdada52faf29e</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,14 +3121,14 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee5cdada52faf29e</t>
+          <t>https://www.indeed.com/viewjob?jk=5676e61db2aa81f3</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,14 +3156,14 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5676e61db2aa81f3</t>
+          <t>https://www.indeed.com/viewjob?jk=de6aa6e4975245c5</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,17 +3181,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de6aa6e4975245c5</t>
+          <t>https://www.indeed.com/viewjob?jk=e73fae08616e3afd</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73fae08616e3afd</t>
+          <t>https://www.indeed.com/viewjob?jk=2cdec8d2c07ce6a8</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+          <t>Software Engineer III - DevOps Automation Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cdec8d2c07ce6a8</t>
+          <t>https://www.indeed.com/viewjob?jk=58638a1a93a5925c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
+          <t>Enterprise AI Architect</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>University of Texas Health Science Center at San Antonio</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fff225f154716cc</t>
+          <t>https://www.indeed.com/viewjob?jk=291c96af0e7cea02</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Teradata Developer-5</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>University of Texas Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f4f91dff933f5cc</t>
+          <t>https://www.indeed.com/viewjob?jk=6fff225f154716cc</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Teradata Developer-5</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>NiyamIT</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a1802cfcb8371e8</t>
+          <t>https://www.indeed.com/viewjob?jk=6f4f91dff933f5cc</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer III - DevOps Automation Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NiyamIT</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58638a1a93a5925c</t>
+          <t>https://www.indeed.com/viewjob?jk=1a1802cfcb8371e8</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Enterprise AI Architect</t>
+          <t>(Remote) Fullstack Software Engineer (Special Projects Team)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>Aeroflow Health</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Asheville, NC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=291c96af0e7cea02</t>
+          <t>https://www.indeed.com/viewjob?jk=61e2c56fc5827763</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>(Remote) Fullstack Software Engineer (Special Projects Team)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Aeroflow Health</t>
+          <t>Matrix Medical Network</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Asheville, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,50 +3461,15 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=61e2c56fc5827763</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Matrix Medical Network</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-01-29</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=939ed479d96c418b</t>
         </is>

--- a/results/job_matches_2026-02-26.xlsx
+++ b/results/job_matches_2026-02-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Application Developer III, Platform Engineering</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Herbalife</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Torrance, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b57d55c8e2a74923</t>
+          <t>https://www.indeed.com/viewjob?jk=116acc2ab05b269d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Remote)</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Inspira Financial</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,104 +1326,104 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03f6284daa41bb63</t>
+          <t>https://www.indeed.com/viewjob?jk=b57d55c8e2a74923</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Application Developer III, Platform Engineering</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Herbalife</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Torrance, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Cloud Storage, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116acc2ab05b269d</t>
+          <t>https://www.indeed.com/viewjob?jk=79a97f6710d73548</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ramsey Solutions</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, Scala, Power BI, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba46b1aa50f7279f</t>
+          <t>https://www.indeed.com/viewjob?jk=b5df4e674559910e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Ramsey Solutions</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, PostgreSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=693f3e0a054607b0</t>
+          <t>https://www.indeed.com/viewjob?jk=ba46b1aa50f7279f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Solution Engineer I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Associated Wholesale Grocers</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, PostgreSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,94 +1476,94 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5985bee213bf40</t>
+          <t>https://www.indeed.com/viewjob?jk=693f3e0a054607b0</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solution Engineer I</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The Friedkin Group</t>
+          <t>Associated Wholesale Grocers</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Dataflow, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7ede0f34ce25b71</t>
+          <t>https://www.indeed.com/viewjob?jk=5e5985bee213bf40</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Gradient AI</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Terraform</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08f4a08591f4e565</t>
+          <t>https://www.indeed.com/viewjob?jk=1b7f8d62e370d21c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ripple</t>
+          <t>The Friedkin Group</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Athena, S3, API Gateway, ECS, Databricks, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Dataflow, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6988d9d372dc66d3</t>
+          <t>https://www.indeed.com/viewjob?jk=f7ede0f34ce25b71</t>
         </is>
       </c>
     </row>
@@ -1693,17 +1693,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Solutions Architect III</t>
+          <t>Senior Engineer - Wire Payments Platform</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>IDEMIA</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,29 +1711,29 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b223a04c01fe717f</t>
+          <t>https://www.indeed.com/viewjob?jk=55c16c38ef65d0c6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solutions Architect III</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>IDEMIA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Delta Live Tables, BigQuery, Spark, Snowflake, Databricks Lakehouse, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39ce7a464350b080</t>
+          <t>https://www.indeed.com/viewjob?jk=b223a04c01fe717f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Policy Configuration</t>
+          <t>Senior Machine Learning Engineer, Shield</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Box</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, ECS, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1acf3efd34722f19</t>
+          <t>https://www.indeed.com/viewjob?jk=88492e295288a867</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (171679)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Databricks, Delta Live Tables, BigQuery, Spark, Snowflake, Databricks Lakehouse, ELT, dbt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b373595b350ec3d</t>
+          <t>https://www.indeed.com/viewjob?jk=39ce7a464350b080</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
+          <t>Machine Learning Engineer (171679)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Eurest</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4699f552f08a017</t>
+          <t>https://www.indeed.com/viewjob?jk=7b373595b350ec3d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Visualization Engineer</t>
+          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Eurest</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,42 +1886,42 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=867f580c7e3bb0e7</t>
+          <t>https://www.indeed.com/viewjob?jk=a4699f552f08a017</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Engineering Java/Python</t>
+          <t>Senior Software Engineer- Policy Configuration</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ec8999487afb4f6</t>
+          <t>https://www.indeed.com/viewjob?jk=1acf3efd34722f19</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer II 4P/554</t>
+          <t>Senior Data Visualization Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Oracle, SQL Server, NoSQL, Data Modeling</t>
+          <t>Redshift, S3, RDS, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d963e021c819ac</t>
+          <t>https://www.indeed.com/viewjob?jk=867f580c7e3bb0e7</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, CRM</t>
+          <t>Software Engineer III - Data Engineering Java/Python</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b266df7f25223b6</t>
+          <t>https://www.indeed.com/viewjob?jk=5ec8999487afb4f6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer (HPC/AI &amp; Distributed Systems)</t>
+          <t>Data Engineer II 4P/554</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Oracle, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dce54831329652c4</t>
+          <t>https://www.indeed.com/viewjob?jk=43d963e021c819ac</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Senior Data Engineer, CRM</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b11bc9d20fc1e2e2</t>
+          <t>https://www.indeed.com/viewjob?jk=7b266df7f25223b6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Sr. Full Stack Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, Splunk, Jenkins, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a6f623279ee6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=8fb9b3b22d6fa4bd</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>VistaCNO</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, Sqoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3cccca60e879db</t>
+          <t>https://www.indeed.com/viewjob?jk=aa8ab0c91f7227f7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Senior Backend Software Engineer (HPC/AI &amp; Distributed Systems)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f821dc8a5f6559</t>
+          <t>https://www.indeed.com/viewjob?jk=dce54831329652c4</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Consultant</t>
+          <t>Data Operations Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Geotab</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e6f7f78ae5d82f3</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd3315942275dbc</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3763de2ff690fcf</t>
+          <t>https://www.indeed.com/viewjob?jk=b11bc9d20fc1e2e2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3583ff1e8ab8b831</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a6f623279ee6d4</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dresher, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a764bcc9a479a693</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3cccca60e879db</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8b0a891a5da57c1</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f821dc8a5f6559</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full Stack Engineer, Consultant</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,14 +2386,14 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fdde135d701446e</t>
+          <t>https://www.indeed.com/viewjob?jk=1e6f7f78ae5d82f3</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68e8fc35af3fc28f</t>
+          <t>https://www.indeed.com/viewjob?jk=e3763de2ff690fcf</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>HealthMark Group</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd869bd281c90f0</t>
+          <t>https://www.indeed.com/viewjob?jk=3583ff1e8ab8b831</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Manufacturing Systems Integration Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Dresher, PA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, Power BI, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8532be76b040bdb</t>
+          <t>https://www.indeed.com/viewjob?jk=a764bcc9a479a693</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr Advisor II, AI Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b85a978b0b96b10</t>
+          <t>https://www.indeed.com/viewjob?jk=d8b0a891a5da57c1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Operations Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Geotab</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,77 +2551,77 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd3315942275dbc</t>
+          <t>https://www.indeed.com/viewjob?jk=0fdde135d701446e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer - II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CINC</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, ECS, Scala, Kafka, DynamoDB, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32c97e76b6269664</t>
+          <t>https://www.indeed.com/viewjob?jk=68e8fc35af3fc28f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MLOps Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>HealthMark Group</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4687b9b235a9a6ce</t>
+          <t>https://www.indeed.com/viewjob?jk=abd869bd281c90f0</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Manufacturing Systems Integration Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Trepp</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, Power BI, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,59 +2666,59 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd8df1b20c5849b</t>
+          <t>https://www.indeed.com/viewjob?jk=d8532be76b040bdb</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II (Remote)</t>
+          <t>Sr Advisor II, AI Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, CI/CD, Git, Python, SQL, Java</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd0ef78a415d3113</t>
+          <t>https://www.indeed.com/viewjob?jk=1b85a978b0b96b10</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>Burrell Behavioral Health</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Spark, Scala, CI/CD, Terraform, Git</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7929c83226ae75b</t>
+          <t>https://www.indeed.com/viewjob?jk=2ff4ba7951fc9c97</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Data Engineer - II</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>CINC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
+          <t>AWS, Kinesis, Redshift, ECS, Scala, Kafka, DynamoDB, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62210abb12166a07</t>
+          <t>https://www.indeed.com/viewjob?jk=32c97e76b6269664</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>MLOps Platform Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
+          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26a71508d797185b</t>
+          <t>https://www.indeed.com/viewjob?jk=4687b9b235a9a6ce</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Trepp</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc8599dc51df5400</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd8df1b20c5849b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Machine Learning Engineer II (Remote)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, CI/CD, Git, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503269b060f28151</t>
+          <t>https://www.indeed.com/viewjob?jk=dd0ef78a415d3113</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Spark, Scala, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbeb792ea58b7a87</t>
+          <t>https://www.indeed.com/viewjob?jk=e7929c83226ae75b</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd899ffea8f1b74c</t>
+          <t>https://www.indeed.com/viewjob?jk=62210abb12166a07</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f22565dd904e0808</t>
+          <t>https://www.indeed.com/viewjob?jk=26a71508d797185b</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
+          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8fcbfbc5352b0bf</t>
+          <t>https://www.indeed.com/viewjob?jk=bc8599dc51df5400</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Senior DevOps Engineer (Remote)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tango</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1da94812ec374b4</t>
+          <t>https://www.indeed.com/viewjob?jk=8d66e27cb89a5630</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>University of Texas Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee5cdada52faf29e</t>
+          <t>https://www.indeed.com/viewjob?jk=6fff225f154716cc</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Teradata Developer-5</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5676e61db2aa81f3</t>
+          <t>https://www.indeed.com/viewjob?jk=6f4f91dff933f5cc</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NiyamIT</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,24 +3146,24 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de6aa6e4975245c5</t>
+          <t>https://www.indeed.com/viewjob?jk=1a1802cfcb8371e8</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,24 +3181,24 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73fae08616e3afd</t>
+          <t>https://www.indeed.com/viewjob?jk=503269b060f28151</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cdec8d2c07ce6a8</t>
+          <t>https://www.indeed.com/viewjob?jk=dbeb792ea58b7a87</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer III - DevOps Automation Engineer</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58638a1a93a5925c</t>
+          <t>https://www.indeed.com/viewjob?jk=fd899ffea8f1b74c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Enterprise AI Architect</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=291c96af0e7cea02</t>
+          <t>https://www.indeed.com/viewjob?jk=f22565dd904e0808</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>University of Texas Health Science Center at San Antonio</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fff225f154716cc</t>
+          <t>https://www.indeed.com/viewjob?jk=f8fcbfbc5352b0bf</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Teradata Developer-5</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f4f91dff933f5cc</t>
+          <t>https://www.indeed.com/viewjob?jk=d1da94812ec374b4</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>NiyamIT</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a1802cfcb8371e8</t>
+          <t>https://www.indeed.com/viewjob?jk=ee5cdada52faf29e</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>(Remote) Fullstack Software Engineer (Special Projects Team)</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Aeroflow Health</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Asheville, NC, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61e2c56fc5827763</t>
+          <t>https://www.indeed.com/viewjob?jk=5676e61db2aa81f3</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Matrix Medical Network</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,15 +3461,225 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de6aa6e4975245c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e73fae08616e3afd</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2cdec8d2c07ce6a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Software Engineer III - DevOps Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=58638a1a93a5925c</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Enterprise AI Architect</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Radwell International</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Willingboro, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=291c96af0e7cea02</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>(Remote) Fullstack Software Engineer (Special Projects Team)</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Aeroflow Health</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Asheville, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, DynamoDB, CI/CD</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61e2c56fc5827763</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Matrix Medical Network</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>2026-01-29</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=939ed479d96c418b</t>
         </is>

--- a/results/job_matches_2026-02-26.xlsx
+++ b/results/job_matches_2026-02-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Application Developer III, Platform Engineering</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Herbalife</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Torrance, CA, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116acc2ab05b269d</t>
+          <t>https://www.indeed.com/viewjob?jk=b57d55c8e2a74923</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Application Developer III, Platform Engineering</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Herbalife</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Torrance, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b57d55c8e2a74923</t>
+          <t>https://www.indeed.com/viewjob?jk=116acc2ab05b269d</t>
         </is>
       </c>
     </row>
@@ -1728,17 +1728,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Solutions Architect III</t>
+          <t>Senior Machine Learning Engineer, Shield</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>IDEMIA</t>
+          <t>Box</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, ECS, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b223a04c01fe717f</t>
+          <t>https://www.indeed.com/viewjob?jk=88492e295288a867</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Shield</t>
+          <t>Solutions Architect III</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Box</t>
+          <t>IDEMIA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88492e295288a867</t>
+          <t>https://www.indeed.com/viewjob?jk=b223a04c01fe717f</t>
         </is>
       </c>
     </row>
@@ -1903,17 +1903,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Policy Configuration</t>
+          <t>Senior Data Visualization Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
+          <t>Redshift, S3, RDS, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1acf3efd34722f19</t>
+          <t>https://www.indeed.com/viewjob?jk=867f580c7e3bb0e7</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Visualization Engineer</t>
+          <t>Senior Software Engineer- Policy Configuration</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,17 +1956,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=867f580c7e3bb0e7</t>
+          <t>https://www.indeed.com/viewjob?jk=1acf3efd34722f19</t>
         </is>
       </c>
     </row>
@@ -2113,17 +2113,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Backend Software Engineer (HPC/AI &amp; Distributed Systems)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>VistaCNO</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, Sqoop, Spark, Scala, Snowflake</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa8ab0c91f7227f7</t>
+          <t>https://www.indeed.com/viewjob?jk=dce54831329652c4</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer (HPC/AI &amp; Distributed Systems)</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Chess.com</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,17 +2166,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dce54831329652c4</t>
+          <t>https://www.indeed.com/viewjob?jk=ada1c920f207c639</t>
         </is>
       </c>
     </row>
@@ -2218,17 +2218,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Manufacturing Systems Integration Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, Power BI, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b11bc9d20fc1e2e2</t>
+          <t>https://www.indeed.com/viewjob?jk=d8532be76b040bdb</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Sr Advisor II, AI Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,17 +2271,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a6f623279ee6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=1b85a978b0b96b10</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3cccca60e879db</t>
+          <t>https://www.indeed.com/viewjob?jk=b11bc9d20fc1e2e2</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f821dc8a5f6559</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a6f623279ee6d4</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Consultant</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e6f7f78ae5d82f3</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3cccca60e879db</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3763de2ff690fcf</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f821dc8a5f6559</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Engineer, Consultant</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,14 +2456,14 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3583ff1e8ab8b831</t>
+          <t>https://www.indeed.com/viewjob?jk=1e6f7f78ae5d82f3</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dresher, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,14 +2491,14 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a764bcc9a479a693</t>
+          <t>https://www.indeed.com/viewjob?jk=e3763de2ff690fcf</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8b0a891a5da57c1</t>
+          <t>https://www.indeed.com/viewjob?jk=3583ff1e8ab8b831</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dresher, PA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fdde135d701446e</t>
+          <t>https://www.indeed.com/viewjob?jk=a764bcc9a479a693</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68e8fc35af3fc28f</t>
+          <t>https://www.indeed.com/viewjob?jk=d8b0a891a5da57c1</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>HealthMark Group</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd869bd281c90f0</t>
+          <t>https://www.indeed.com/viewjob?jk=0fdde135d701446e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Manufacturing Systems Integration Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, Power BI, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8532be76b040bdb</t>
+          <t>https://www.indeed.com/viewjob?jk=68e8fc35af3fc28f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr Advisor II, AI Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>HealthMark Group</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b85a978b0b96b10</t>
+          <t>https://www.indeed.com/viewjob?jk=abd869bd281c90f0</t>
         </is>
       </c>
     </row>
@@ -2778,17 +2778,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MLOps Platform Engineer</t>
+          <t>Cloud Platform Engineer - Control Plane</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>clickhouse</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, IAM, RDS, Scala, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4687b9b235a9a6ce</t>
+          <t>https://www.indeed.com/viewjob?jk=d85ac5dbf541cd3b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>MLOps Platform Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Trepp</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
+          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd8df1b20c5849b</t>
+          <t>https://www.indeed.com/viewjob?jk=4687b9b235a9a6ce</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II (Remote)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Trepp</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, CI/CD, Git, Python, SQL, Java</t>
+          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd0ef78a415d3113</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd8df1b20c5849b</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Machine Learning Engineer II (Remote)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Spark, Scala, CI/CD, Terraform, Git</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, CI/CD, Git, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7929c83226ae75b</t>
+          <t>https://www.indeed.com/viewjob?jk=dd0ef78a415d3113</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,17 +2936,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Spark, Scala, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62210abb12166a07</t>
+          <t>https://www.indeed.com/viewjob?jk=e7929c83226ae75b</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26a71508d797185b</t>
+          <t>https://www.indeed.com/viewjob?jk=62210abb12166a07</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,17 +3006,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc8599dc51df5400</t>
+          <t>https://www.indeed.com/viewjob?jk=26a71508d797185b</t>
         </is>
       </c>
     </row>
@@ -3058,17 +3058,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
+          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>University of Texas Health Science Center at San Antonio</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
+          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fff225f154716cc</t>
+          <t>https://www.indeed.com/viewjob?jk=bc8599dc51df5400</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Teradata Developer-5</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>University of Texas Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f4f91dff933f5cc</t>
+          <t>https://www.indeed.com/viewjob?jk=6fff225f154716cc</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Teradata Developer-5</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NiyamIT</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a1802cfcb8371e8</t>
+          <t>https://www.indeed.com/viewjob?jk=6f4f91dff933f5cc</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NiyamIT</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503269b060f28151</t>
+          <t>https://www.indeed.com/viewjob?jk=1a1802cfcb8371e8</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Software Engineer III - DevOps Automation Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbeb792ea58b7a87</t>
+          <t>https://www.indeed.com/viewjob?jk=58638a1a93a5925c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Enterprise AI Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd899ffea8f1b74c</t>
+          <t>https://www.indeed.com/viewjob?jk=291c96af0e7cea02</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>(Remote) Fullstack Software Engineer (Special Projects Team)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Aeroflow Health</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Asheville, NC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,14 +3296,14 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f22565dd904e0808</t>
+          <t>https://www.indeed.com/viewjob?jk=61e2c56fc5827763</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,14 +3331,14 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8fcbfbc5352b0bf</t>
+          <t>https://www.indeed.com/viewjob?jk=503269b060f28151</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,14 +3366,14 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1da94812ec374b4</t>
+          <t>https://www.indeed.com/viewjob?jk=dbeb792ea58b7a87</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,14 +3401,14 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee5cdada52faf29e</t>
+          <t>https://www.indeed.com/viewjob?jk=fd899ffea8f1b74c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,14 +3436,14 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5676e61db2aa81f3</t>
+          <t>https://www.indeed.com/viewjob?jk=f22565dd904e0808</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,14 +3471,14 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de6aa6e4975245c5</t>
+          <t>https://www.indeed.com/viewjob?jk=f8fcbfbc5352b0bf</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,24 +3496,24 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73fae08616e3afd</t>
+          <t>https://www.indeed.com/viewjob?jk=d1da94812ec374b4</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cdec8d2c07ce6a8</t>
+          <t>https://www.indeed.com/viewjob?jk=ee5cdada52faf29e</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Engineer III - DevOps Automation Engineer</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58638a1a93a5925c</t>
+          <t>https://www.indeed.com/viewjob?jk=5676e61db2aa81f3</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Enterprise AI Architect</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=291c96af0e7cea02</t>
+          <t>https://www.indeed.com/viewjob?jk=de6aa6e4975245c5</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>(Remote) Fullstack Software Engineer (Special Projects Team)</t>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Aeroflow Health</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Asheville, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, DynamoDB, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61e2c56fc5827763</t>
+          <t>https://www.indeed.com/viewjob?jk=e73fae08616e3afd</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Matrix Medical Network</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,15 +3671,50 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2cdec8d2c07ce6a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Matrix Medical Network</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>2026-01-29</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=939ed479d96c418b</t>
         </is>

--- a/results/job_matches_2026-02-26.xlsx
+++ b/results/job_matches_2026-02-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,7 +543,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35decd7954b0dd0a</t>
+          <t>https://www.indeed.com/viewjob?jk=1d9cf410db691568</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineering III</t>
+          <t>Full Stack Engineer (React + Node.js)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Equitable</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Flume, Zookeeper</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1753914a33e85905</t>
+          <t>https://www.indeed.com/viewjob?jk=35decd7954b0dd0a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote in CA)</t>
+          <t>Software Engineering III</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>First American</t>
+          <t>Equitable</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Hadoop, Hive, Spark, Scala</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Flume, Zookeeper</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05ccb57abd2eb2be</t>
+          <t>https://www.indeed.com/viewjob?jk=1753914a33e85905</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Advisor II, Data Architect</t>
+          <t>Senior Data Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>First American</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21bd27b152469170</t>
+          <t>https://www.indeed.com/viewjob?jk=05ccb57abd2eb2be</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Disney Entertainment Television</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, ECS, RDS, Databricks, BigQuery, Vertex AI, Spark, Scala, Kafka</t>
+          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c7525b9f402e34</t>
+          <t>https://www.indeed.com/viewjob?jk=45366327b45aca00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Senior Advisor II, Data Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, ECS, RDS, Databricks, BigQuery, Vertex AI, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15f2e018b3b0d55e</t>
+          <t>https://www.indeed.com/viewjob?jk=21bd27b152469170</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>Blockchain Java Backend Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc1052fb6437c3a3</t>
+          <t>https://www.indeed.com/viewjob?jk=c48f5c60379802d3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SolidLine Media</t>
+          <t>Disney Entertainment Television</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Kinesis, ECS, RDS, Databricks, BigQuery, Vertex AI, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e8185f66fc8c270</t>
+          <t>https://www.indeed.com/viewjob?jk=06c7525b9f402e34</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, SQL, AWS) - Navigator Platform</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Kinesis, ECS, RDS, Databricks, BigQuery, Vertex AI, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38b02b46801c7f10</t>
+          <t>https://www.indeed.com/viewjob?jk=15f2e018b3b0d55e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef8a3d8ad1cf49b7</t>
+          <t>https://www.indeed.com/viewjob?jk=fc1052fb6437c3a3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>American Family Insurance</t>
+          <t>SolidLine Media</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c5e79cbd14d908</t>
+          <t>https://www.indeed.com/viewjob?jk=8e8185f66fc8c270</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Data Engineer (Python, SQL, AWS) - Navigator Platform</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e89cb44acf96f0ce</t>
+          <t>https://www.indeed.com/viewjob?jk=38b02b46801c7f10</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer - Boston</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9b3e4586db8c7fd</t>
+          <t>https://www.indeed.com/viewjob?jk=ef8a3d8ad1cf49b7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>American Family Insurance</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d7b87445d04d0bb</t>
+          <t>https://www.indeed.com/viewjob?jk=54c5e79cbd14d908</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer II (USA)</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,102 +1056,102 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=079fa62336e07385</t>
+          <t>https://www.indeed.com/viewjob?jk=e89cb44acf96f0ce</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-5</t>
+          <t>Data Engineer - Boston</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=656bcb1553978517</t>
+          <t>https://www.indeed.com/viewjob?jk=b9b3e4586db8c7fd</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Azure Data Engineer I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Premise Health</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ELT, Talend</t>
+          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=353cdf1ee00c6fd9</t>
+          <t>https://www.indeed.com/viewjob?jk=2d7b87445d04d0bb</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Ops Engineer</t>
+          <t>Software Engineer II (USA)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MLOps, MLflow, CI/CD</t>
+          <t>AWS, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8203af416f8f7f</t>
+          <t>https://www.indeed.com/viewjob?jk=079fa62336e07385</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Databricks Developer-5</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SRS Distribution</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9fcb451d7086751</t>
+          <t>https://www.indeed.com/viewjob?jk=656bcb1553978517</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Data Engineer I</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GovWorx</t>
+          <t>Premise Health</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Spark, PySpark, Scala, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ELT, Talend</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,59 +1231,59 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ee6445287271c9d</t>
+          <t>https://www.indeed.com/viewjob?jk=353cdf1ee00c6fd9</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Distinguished Engineer</t>
+          <t>Senior Machine Learning Ops Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Cassandra, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab3a4b9f2c783845</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8203af416f8f7f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>SRS Distribution</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b57d55c8e2a74923</t>
+          <t>https://www.indeed.com/viewjob?jk=e9fcb451d7086751</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Application Developer III, Platform Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Herbalife</t>
+          <t>GovWorx</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Torrance, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Spark, PySpark, Scala, MySQL, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116acc2ab05b269d</t>
+          <t>https://www.indeed.com/viewjob?jk=8ee6445287271c9d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>F5</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Cloud Storage, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,67 +1371,67 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79a97f6710d73548</t>
+          <t>https://www.indeed.com/viewjob?jk=54fbc1b6f53ddcb1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Application Developer III, Platform Engineering</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Herbalife</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Torrance, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, Scala, Power BI, MLOps, MLflow, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5df4e674559910e</t>
+          <t>https://www.indeed.com/viewjob?jk=116acc2ab05b269d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ramsey Solutions</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,102 +1441,102 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba46b1aa50f7279f</t>
+          <t>https://www.indeed.com/viewjob?jk=b57d55c8e2a74923</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Intermediate Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Progressive</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, PostgreSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, S3, Azure, Scala, Snowflake, ETL, ELT, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=693f3e0a054607b0</t>
+          <t>https://www.indeed.com/viewjob?jk=6b465e27586b38fb</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Solution Engineer I</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Associated Wholesale Grocers</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Cloud Storage, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5985bee213bf40</t>
+          <t>https://www.indeed.com/viewjob?jk=79a97f6710d73548</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b7f8d62e370d21c</t>
+          <t>https://www.indeed.com/viewjob?jk=2845c99fbf7bb445</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The Friedkin Group</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Dataflow, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, Scala, Power BI, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,137 +1581,137 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7ede0f34ce25b71</t>
+          <t>https://www.indeed.com/viewjob?jk=b5df4e674559910e</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Ramsey Solutions</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30154588ed7f957f</t>
+          <t>https://www.indeed.com/viewjob?jk=ba46b1aa50f7279f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, PostgreSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64eeda5b2dfcfe99</t>
+          <t>https://www.indeed.com/viewjob?jk=693f3e0a054607b0</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Solution Engineer I</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Associated Wholesale Grocers</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, Redshift, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a077c257a4cf0b5</t>
+          <t>https://www.indeed.com/viewjob?jk=5e5985bee213bf40</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Engineer - Wire Payments Platform</t>
+          <t>Snowflake SME</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55c16c38ef65d0c6</t>
+          <t>https://www.indeed.com/viewjob?jk=ccefe385c15cc707</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Shield</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Box</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88492e295288a867</t>
+          <t>https://www.indeed.com/viewjob?jk=1b7f8d62e370d21c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Solutions Architect III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>IDEMIA</t>
+          <t>The Friedkin Group</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Dataflow, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b223a04c01fe717f</t>
+          <t>https://www.indeed.com/viewjob?jk=f7ede0f34ce25b71</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Delta Live Tables, BigQuery, Spark, Snowflake, Databricks Lakehouse, ELT, dbt</t>
+          <t>AWS, S3, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39ce7a464350b080</t>
+          <t>https://www.indeed.com/viewjob?jk=30154588ed7f957f</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (171679)</t>
+          <t>Senior Machine Learning Engineer (Remote)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b373595b350ec3d</t>
+          <t>https://www.indeed.com/viewjob?jk=64eeda5b2dfcfe99</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Eurest</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4699f552f08a017</t>
+          <t>https://www.indeed.com/viewjob?jk=4a077c257a4cf0b5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Visualization Engineer</t>
+          <t>Senior Engineer - Wire Payments Platform</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=867f580c7e3bb0e7</t>
+          <t>https://www.indeed.com/viewjob?jk=55c16c38ef65d0c6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Policy Configuration</t>
+          <t>Solutions Architect III</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>IDEMIA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,42 +1956,42 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1acf3efd34722f19</t>
+          <t>https://www.indeed.com/viewjob?jk=b223a04c01fe717f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Engineering Java/Python</t>
+          <t>Senior Machine Learning Engineer, Shield</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Box</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ec8999487afb4f6</t>
+          <t>https://www.indeed.com/viewjob?jk=88492e295288a867</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer II 4P/554</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Oracle, SQL Server, NoSQL, Data Modeling</t>
+          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d963e021c819ac</t>
+          <t>https://www.indeed.com/viewjob?jk=74494a10316e7fe4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, CRM</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Databricks, Delta Live Tables, BigQuery, Spark, Snowflake, Databricks Lakehouse, ELT, dbt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,102 +2071,102 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b266df7f25223b6</t>
+          <t>https://www.indeed.com/viewjob?jk=39ce7a464350b080</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer</t>
+          <t>Machine Learning Engineer (171679)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, Splunk, Jenkins, Maven, Docker, Jenkins</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fb9b3b22d6fa4bd</t>
+          <t>https://www.indeed.com/viewjob?jk=7b373595b350ec3d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer (HPC/AI &amp; Distributed Systems)</t>
+          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Eurest</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dce54831329652c4</t>
+          <t>https://www.indeed.com/viewjob?jk=a4699f552f08a017</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Senior Software Engineer- Policy Configuration</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Chess.com</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,59 +2176,59 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ada1c920f207c639</t>
+          <t>https://www.indeed.com/viewjob?jk=1acf3efd34722f19</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Operations Developer</t>
+          <t>Senior Data Visualization Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Geotab</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, CI/CD, Airflow</t>
+          <t>Redshift, S3, RDS, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd3315942275dbc</t>
+          <t>https://www.indeed.com/viewjob?jk=867f580c7e3bb0e7</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Manufacturing Systems Integration Engineer</t>
+          <t>Software Engineer III - Data Engineering Java/Python</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, Power BI, Docker, Kubernetes, Git</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8532be76b040bdb</t>
+          <t>https://www.indeed.com/viewjob?jk=5ec8999487afb4f6</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr Advisor II, AI Architect</t>
+          <t>Data Engineer II 4P/554</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Oracle, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b85a978b0b96b10</t>
+          <t>https://www.indeed.com/viewjob?jk=43d963e021c819ac</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Senior Data Engineer, CRM</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b11bc9d20fc1e2e2</t>
+          <t>https://www.indeed.com/viewjob?jk=7b266df7f25223b6</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Chess.com</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a6f623279ee6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=ada1c920f207c639</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Senior Backend Software Engineer (HPC/AI &amp; Distributed Systems)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3cccca60e879db</t>
+          <t>https://www.indeed.com/viewjob?jk=dce54831329652c4</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Data Operations Developer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Geotab</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f821dc8a5f6559</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd3315942275dbc</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Consultant</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e6f7f78ae5d82f3</t>
+          <t>https://www.indeed.com/viewjob?jk=b11bc9d20fc1e2e2</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3763de2ff690fcf</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a6f623279ee6d4</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3583ff1e8ab8b831</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3cccca60e879db</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dresher, PA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a764bcc9a479a693</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f821dc8a5f6559</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full Stack Engineer, Consultant</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,14 +2596,14 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8b0a891a5da57c1</t>
+          <t>https://www.indeed.com/viewjob?jk=1e6f7f78ae5d82f3</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fdde135d701446e</t>
+          <t>https://www.indeed.com/viewjob?jk=e3763de2ff690fcf</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68e8fc35af3fc28f</t>
+          <t>https://www.indeed.com/viewjob?jk=3583ff1e8ab8b831</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>HealthMark Group</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dresher, PA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,89 +2701,89 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd869bd281c90f0</t>
+          <t>https://www.indeed.com/viewjob?jk=a764bcc9a479a693</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Burrell Behavioral Health</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ff4ba7951fc9c97</t>
+          <t>https://www.indeed.com/viewjob?jk=d8b0a891a5da57c1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer - II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CINC</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, ECS, Scala, Kafka, DynamoDB, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32c97e76b6269664</t>
+          <t>https://www.indeed.com/viewjob?jk=0fdde135d701446e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer - Control Plane</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>clickhouse</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2792,11 +2792,11 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, IAM, RDS, Scala, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d85ac5dbf541cd3b</t>
+          <t>https://www.indeed.com/viewjob?jk=68e8fc35af3fc28f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MLOps Platform Engineer</t>
+          <t>Manufacturing Systems Integration Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, Power BI, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4687b9b235a9a6ce</t>
+          <t>https://www.indeed.com/viewjob?jk=d8532be76b040bdb</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Trepp</t>
+          <t>Finance of America</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, Spark, Scala, Data Modeling, CI/CD, Git</t>
+          <t>AWS, Azure, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, MS Excel, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd8df1b20c5849b</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8846493996e830</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II (Remote)</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Burrell Behavioral Health</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, CI/CD, Git, Python, SQL, Java</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd0ef78a415d3113</t>
+          <t>https://www.indeed.com/viewjob?jk=2ff4ba7951fc9c97</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>MLOps Platform Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Spark, Scala, CI/CD, Terraform, Git</t>
+          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7929c83226ae75b</t>
+          <t>https://www.indeed.com/viewjob?jk=4687b9b235a9a6ce</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Machine Learning Engineer II (Remote)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, CI/CD, Git, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62210abb12166a07</t>
+          <t>https://www.indeed.com/viewjob?jk=dd0ef78a415d3113</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Spark, Scala, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26a71508d797185b</t>
+          <t>https://www.indeed.com/viewjob?jk=e7929c83226ae75b</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Remote)</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tango</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Git</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d66e27cb89a5630</t>
+          <t>https://www.indeed.com/viewjob?jk=62210abb12166a07</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc8599dc51df5400</t>
+          <t>https://www.indeed.com/viewjob?jk=26a71508d797185b</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
+          <t>Senior DevOps Engineer (Remote)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>University of Texas Health Science Center at San Antonio</t>
+          <t>Tango</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fff225f154716cc</t>
+          <t>https://www.indeed.com/viewjob?jk=8d66e27cb89a5630</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Teradata Developer-5</t>
+          <t>Product Engineer, Partnerships</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Replit</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f4f91dff933f5cc</t>
+          <t>https://www.indeed.com/viewjob?jk=b40a810716931b39</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NiyamIT</t>
+          <t>University of Texas Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a1802cfcb8371e8</t>
+          <t>https://www.indeed.com/viewjob?jk=6fff225f154716cc</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer III - DevOps Automation Engineer</t>
+          <t>Teradata Developer-5</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58638a1a93a5925c</t>
+          <t>https://www.indeed.com/viewjob?jk=6f4f91dff933f5cc</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Enterprise AI Architect</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>NiyamIT</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=291c96af0e7cea02</t>
+          <t>https://www.indeed.com/viewjob?jk=1a1802cfcb8371e8</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>(Remote) Fullstack Software Engineer (Special Projects Team)</t>
+          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Aeroflow Health</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Asheville, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, DynamoDB, CI/CD</t>
+          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61e2c56fc5827763</t>
+          <t>https://www.indeed.com/viewjob?jk=77bef7280137d41c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,14 +3331,14 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503269b060f28151</t>
+          <t>https://www.indeed.com/viewjob?jk=bc8599dc51df5400</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,14 +3366,14 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbeb792ea58b7a87</t>
+          <t>https://www.indeed.com/viewjob?jk=503269b060f28151</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,14 +3401,14 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd899ffea8f1b74c</t>
+          <t>https://www.indeed.com/viewjob?jk=dbeb792ea58b7a87</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,14 +3436,14 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f22565dd904e0808</t>
+          <t>https://www.indeed.com/viewjob?jk=fd899ffea8f1b74c</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,14 +3471,14 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8fcbfbc5352b0bf</t>
+          <t>https://www.indeed.com/viewjob?jk=f22565dd904e0808</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,14 +3506,14 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1da94812ec374b4</t>
+          <t>https://www.indeed.com/viewjob?jk=f8fcbfbc5352b0bf</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3541,14 +3541,14 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee5cdada52faf29e</t>
+          <t>https://www.indeed.com/viewjob?jk=d1da94812ec374b4</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,14 +3576,14 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5676e61db2aa81f3</t>
+          <t>https://www.indeed.com/viewjob?jk=ee5cdada52faf29e</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,14 +3611,14 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de6aa6e4975245c5</t>
+          <t>https://www.indeed.com/viewjob?jk=5676e61db2aa81f3</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,17 +3636,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73fae08616e3afd</t>
+          <t>https://www.indeed.com/viewjob?jk=de6aa6e4975245c5</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cdec8d2c07ce6a8</t>
+          <t>https://www.indeed.com/viewjob?jk=e73fae08616e3afd</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Matrix Medical Network</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,15 +3706,155 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2cdec8d2c07ce6a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Software Engineer III - DevOps Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=58638a1a93a5925c</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Enterprise AI Architect</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Radwell International</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Willingboro, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=291c96af0e7cea02</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>(Remote) Fullstack Software Engineer (Special Projects Team)</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Aeroflow Health</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Asheville, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, DynamoDB, CI/CD</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61e2c56fc5827763</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Matrix Medical Network</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>2026-01-29</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=939ed479d96c418b</t>
         </is>

--- a/results/job_matches_2026-02-26.xlsx
+++ b/results/job_matches_2026-02-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,52 +643,52 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote in CA)</t>
+          <t>DevOps Software Engineer III</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>First American</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, EMR, Lambda, Redshift, Athena, S3, RDS, Oozie, Scala, Oracle</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05ccb57abd2eb2be</t>
+          <t>https://www.indeed.com/viewjob?jk=ae9c515199307b36</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>Senior Data Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>First American</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45366327b45aca00</t>
+          <t>https://www.indeed.com/viewjob?jk=05ccb57abd2eb2be</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Advisor II, Data Architect</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21bd27b152469170</t>
+          <t>https://www.indeed.com/viewjob?jk=45366327b45aca00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Blockchain Java Backend Engineer</t>
+          <t>Senior Advisor II, Data Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,17 +766,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48f5c60379802d3</t>
+          <t>https://www.indeed.com/viewjob?jk=21bd27b152469170</t>
         </is>
       </c>
     </row>
@@ -853,25 +853,25 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>Blockchain Java Backend Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc1052fb6437c3a3</t>
+          <t>https://www.indeed.com/viewjob?jk=c48f5c60379802d3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SolidLine Media</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e8185f66fc8c270</t>
+          <t>https://www.indeed.com/viewjob?jk=fc1052fb6437c3a3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, SQL, AWS) - Navigator Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>SolidLine Media</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,24 +941,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38b02b46801c7f10</t>
+          <t>https://www.indeed.com/viewjob?jk=8e8185f66fc8c270</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (Python, SQL, AWS) - Navigator Platform</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef8a3d8ad1cf49b7</t>
+          <t>https://www.indeed.com/viewjob?jk=38b02b46801c7f10</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>American Family Insurance</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c5e79cbd14d908</t>
+          <t>https://www.indeed.com/viewjob?jk=ef8a3d8ad1cf49b7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>American Family Insurance</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e89cb44acf96f0ce</t>
+          <t>https://www.indeed.com/viewjob?jk=54c5e79cbd14d908</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer - Boston</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9b3e4586db8c7fd</t>
+          <t>https://www.indeed.com/viewjob?jk=e89cb44acf96f0ce</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Boston</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d7b87445d04d0bb</t>
+          <t>https://www.indeed.com/viewjob?jk=b9b3e4586db8c7fd</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer II (USA)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,69 +1151,69 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=079fa62336e07385</t>
+          <t>https://www.indeed.com/viewjob?jk=2d7b87445d04d0bb</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-5</t>
+          <t>Software Engineer II (USA)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=656bcb1553978517</t>
+          <t>https://www.indeed.com/viewjob?jk=079fa62336e07385</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Azure Data Engineer I</t>
+          <t>Senior Databricks Developer-5</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Premise Health</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ELT, Talend</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=353cdf1ee00c6fd9</t>
+          <t>https://www.indeed.com/viewjob?jk=656bcb1553978517</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Ops Engineer</t>
+          <t>Azure Data Engineer I</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Premise Health</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ELT, Talend</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,59 +1266,59 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8203af416f8f7f</t>
+          <t>https://www.indeed.com/viewjob?jk=353cdf1ee00c6fd9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Machine Learning Ops Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SRS Distribution</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9fcb451d7086751</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8203af416f8f7f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GovWorx</t>
+          <t>SRS Distribution</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Spark, PySpark, Scala, MySQL, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ee6445287271c9d</t>
+          <t>https://www.indeed.com/viewjob?jk=e9fcb451d7086751</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>GovWorx</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Spark, PySpark, Scala, MySQL, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54fbc1b6f53ddcb1</t>
+          <t>https://www.indeed.com/viewjob?jk=8ee6445287271c9d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Application Developer III, Platform Engineering</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Herbalife</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Torrance, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,17 +1396,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116acc2ab05b269d</t>
+          <t>https://www.indeed.com/viewjob?jk=54fbc1b6f53ddcb1</t>
         </is>
       </c>
     </row>
@@ -1448,52 +1448,52 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Intermediate Data Engineer</t>
+          <t>Application Developer III, Platform Engineering</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Progressive</t>
+          <t>Herbalife</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Torrance, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, Snowflake, ETL, ELT, dbt, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b465e27586b38fb</t>
+          <t>https://www.indeed.com/viewjob?jk=116acc2ab05b269d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Intermediate Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>F5</t>
+          <t>Progressive</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Cloud Storage, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, S3, Azure, Scala, Snowflake, ETL, ELT, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79a97f6710d73548</t>
+          <t>https://www.indeed.com/viewjob?jk=6b465e27586b38fb</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Cloud Storage, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2845c99fbf7bb445</t>
+          <t>https://www.indeed.com/viewjob?jk=79a97f6710d73548</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, Scala, Power BI, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,94 +1581,94 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5df4e674559910e</t>
+          <t>https://www.indeed.com/viewjob?jk=2845c99fbf7bb445</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ramsey Solutions</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, Scala, Power BI, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba46b1aa50f7279f</t>
+          <t>https://www.indeed.com/viewjob?jk=b5df4e674559910e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer with AI &amp; Kubernetes</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, PostgreSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=693f3e0a054607b0</t>
+          <t>https://www.indeed.com/viewjob?jk=fe3d2714f39bd085</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Solution Engineer I</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Associated Wholesale Grocers</t>
+          <t>Ramsey Solutions</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5985bee213bf40</t>
+          <t>https://www.indeed.com/viewjob?jk=ba46b1aa50f7279f</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Snowflake SME</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, PostgreSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccefe385c15cc707</t>
+          <t>https://www.indeed.com/viewjob?jk=693f3e0a054607b0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Solution Engineer I</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>Associated Wholesale Grocers</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,42 +1746,42 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, Redshift, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b7f8d62e370d21c</t>
+          <t>https://www.indeed.com/viewjob?jk=5e5985bee213bf40</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Snowflake SME</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>The Friedkin Group</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Dataflow, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,59 +1791,59 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7ede0f34ce25b71</t>
+          <t>https://www.indeed.com/viewjob?jk=ccefe385c15cc707</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30154588ed7f957f</t>
+          <t>https://www.indeed.com/viewjob?jk=1b7f8d62e370d21c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>The Friedkin Group</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Dataflow, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64eeda5b2dfcfe99</t>
+          <t>https://www.indeed.com/viewjob?jk=f7ede0f34ce25b71</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, S3, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a077c257a4cf0b5</t>
+          <t>https://www.indeed.com/viewjob?jk=30154588ed7f957f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Engineer - Wire Payments Platform</t>
+          <t>Senior Machine Learning Engineer (Remote)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55c16c38ef65d0c6</t>
+          <t>https://www.indeed.com/viewjob?jk=64eeda5b2dfcfe99</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Solutions Architect III</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>IDEMIA</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b223a04c01fe717f</t>
+          <t>https://www.indeed.com/viewjob?jk=4a077c257a4cf0b5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Shield</t>
+          <t>Senior Engineer - Wire Payments Platform</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Box</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88492e295288a867</t>
+          <t>https://www.indeed.com/viewjob?jk=55c16c38ef65d0c6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Machine Learning Engineer (171679)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,19 +2036,19 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74494a10316e7fe4</t>
+          <t>https://www.indeed.com/viewjob?jk=7b373595b350ec3d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solutions Architect III</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>IDEMIA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Delta Live Tables, BigQuery, Spark, Snowflake, Databricks Lakehouse, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39ce7a464350b080</t>
+          <t>https://www.indeed.com/viewjob?jk=b223a04c01fe717f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (171679)</t>
+          <t>Senior Machine Learning Engineer, Shield</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Box</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, ECS, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b373595b350ec3d</t>
+          <t>https://www.indeed.com/viewjob?jk=88492e295288a867</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Eurest</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4699f552f08a017</t>
+          <t>https://www.indeed.com/viewjob?jk=74494a10316e7fe4</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Policy Configuration</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Databricks, Delta Live Tables, BigQuery, Spark, Snowflake, Databricks Lakehouse, ELT, dbt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1acf3efd34722f19</t>
+          <t>https://www.indeed.com/viewjob?jk=39ce7a464350b080</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Visualization Engineer</t>
+          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Eurest</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,139 +2201,139 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=867f580c7e3bb0e7</t>
+          <t>https://www.indeed.com/viewjob?jk=a4699f552f08a017</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Engineering Java/Python</t>
+          <t>Senior Data Visualization Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
+          <t>Redshift, S3, RDS, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ec8999487afb4f6</t>
+          <t>https://www.indeed.com/viewjob?jk=867f580c7e3bb0e7</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer II 4P/554</t>
+          <t>Senior Software Engineer- Policy Configuration</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Oracle, SQL Server, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d963e021c819ac</t>
+          <t>https://www.indeed.com/viewjob?jk=1acf3efd34722f19</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, CRM</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Zonos</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Saint George, UT, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
+          <t>AWS, ECS, IAM, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b266df7f25223b6</t>
+          <t>https://www.indeed.com/viewjob?jk=3bee8d25021d9111</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Software Engineer III - Data Engineering Java/Python</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Chess.com</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ada1c920f207c639</t>
+          <t>https://www.indeed.com/viewjob?jk=5ec8999487afb4f6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer (HPC/AI &amp; Distributed Systems)</t>
+          <t>Data Engineer II 4P/554</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Oracle, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dce54831329652c4</t>
+          <t>https://www.indeed.com/viewjob?jk=43d963e021c819ac</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Operations Developer</t>
+          <t>Senior Data Engineer, CRM</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Geotab</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, CI/CD, Airflow</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd3315942275dbc</t>
+          <t>https://www.indeed.com/viewjob?jk=7b266df7f25223b6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Nation's Best Sports</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>API Gateway, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b11bc9d20fc1e2e2</t>
+          <t>https://www.indeed.com/viewjob?jk=4021abb69b19b3ac</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Chess.com</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a6f623279ee6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=ada1c920f207c639</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Data Operations Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Geotab</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3cccca60e879db</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd3315942275dbc</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Manufacturing Systems Integration Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, Power BI, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f821dc8a5f6559</t>
+          <t>https://www.indeed.com/viewjob?jk=d8532be76b040bdb</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Consultant</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e6f7f78ae5d82f3</t>
+          <t>https://www.indeed.com/viewjob?jk=b11bc9d20fc1e2e2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3763de2ff690fcf</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a6f623279ee6d4</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3583ff1e8ab8b831</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3cccca60e879db</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dresher, PA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a764bcc9a479a693</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f821dc8a5f6559</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full Stack Engineer, Consultant</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,14 +2736,14 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8b0a891a5da57c1</t>
+          <t>https://www.indeed.com/viewjob?jk=1e6f7f78ae5d82f3</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2771,14 +2771,14 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fdde135d701446e</t>
+          <t>https://www.indeed.com/viewjob?jk=e3763de2ff690fcf</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68e8fc35af3fc28f</t>
+          <t>https://www.indeed.com/viewjob?jk=3583ff1e8ab8b831</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Manufacturing Systems Integration Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Dresher, PA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, Power BI, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,102 +2841,102 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8532be76b040bdb</t>
+          <t>https://www.indeed.com/viewjob?jk=a764bcc9a479a693</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Finance of America</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Newton, MA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, MS Excel, Python</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8846493996e830</t>
+          <t>https://www.indeed.com/viewjob?jk=d8b0a891a5da57c1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Burrell Behavioral Health</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ff4ba7951fc9c97</t>
+          <t>https://www.indeed.com/viewjob?jk=0fdde135d701446e</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MLOps Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Ascensus</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,59 +2946,59 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4687b9b235a9a6ce</t>
+          <t>https://www.indeed.com/viewjob?jk=68e8fc35af3fc28f</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II (Remote)</t>
+          <t>Senior Backend Software Engineer (HPC/AI &amp; Distributed Systems)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, CI/CD, Git, Python, SQL, Java</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd0ef78a415d3113</t>
+          <t>https://www.indeed.com/viewjob?jk=dce54831329652c4</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>Finance of America</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Spark, Scala, CI/CD, Terraform, Git</t>
+          <t>AWS, Azure, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, MS Excel, Python</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7929c83226ae75b</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8846493996e830</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Burrell Behavioral Health</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62210abb12166a07</t>
+          <t>https://www.indeed.com/viewjob?jk=2ff4ba7951fc9c97</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>MLOps Platform Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
+          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26a71508d797185b</t>
+          <t>https://www.indeed.com/viewjob?jk=4687b9b235a9a6ce</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Remote)</t>
+          <t>Machine Learning Engineer II (Remote)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Tango</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Git</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, CI/CD, Git, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d66e27cb89a5630</t>
+          <t>https://www.indeed.com/viewjob?jk=dd0ef78a415d3113</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Product Engineer, Partnerships</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Replit</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Spark, Scala, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b40a810716931b39</t>
+          <t>https://www.indeed.com/viewjob?jk=e7929c83226ae75b</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>University of Texas Health Science Center at San Antonio</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fff225f154716cc</t>
+          <t>https://www.indeed.com/viewjob?jk=62210abb12166a07</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Teradata Developer-5</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f4f91dff933f5cc</t>
+          <t>https://www.indeed.com/viewjob?jk=26a71508d797185b</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Enterprise AI Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>NiyamIT</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a1802cfcb8371e8</t>
+          <t>https://www.indeed.com/viewjob?jk=291c96af0e7cea02</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
+          <t>Senior DevOps Engineer (Remote)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Tango</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77bef7280137d41c</t>
+          <t>https://www.indeed.com/viewjob?jk=8d66e27cb89a5630</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
+          <t>Product Engineer, Partnerships</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Replit</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc8599dc51df5400</t>
+          <t>https://www.indeed.com/viewjob?jk=b40a810716931b39</t>
         </is>
       </c>
     </row>
@@ -3408,17 +3408,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>University of Texas Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd899ffea8f1b74c</t>
+          <t>https://www.indeed.com/viewjob?jk=6fff225f154716cc</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Teradata Developer-5</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f22565dd904e0808</t>
+          <t>https://www.indeed.com/viewjob?jk=6f4f91dff933f5cc</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NiyamIT</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8fcbfbc5352b0bf</t>
+          <t>https://www.indeed.com/viewjob?jk=1a1802cfcb8371e8</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Software Engineer III - DevOps Automation Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1da94812ec374b4</t>
+          <t>https://www.indeed.com/viewjob?jk=58638a1a93a5925c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>(Remote) Fullstack Software Engineer (Special Projects Team)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Aeroflow Health</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Asheville, NC, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee5cdada52faf29e</t>
+          <t>https://www.indeed.com/viewjob?jk=61e2c56fc5827763</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5676e61db2aa81f3</t>
+          <t>https://www.indeed.com/viewjob?jk=77bef7280137d41c</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,14 +3646,14 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de6aa6e4975245c5</t>
+          <t>https://www.indeed.com/viewjob?jk=bc8599dc51df5400</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,24 +3671,24 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73fae08616e3afd</t>
+          <t>https://www.indeed.com/viewjob?jk=fd899ffea8f1b74c</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cdec8d2c07ce6a8</t>
+          <t>https://www.indeed.com/viewjob?jk=f22565dd904e0808</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Engineer III - DevOps Automation Engineer</t>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58638a1a93a5925c</t>
+          <t>https://www.indeed.com/viewjob?jk=f8fcbfbc5352b0bf</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Enterprise AI Architect</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=291c96af0e7cea02</t>
+          <t>https://www.indeed.com/viewjob?jk=d1da94812ec374b4</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>(Remote) Fullstack Software Engineer (Special Projects Team)</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Aeroflow Health</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Asheville, NC, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61e2c56fc5827763</t>
+          <t>https://www.indeed.com/viewjob?jk=ee5cdada52faf29e</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Matrix Medical Network</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,15 +3846,155 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5676e61db2aa81f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Engineer II- .Net</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Chevy Chase, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de6aa6e4975245c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e73fae08616e3afd</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2cdec8d2c07ce6a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Matrix Medical Network</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="F102" t="inlineStr">
         <is>
           <t>2026-01-29</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="G102" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=939ed479d96c418b</t>
         </is>

--- a/results/job_matches_2026-02-26.xlsx
+++ b/results/job_matches_2026-02-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,60 +573,60 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (React + Node.js)</t>
+          <t>Software Engineering III</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Equitable</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Flume, Zookeeper</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35decd7954b0dd0a</t>
+          <t>https://www.indeed.com/viewjob?jk=1753914a33e85905</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineering III</t>
+          <t>Senior Data Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Equitable</t>
+          <t>First American</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Flume, Zookeeper</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1753914a33e85905</t>
+          <t>https://www.indeed.com/viewjob?jk=05ccb57abd2eb2be</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer III</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, Athena, S3, RDS, Oozie, Scala, Oracle</t>
+          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae9c515199307b36</t>
+          <t>https://www.indeed.com/viewjob?jk=45366327b45aca00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote in CA)</t>
+          <t>Senior Advisor II, Data Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>First American</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05ccb57abd2eb2be</t>
+          <t>https://www.indeed.com/viewjob?jk=21bd27b152469170</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>Sr. Full Stack Digital Services Software Engineer #1741</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Wellmark Blue Cross and Blue Shield</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45366327b45aca00</t>
+          <t>https://www.indeed.com/viewjob?jk=ef36d6b0df82b802</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Advisor II, Data Architect</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Disney Entertainment Television</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,17 +766,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, Kinesis, ECS, RDS, Databricks, BigQuery, Vertex AI, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21bd27b152469170</t>
+          <t>https://www.indeed.com/viewjob?jk=06c7525b9f402e34</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Disney Entertainment Television</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -806,24 +806,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c7525b9f402e34</t>
+          <t>https://www.indeed.com/viewjob?jk=15f2e018b3b0d55e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Blockchain Java Backend Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -836,42 +836,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, ECS, RDS, Databricks, BigQuery, Vertex AI, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15f2e018b3b0d55e</t>
+          <t>https://www.indeed.com/viewjob?jk=c48f5c60379802d3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Blockchain Java Backend Engineer</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48f5c60379802d3</t>
+          <t>https://www.indeed.com/viewjob?jk=fc1052fb6437c3a3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SolidLine Media</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc1052fb6437c3a3</t>
+          <t>https://www.indeed.com/viewjob?jk=8e8185f66fc8c270</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Python, SQL, AWS) - Navigator Platform</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SolidLine Media</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,24 +941,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e8185f66fc8c270</t>
+          <t>https://www.indeed.com/viewjob?jk=38b02b46801c7f10</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, SQL, AWS) - Navigator Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38b02b46801c7f10</t>
+          <t>https://www.indeed.com/viewjob?jk=ef8a3d8ad1cf49b7</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>American Family Insurance</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef8a3d8ad1cf49b7</t>
+          <t>https://www.indeed.com/viewjob?jk=54c5e79cbd14d908</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>American Family Insurance</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c5e79cbd14d908</t>
+          <t>https://www.indeed.com/viewjob?jk=e89cb44acf96f0ce</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Data Engineer - Boston</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e89cb44acf96f0ce</t>
+          <t>https://www.indeed.com/viewjob?jk=b9b3e4586db8c7fd</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer - Boston</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9b3e4586db8c7fd</t>
+          <t>https://www.indeed.com/viewjob?jk=2d7b87445d04d0bb</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SAP Security Consultant</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Azure, Google Cloud Platform</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d7b87445d04d0bb</t>
+          <t>https://www.indeed.com/viewjob?jk=99f20f1d8e4ac8db</t>
         </is>
       </c>
     </row>
@@ -1203,17 +1203,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer-5</t>
+          <t>Azure Data Engineer I</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Premise Health</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ELT, Talend</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=656bcb1553978517</t>
+          <t>https://www.indeed.com/viewjob?jk=353cdf1ee00c6fd9</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Azure Data Engineer I</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Premise Health</t>
+          <t>GreatAmerica Financial Services</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,17 +1256,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ELT, Talend</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=353cdf1ee00c6fd9</t>
+          <t>https://www.indeed.com/viewjob?jk=a73f224d7e2859e4</t>
         </is>
       </c>
     </row>
@@ -1413,17 +1413,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Application Developer III, Platform Engineering</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Herbalife</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Torrance, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b57d55c8e2a74923</t>
+          <t>https://www.indeed.com/viewjob?jk=116acc2ab05b269d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Application Developer III, Platform Engineering</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Herbalife</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Torrance, CA, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116acc2ab05b269d</t>
+          <t>https://www.indeed.com/viewjob?jk=b57d55c8e2a74923</t>
         </is>
       </c>
     </row>
@@ -1553,17 +1553,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Engineer with AI &amp; Kubernetes</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2845c99fbf7bb445</t>
+          <t>https://www.indeed.com/viewjob?jk=fe3d2714f39bd085</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Sr. Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, Scala, Power BI, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5df4e674559910e</t>
+          <t>https://www.indeed.com/viewjob?jk=7ac4966435dab5e0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer with AI &amp; Kubernetes</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,59 +1651,59 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe3d2714f39bd085</t>
+          <t>https://www.indeed.com/viewjob?jk=2845c99fbf7bb445</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ramsey Solutions</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, Scala, Power BI, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba46b1aa50f7279f</t>
+          <t>https://www.indeed.com/viewjob?jk=b5df4e674559910e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Ramsey Solutions</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, PostgreSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=693f3e0a054607b0</t>
+          <t>https://www.indeed.com/viewjob?jk=ba46b1aa50f7279f</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Solution Engineer I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Associated Wholesale Grocers</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, PostgreSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5985bee213bf40</t>
+          <t>https://www.indeed.com/viewjob?jk=693f3e0a054607b0</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Snowflake SME</t>
+          <t>AI DevOps Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>Reef Capital Partners</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Snowflake, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccefe385c15cc707</t>
+          <t>https://www.indeed.com/viewjob?jk=1e695ed23053b341</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Snowflake SME</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b7f8d62e370d21c</t>
+          <t>https://www.indeed.com/viewjob?jk=ccefe385c15cc707</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>The Friedkin Group</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Dataflow, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7ede0f34ce25b71</t>
+          <t>https://www.indeed.com/viewjob?jk=1b7f8d62e370d21c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>The Friedkin Group</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Dataflow, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30154588ed7f957f</t>
+          <t>https://www.indeed.com/viewjob?jk=f7ede0f34ce25b71</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Remote)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
+          <t>AWS, S3, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64eeda5b2dfcfe99</t>
+          <t>https://www.indeed.com/viewjob?jk=30154588ed7f957f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Machine Learning Engineer (Remote)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a077c257a4cf0b5</t>
+          <t>https://www.indeed.com/viewjob?jk=64eeda5b2dfcfe99</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Engineer - Wire Payments Platform</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55c16c38ef65d0c6</t>
+          <t>https://www.indeed.com/viewjob?jk=4a077c257a4cf0b5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (171679)</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Hightower Advisors</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b373595b350ec3d</t>
+          <t>https://www.indeed.com/viewjob?jk=73d8a7818486ff2d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Solutions Architect III</t>
+          <t>SAP Application Support Trainee</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>IDEMIA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b223a04c01fe717f</t>
+          <t>https://www.indeed.com/viewjob?jk=71e8e9db0adaeff1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Shield</t>
+          <t>Machine Learning Engineer (171679)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Box</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88492e295288a867</t>
+          <t>https://www.indeed.com/viewjob?jk=7b373595b350ec3d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Eurest</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74494a10316e7fe4</t>
+          <t>https://www.indeed.com/viewjob?jk=a4699f552f08a017</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Visualization Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Delta Live Tables, BigQuery, Spark, Snowflake, Databricks Lakehouse, ELT, dbt</t>
+          <t>Redshift, S3, RDS, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39ce7a464350b080</t>
+          <t>https://www.indeed.com/viewjob?jk=867f580c7e3bb0e7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SENIOR POWER BI DEVELOPER (HYBRID - REDMOND, WA)</t>
+          <t>Senior Software Engineer- Policy Configuration</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Eurest</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4699f552f08a017</t>
+          <t>https://www.indeed.com/viewjob?jk=1acf3efd34722f19</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Visualization Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
+          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=867f580c7e3bb0e7</t>
+          <t>https://www.indeed.com/viewjob?jk=74494a10316e7fe4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Policy Configuration</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Bayer</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,59 +2281,59 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1acf3efd34722f19</t>
+          <t>https://www.indeed.com/viewjob?jk=defb7c286d56b171</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer III - Data Engineering Java/Python</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Zonos</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Saint George, UT, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bee8d25021d9111</t>
+          <t>https://www.indeed.com/viewjob?jk=5ec8999487afb4f6</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Engineering Java/Python</t>
+          <t>Data Engineer II 4P/554</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>4P Consulting Inc.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Oracle, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ec8999487afb4f6</t>
+          <t>https://www.indeed.com/viewjob?jk=43d963e021c819ac</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer II 4P/554</t>
+          <t>Senior Data Engineer, CRM</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Oracle, SQL Server, NoSQL, Data Modeling</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d963e021c819ac</t>
+          <t>https://www.indeed.com/viewjob?jk=7b266df7f25223b6</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, CRM</t>
+          <t>Data Operations Developer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Geotab</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,17 +2411,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b266df7f25223b6</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd3315942275dbc</t>
         </is>
       </c>
     </row>
@@ -2463,17 +2463,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Chess.com</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ada1c920f207c639</t>
+          <t>https://www.indeed.com/viewjob?jk=b11bc9d20fc1e2e2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Operations Developer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Geotab</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd3315942275dbc</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a6f623279ee6d4</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Manufacturing Systems Integration Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,17 +2551,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, Power BI, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8532be76b040bdb</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3cccca60e879db</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b11bc9d20fc1e2e2</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f821dc8a5f6559</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Full Stack Engineer, Consultant</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a6f623279ee6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=1e6f7f78ae5d82f3</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Senior Backend Software Engineer (HPC/AI &amp; Distributed Systems)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3cccca60e879db</t>
+          <t>https://www.indeed.com/viewjob?jk=dce54831329652c4</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Manufacturing Systems Integration Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,112 +2691,112 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, Power BI, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f821dc8a5f6559</t>
+          <t>https://www.indeed.com/viewjob?jk=d8532be76b040bdb</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Consultant</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Finance of America</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>AWS, Azure, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, MS Excel, Python</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e6f7f78ae5d82f3</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8846493996e830</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Burrell Behavioral Health</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3763de2ff690fcf</t>
+          <t>https://www.indeed.com/viewjob?jk=2ff4ba7951fc9c97</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>MLOps Platform Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,42 +2806,42 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3583ff1e8ab8b831</t>
+          <t>https://www.indeed.com/viewjob?jk=4687b9b235a9a6ce</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Machine Learning Engineer II (Remote)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Dresher, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, CI/CD, Git, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a764bcc9a479a693</t>
+          <t>https://www.indeed.com/viewjob?jk=dd0ef78a415d3113</t>
         </is>
       </c>
     </row>
@@ -2853,20 +2853,20 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Newton, MA, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Spark, Scala, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,129 +2876,129 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8b0a891a5da57c1</t>
+          <t>https://www.indeed.com/viewjob?jk=e7929c83226ae75b</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fdde135d701446e</t>
+          <t>https://www.indeed.com/viewjob?jk=62210abb12166a07</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ascensus</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, DynamoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68e8fc35af3fc28f</t>
+          <t>https://www.indeed.com/viewjob?jk=26a71508d797185b</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer (HPC/AI &amp; Distributed Systems)</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>A. Duie Pyle, INC.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, CloudWatch, Python</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dce54831329652c4</t>
+          <t>https://www.indeed.com/viewjob?jk=df95271c65edaa7c</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Consultant, Data Management</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Finance of America</t>
+          <t>Beghou Consulting</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Thousand Oaks, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, MS Excel, Python</t>
+          <t>Azure, Data Factory, Databricks, Snowflake, Oracle, PostgreSQL, MySQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8846493996e830</t>
+          <t>https://www.indeed.com/viewjob?jk=a1ad03af6a4ac792</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Burrell Behavioral Health</t>
+          <t>University of Texas Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ff4ba7951fc9c97</t>
+          <t>https://www.indeed.com/viewjob?jk=6fff225f154716cc</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MLOps Platform Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>NiyamIT</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4687b9b235a9a6ce</t>
+          <t>https://www.indeed.com/viewjob?jk=1a1802cfcb8371e8</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II (Remote)</t>
+          <t>(Remote) Fullstack Software Engineer (Special Projects Team)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Aeroflow Health</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Asheville, NC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, CI/CD, Git, Python, SQL, Java</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd0ef78a415d3113</t>
+          <t>https://www.indeed.com/viewjob?jk=61e2c56fc5827763</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Spark, Scala, CI/CD, Terraform, Git</t>
+          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7929c83226ae75b</t>
+          <t>https://www.indeed.com/viewjob?jk=77bef7280137d41c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Senior DevOps Engineer (Remote)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Tango</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62210abb12166a07</t>
+          <t>https://www.indeed.com/viewjob?jk=8d66e27cb89a5630</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
+          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26a71508d797185b</t>
+          <t>https://www.indeed.com/viewjob?jk=bc8599dc51df5400</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Enterprise AI Architect</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=291c96af0e7cea02</t>
+          <t>https://www.indeed.com/viewjob?jk=503269b060f28151</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Remote)</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Tango</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d66e27cb89a5630</t>
+          <t>https://www.indeed.com/viewjob?jk=dbeb792ea58b7a87</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Product Engineer, Partnerships</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Replit</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,14 +3331,14 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b40a810716931b39</t>
+          <t>https://www.indeed.com/viewjob?jk=fd899ffea8f1b74c</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3366,14 +3366,14 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503269b060f28151</t>
+          <t>https://www.indeed.com/viewjob?jk=f22565dd904e0808</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbeb792ea58b7a87</t>
+          <t>https://www.indeed.com/viewjob?jk=f8fcbfbc5352b0bf</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>University of Texas Health Science Center at San Antonio</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fff225f154716cc</t>
+          <t>https://www.indeed.com/viewjob?jk=d1da94812ec374b4</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Teradata Developer-5</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f4f91dff933f5cc</t>
+          <t>https://www.indeed.com/viewjob?jk=ee5cdada52faf29e</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>NiyamIT</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a1802cfcb8371e8</t>
+          <t>https://www.indeed.com/viewjob?jk=5676e61db2aa81f3</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer III - DevOps Automation Engineer</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58638a1a93a5925c</t>
+          <t>https://www.indeed.com/viewjob?jk=de6aa6e4975245c5</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>(Remote) Fullstack Software Engineer (Special Projects Team)</t>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Aeroflow Health</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Asheville, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, DynamoDB, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61e2c56fc5827763</t>
+          <t>https://www.indeed.com/viewjob?jk=e73fae08616e3afd</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77bef7280137d41c</t>
+          <t>https://www.indeed.com/viewjob?jk=2cdec8d2c07ce6a8</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
+          <t>Software Engineer III - DevOps Automation Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc8599dc51df5400</t>
+          <t>https://www.indeed.com/viewjob?jk=58638a1a93a5925c</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Enterprise AI Architect</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,322 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd899ffea8f1b74c</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f22565dd904e0808</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f8fcbfbc5352b0bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Senior Engineer - .NET</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d1da94812ec374b4</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ee5cdada52faf29e</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Engineer II</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5676e61db2aa81f3</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Engineer II- .Net</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=de6aa6e4975245c5</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e73fae08616e3afd</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2cdec8d2c07ce6a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Matrix Medical Network</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-01-29</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=939ed479d96c418b</t>
+          <t>https://www.indeed.com/viewjob?jk=291c96af0e7cea02</t>
         </is>
       </c>
     </row>
